--- a/セリフ編集/キャラタイプ別/丁寧×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×真面目.xlsx
@@ -482,7 +482,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H334"/>
+  <dimension ref="A1:H358"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1948,7 +1948,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.earnest.polite[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest.polite[1]</t>
+          <t xml:space="preserve">ahead.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1973,14 +1973,14 @@
       </c>
       <c r="F46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……認めません。こんな結末は……認められません</t>
+          <t xml:space="preserve">済んだことにしたいのです。……できないだけで</t>
         </is>
       </c>
     </row>
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.earnest.polite[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1990,12 +1990,12 @@
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.earnest.polite[1]</t>
+          <t xml:space="preserve">behind.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -2005,14 +2005,14 @@
       </c>
       <c r="F47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着がつきました。……もう、十分です</t>
+          <t xml:space="preserve">決着は……ついておりません。私の中では、まだ</t>
         </is>
       </c>
     </row>
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.earnest.polite[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="12">
@@ -2037,14 +2037,14 @@
       </c>
       <c r="F48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けました。でもこの試合は一生の宝です</t>
+          <t xml:space="preserve">……認めません。こんな結末は……認められません</t>
         </is>
       </c>
     </row>
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.earnest.polite[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="12">
@@ -2069,14 +2069,14 @@
       </c>
       <c r="F49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたのおかげで成長できました。これからもよろしくお願いいたします</t>
+          <t xml:space="preserve">決着がつきました。……もう、十分です</t>
         </is>
       </c>
     </row>
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.earnest.polite[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -2086,12 +2086,12 @@
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.earnest.polite[1]</t>
+          <t xml:space="preserve">loser.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -2101,14 +2101,14 @@
       </c>
       <c r="F50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本日こそ、決着をつけさせていただきます</t>
+          <t xml:space="preserve">負けました。でもこの試合は一生の宝です</t>
         </is>
       </c>
     </row>
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.earnest.polite[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.earnest.polite[1]</t>
+          <t xml:space="preserve">winner.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -2133,14 +2133,14 @@
       </c>
       <c r="F51" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力でお相手させていただきます</t>
+          <t xml:space="preserve">あなたのおかげで成長できました。これからもよろしくお願いいたします</t>
         </is>
       </c>
     </row>
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.earnest.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D52" t="inlineStr" s="12">
@@ -2165,14 +2165,14 @@
       </c>
       <c r="F52" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この日を、ずっと待っておりました。全てを賭けます</t>
+          <t xml:space="preserve">本日こそ、決着をつけさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.earnest.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D53" t="inlineStr" s="12">
@@ -2197,14 +2197,14 @@
       </c>
       <c r="F53" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……はい。全力で、お受けいたします</t>
+          <t xml:space="preserve">全力でお相手させていただきます</t>
         </is>
       </c>
     </row>
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.earnest.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D54" t="inlineStr" s="12">
@@ -2229,14 +2229,14 @@
       </c>
       <c r="F54" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本日、決着をつけさせていただきます</t>
+          <t xml:space="preserve">……この日を、ずっと待っておりました。全てを賭けます</t>
         </is>
       </c>
     </row>
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.earnest.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="12">
@@ -2261,14 +2261,14 @@
       </c>
       <c r="F55" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お受けいたします。全力で参ります</t>
+          <t xml:space="preserve">……はい。全力で、お受けいたします</t>
         </is>
       </c>
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.earnest.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.earnest.polite[1]</t>
+          <t xml:space="preserve">attacker.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2293,14 +2293,14 @@
       </c>
       <c r="F56" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悔しいです。でも、次は必ず</t>
+          <t xml:space="preserve">本日、決着をつけさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.earnest.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2310,12 +2310,12 @@
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.earnest.polite[1]</t>
+          <t xml:space="preserve">defender.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2325,14 +2325,14 @@
       </c>
       <c r="F57" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝たせていただきました。でもまだ……終わりではありません</t>
+          <t xml:space="preserve">お受けいたします。全力で参ります</t>
         </is>
       </c>
     </row>
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.earnest.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest.polite[1]</t>
+          <t xml:space="preserve">loserLines.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2357,14 +2357,14 @@
       </c>
       <c r="F58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けました…でも、次の機会に必ず結果を出してみせます</t>
+          <t xml:space="preserve">……悔しいです。でも、次は必ず</t>
         </is>
       </c>
     </row>
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.earnest.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.earnest.polite[1]</t>
+          <t xml:space="preserve">winnerLines.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2389,14 +2389,14 @@
       </c>
       <c r="F59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ひとまず決着です…でも、まだ先がある気がするんです</t>
+          <t xml:space="preserve">勝たせていただきました。でもまだ……終わりではありません</t>
         </is>
       </c>
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.earnest.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.earnest.polite[1]</t>
+          <t xml:space="preserve">loser.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -2421,14 +2421,14 @@
       </c>
       <c r="F60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな……全力を出したはずなのに……</t>
+          <t xml:space="preserve">負けました…でも、次の機会に必ず結果を出してみせます</t>
         </is>
       </c>
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.earnest.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.earnest.polite[1]</t>
+          <t xml:space="preserve">winner.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -2453,14 +2453,14 @@
       </c>
       <c r="F61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました……！ ずっと追いかけてきた背中に……ついに……！</t>
+          <t xml:space="preserve">ひとまず決着です…でも、まだ先がある気がするんです</t>
         </is>
       </c>
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.earnest.polite[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.earnest.polite[1]</t>
+          <t xml:space="preserve">loserLines.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
@@ -2485,14 +2485,14 @@
       </c>
       <c r="F62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}が深く息を吸い、言い放った。「これ以上は……お許しいただけません。全力で参ります」</t>
+          <t xml:space="preserve">こんな……全力を出したはずなのに……</t>
         </is>
       </c>
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.polite_earnest.lose[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2502,29 +2502,29 @@
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_earnest.lose[1]</t>
+          <t xml:space="preserve">winnerLines.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けました。申し訳ありません。</t>
+          <t xml:space="preserve">勝ちました……！ ずっと追いかけてきた背中に……ついに……！</t>
         </is>
       </c>
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.polite_earnest.lose[2]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2534,29 +2534,29 @@
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
         </is>
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_earnest.lose[2]</t>
+          <t xml:space="preserve">awakening.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てませんでした。……社長の顔に、泥を塗ってしまいました。</t>
+          <t xml:space="preserve">{nameB}が深く息を吸い、言い放った。「これ以上は……お許しいただけません。全力で参ります」</t>
         </is>
       </c>
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.polite_earnest.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.polite_earnest.lose[1]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_earnest.lose[3]</t>
+          <t xml:space="preserve">polite_earnest.lose[1]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr" s="2">
@@ -2581,14 +2581,14 @@
       </c>
       <c r="F65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すみません。……許していただいたのに、この結果で。</t>
+          <t xml:space="preserve">……負けました。申し訳ありません。</t>
         </is>
       </c>
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.polite_earnest.petition[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.polite_earnest.lose[2]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_earnest.petition[1]</t>
+          <t xml:space="preserve">polite_earnest.lose[2]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr" s="2">
@@ -2613,14 +2613,14 @@
       </c>
       <c r="F66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、ご迷惑は承知しています。それでも、あの方とやらせていただけませんか。</t>
+          <t xml:space="preserve">勝てませんでした。……社長の顔に、泥を塗ってしまいました。</t>
         </is>
       </c>
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.polite_earnest.petition[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.polite_earnest.lose[3]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_earnest.petition[2]</t>
+          <t xml:space="preserve">polite_earnest.lose[3]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr" s="2">
@@ -2645,14 +2645,14 @@
       </c>
       <c r="F67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不躾なお願いだと分かっています。……あの方と、闘わせてください。</t>
+          <t xml:space="preserve">すみません。……許していただいたのに、この結果で。</t>
         </is>
       </c>
     </row>
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.polite_earnest.petition[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.polite_earnest.petition[1]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_earnest.petition[3]</t>
+          <t xml:space="preserve">polite_earnest.petition[1]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr" s="2">
@@ -2677,14 +2677,14 @@
       </c>
       <c r="F68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。どうかお願いします。あの方とだけは、やらせていただきたくて。</t>
+          <t xml:space="preserve">社長、ご迷惑は承知しています。それでも、あの方とやらせていただけませんか。</t>
         </is>
       </c>
     </row>
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.polite_earnest.sendoff[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.polite_earnest.petition[2]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_earnest.sendoff[1]</t>
+          <t xml:space="preserve">polite_earnest.petition[2]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr" s="2">
@@ -2709,14 +2709,14 @@
       </c>
       <c r="F69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。……このご恩は、必ず結果でお返しします。</t>
+          <t xml:space="preserve">不躾なお願いだと分かっています。……あの方と、闘わせてください。</t>
         </is>
       </c>
     </row>
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.polite_earnest.sendoff[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.polite_earnest.petition[3]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_earnest.sendoff[2]</t>
+          <t xml:space="preserve">polite_earnest.petition[3]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr" s="2">
@@ -2741,14 +2741,14 @@
       </c>
       <c r="F70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">許していただけて、本当に嬉しいです。行ってまいります。</t>
+          <t xml:space="preserve">社長。どうかお願いします。あの方とだけは、やらせていただきたくて。</t>
         </is>
       </c>
     </row>
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.polite_earnest.sendoff[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.polite_earnest.sendoff[1]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_earnest.sendoff[3]</t>
+          <t xml:space="preserve">polite_earnest.sendoff[1]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr" s="2">
@@ -2773,14 +2773,14 @@
       </c>
       <c r="F71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わがままを聞いていただいて、ありがとうございます。精一杯やってきます。</t>
+          <t xml:space="preserve">ありがとうございます。……このご恩は、必ず結果でお返しします。</t>
         </is>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.polite_earnest.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.polite_earnest.sendoff[2]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_earnest.win[1]</t>
+          <t xml:space="preserve">polite_earnest.sendoff[2]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr" s="2">
@@ -2805,14 +2805,14 @@
       </c>
       <c r="F72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました。……社長、ありがとうございました。</t>
+          <t xml:space="preserve">許していただけて、本当に嬉しいです。行ってまいります。</t>
         </is>
       </c>
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.polite_earnest.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.polite_earnest.sendoff[3]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_earnest.win[2]</t>
+          <t xml:space="preserve">polite_earnest.sendoff[3]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr" s="2">
@@ -2837,14 +2837,14 @@
       </c>
       <c r="F73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">無理を聞いていただいた甲斐が、ありました。本当にありがとうございます。</t>
+          <t xml:space="preserve">わがままを聞いていただいて、ありがとうございます。精一杯やってきます。</t>
         </is>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.polite_earnest.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.polite_earnest.win[1]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_earnest.win[3]</t>
+          <t xml:space="preserve">polite_earnest.win[1]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr" s="2">
@@ -2869,14 +2869,14 @@
       </c>
       <c r="F74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てました。……ご期待に応えられて、ほっとしています。</t>
+          <t xml:space="preserve">勝ちました。……社長、ありがとうございました。</t>
         </is>
       </c>
     </row>
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_earnest._accept[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.polite_earnest.win[2]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2886,12 +2886,12 @@
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_earnest._accept[1]</t>
+          <t xml:space="preserve">polite_earnest.win[2]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr" s="2">
@@ -2901,14 +2901,14 @@
       </c>
       <c r="F75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご指名、確かに受け取りました。全力でお相手します。</t>
+          <t xml:space="preserve">無理を聞いていただいた甲斐が、ありました。本当にありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_earnest._accept[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.polite_earnest.win[3]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_earnest._accept[2]</t>
+          <t xml:space="preserve">polite_earnest.win[3]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr" s="2">
@@ -2933,14 +2933,14 @@
       </c>
       <c r="F76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしを選んだのなら、その責任は果たします。</t>
+          <t xml:space="preserve">勝てました。……ご期待に応えられて、ほっとしています。</t>
         </is>
       </c>
     </row>
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_earnest._accept[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_earnest._accept[1]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_earnest._accept[3]</t>
+          <t xml:space="preserve">polite_earnest._accept[1]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr" s="2">
@@ -2965,14 +2965,14 @@
       </c>
       <c r="F77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お受けします。半端な気持ちでは、向き合いません。</t>
+          <t xml:space="preserve">ご指名、確かに受け取りました。全力でお相手します。</t>
         </is>
       </c>
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_earnest.draw[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_earnest._accept[2]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_earnest.draw[1]</t>
+          <t xml:space="preserve">polite_earnest._accept[2]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr" s="2">
@@ -2997,14 +2997,14 @@
       </c>
       <c r="F78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着がつかないのが、いちばん心残りです。</t>
+          <t xml:space="preserve">わたしを選んだのなら、その責任は果たします。</t>
         </is>
       </c>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_earnest.draw[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_earnest._accept[3]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_earnest.draw[2]</t>
+          <t xml:space="preserve">polite_earnest._accept[3]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr" s="2">
@@ -3029,14 +3029,14 @@
       </c>
       <c r="F79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ終わっていません。必ず、続きを。</t>
+          <t xml:space="preserve">お受けします。半端な気持ちでは、向き合いません。</t>
         </is>
       </c>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_earnest.draw[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_earnest.draw[1]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_earnest.draw[3]</t>
+          <t xml:space="preserve">polite_earnest.draw[1]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr" s="2">
@@ -3061,14 +3061,14 @@
       </c>
       <c r="F80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決めきれず、申し訳ないです。……次は必ず。</t>
+          <t xml:space="preserve">決着がつかないのが、いちばん心残りです。</t>
         </is>
       </c>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_earnest.lose[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_earnest.draw[2]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_earnest.lose[1]</t>
+          <t xml:space="preserve">polite_earnest.draw[2]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr" s="2">
@@ -3093,14 +3093,14 @@
       </c>
       <c r="F81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……受けておいて、この結果です。悔やみます。</t>
+          <t xml:space="preserve">まだ終わっていません。必ず、続きを。</t>
         </is>
       </c>
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_earnest.lose[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_earnest.draw[3]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_earnest.lose[2]</t>
+          <t xml:space="preserve">polite_earnest.draw[3]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr" s="2">
@@ -3125,14 +3125,14 @@
       </c>
       <c r="F82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたが上でした。言い訳はいたしません。</t>
+          <t xml:space="preserve">決めきれず、申し訳ないです。……次は必ず。</t>
         </is>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_earnest.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_earnest.lose[1]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_earnest.lose[3]</t>
+          <t xml:space="preserve">polite_earnest.lose[1]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr" s="2">
@@ -3157,14 +3157,14 @@
       </c>
       <c r="F83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしの力不足です。……この負けは、忘れません。</t>
+          <t xml:space="preserve">……受けておいて、この結果です。悔やみます。</t>
         </is>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_earnest.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_earnest.lose[2]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_earnest.win[1]</t>
+          <t xml:space="preserve">polite_earnest.lose[2]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
@@ -3189,14 +3189,14 @@
       </c>
       <c r="F84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">受けた以上、負けるわけにはいきませんでした。</t>
+          <t xml:space="preserve">あなたが上でした。言い訳はいたしません。</t>
         </is>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_earnest.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_earnest.lose[3]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_earnest.win[2]</t>
+          <t xml:space="preserve">polite_earnest.lose[3]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
@@ -3221,14 +3221,14 @@
       </c>
       <c r="F85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたの本気、確かに受け止めました。</t>
+          <t xml:space="preserve">わたしの力不足です。……この負けは、忘れません。</t>
         </is>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_earnest.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_earnest.win[1]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite_earnest.win[3]</t>
+          <t xml:space="preserve">polite_earnest.win[1]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3253,14 +3253,14 @@
       </c>
       <c r="F86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました。あなたの覚悟には、応えられたはずです。</t>
+          <t xml:space="preserve">受けた以上、負けるわけにはいきませんでした。</t>
         </is>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.earnest.polite[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_earnest.win[2]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3270,29 +3270,29 @@
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.earnest.polite[1]</t>
+          <t xml:space="preserve">polite_earnest.win[2]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いただいたご恩、新天地で結果として返させていただきます</t>
+          <t xml:space="preserve">あなたの本気、確かに受け止めました。</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.earnest.polite[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.polite_earnest.win[3]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3302,29 +3302,29 @@
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.earnest.polite[1]</t>
+          <t xml:space="preserve">polite_earnest.win[3]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身に余るお言葉です。…ここで結果を出します</t>
+          <t xml:space="preserve">勝ちました。あなたの覚悟には、応えられたはずです。</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.earnest.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.earnest.polite[1]</t>
+          <t xml:space="preserve">accepted.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3349,14 +3349,14 @@
       </c>
       <c r="F89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お引き留めに応えられず、本当に申し訳ありません</t>
+          <t xml:space="preserve">いただいたご恩、新天地で結果として返させていただきます</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.earnest.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.earnest.polite[1]</t>
+          <t xml:space="preserve">defended.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3381,14 +3381,14 @@
       </c>
       <c r="F90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかりました。まだやれることがあるなら続けます</t>
+          <t xml:space="preserve">身に余るお言葉です。…ここで結果を出します</t>
         </is>
       </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.earnest.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.earnest.polite[1]</t>
+          <t xml:space="preserve">defense_failed.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3413,14 +3413,14 @@
       </c>
       <c r="F91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後にもう一度…あのベルトに恥じない闘いをしたいです</t>
+          <t xml:space="preserve">お引き留めに応えられず、本当に申し訳ありません</t>
         </is>
       </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.earnest.polite[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.earnest.polite[1]</t>
+          <t xml:space="preserve">default.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3445,14 +3445,14 @@
       </c>
       <c r="F92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかりました。まだお役に立てるなら全力で</t>
+          <t xml:space="preserve">…わかりました。まだやれることがあるなら続けます</t>
         </is>
       </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.earnest.polite[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.earnest.polite[1]</t>
+          <t xml:space="preserve">former_champ.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3477,14 +3477,14 @@
       </c>
       <c r="F93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">信じてくださってありがとうございます。期待に応えます</t>
+          <t xml:space="preserve">最後にもう一度…あのベルトに恥じない闘いをしたいです</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.earnest.polite[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.earnest.polite[1]</t>
+          <t xml:space="preserve">heel.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3509,14 +3509,14 @@
       </c>
       <c r="F94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後によい試合を。それだけが望みです</t>
+          <t xml:space="preserve">…わかりました。まだお役に立てるなら全力で</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.earnest.polite[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.earnest.polite[1]</t>
+          <t xml:space="preserve">high_trust.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3541,14 +3541,14 @@
       </c>
       <c r="F95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかりました。最後まで演じきれたなら本望です</t>
+          <t xml:space="preserve">信じてくださってありがとうございます。期待に応えます</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.earnest.polite[1]</t>
+          <t xml:space="preserve">accept_former_champ.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3573,14 +3573,14 @@
       </c>
       <c r="F96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…覚悟はできていました。言ってくださってありがとうございます</t>
+          <t xml:space="preserve">最後によい試合を。それだけが望みです</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.earnest.polite[1]</t>
+          <t xml:space="preserve">accept_heel.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3605,14 +3605,14 @@
       </c>
       <c r="F97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。言ってくださって助かりました</t>
+          <t xml:space="preserve">…わかりました。最後まで演じきれたなら本望です</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.earnest.polite[1]</t>
+          <t xml:space="preserve">accept_no_title.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3637,14 +3637,14 @@
       </c>
       <c r="F98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと早く気づくべきでした。…わかりました</t>
+          <t xml:space="preserve">…覚悟はできていました。言ってくださってありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.earnest.polite[1]</t>
+          <t xml:space="preserve">accept_terminal.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3669,14 +3669,14 @@
       </c>
       <c r="F99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このベルトの重みをまだ背負えます。引退はしません</t>
+          <t xml:space="preserve">ありがとうございます。言ってくださって助かりました</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3686,12 +3686,12 @@
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.earnest.polite[1]</t>
+          <t xml:space="preserve">accept_winless.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3701,14 +3701,14 @@
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体のために尽くしてきました。嘘ではありません</t>
+          <t xml:space="preserve">もっと早く気づくべきでした。…わかりました</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.earnest.polite[1]</t>
+          <t xml:space="preserve">refuse_champ.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3733,14 +3733,14 @@
       </c>
       <c r="F101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだやれることがあります。止まるわけにはいきません</t>
+          <t xml:space="preserve">このベルトの重みをまだ背負えます。引退はしません</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.earnest.polite[1]</t>
+          <t xml:space="preserve">refuse_distrust.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3765,14 +3765,14 @@
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次の興行で証明します。後悔させてみせます</t>
+          <t xml:space="preserve">この団体のために尽くしてきました。嘘ではありません</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.earnest.polite[1]</t>
+          <t xml:space="preserve">refuse_fighting.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3797,14 +3797,14 @@
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このベルトに恥じない闘いを…最後までできたと思います</t>
+          <t xml:space="preserve">まだやれることがあります。止まるわけにはいきません</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.earnest.polite[1]</t>
+          <t xml:space="preserve">refuse_heel.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3829,14 +3829,14 @@
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">夢には届きませんでした。でもこの道を選んだことに嘘はありません</t>
+          <t xml:space="preserve">次の興行で証明します。後悔させてみせます</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.earnest.polite[1]</t>
+          <t xml:space="preserve">A1_champion.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3861,14 +3861,14 @@
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嫌われ役は…誰かがやらなければいけませんでしたから</t>
+          <t xml:space="preserve">このベルトに恥じない闘いを…最後までできたと思います</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.earnest.polite[1]</t>
+          <t xml:space="preserve">A2_uncrowned.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3893,14 +3893,14 @@
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で走り抜けました。この時間に嘘はありません</t>
+          <t xml:space="preserve">夢には届きませんでした。でもこの道を選んだことに嘘はありません</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.earnest.polite[1]</t>
+          <t xml:space="preserve">A3_heel.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3925,14 +3925,14 @@
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ何もお返しできていないのに…受け入れられません</t>
+          <t xml:space="preserve">嫌われ役は…誰かがやらなければいけませんでしたから</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.earnest.polite[1]</t>
+          <t xml:space="preserve">A4_veteran.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3957,14 +3957,14 @@
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ足りませんでした。もっと…やりたかったです</t>
+          <t xml:space="preserve">全力で走り抜けました。この時間に嘘はありません</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.earnest.polite[1]</t>
+          <t xml:space="preserve">B1_young.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3989,14 +3989,14 @@
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔いがないとは言えません。でも…やりきりました</t>
+          <t xml:space="preserve">まだ何もお返しできていないのに…受け入れられません</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.earnest.polite[1]</t>
+          <t xml:space="preserve">B2_prime.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -4021,14 +4021,14 @@
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後の防衛戦…やりたかったです。それだけが心残りです</t>
+          <t xml:space="preserve">まだ足りませんでした。もっと…やりたかったです</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="C111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">B3_older.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -4053,14 +4053,14 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">来年もどうぞよろしくお願いいたします。精進してまいります</t>
+          <t xml:space="preserve">悔いがないとは言えません。でも…やりきりました</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -4070,29 +4070,29 @@
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.earnest.polite[1]</t>
+          <t xml:space="preserve">B4_champion_injury.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。ご期待に沿えるよう、精一杯努めます。</t>
+          <t xml:space="preserve">最後の防衛戦…やりたかったです。それだけが心残りです</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.earnest.polite[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -4102,29 +4102,29 @@
       </c>
       <c r="C113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
         </is>
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとうございます。この額で精一杯、お応えいたします。</t>
+          <t xml:space="preserve">来年もどうぞよろしくお願いいたします。精進してまいります</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.earnest.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.earnest.polite[1]</t>
+          <t xml:space="preserve">raise_accept.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -4149,14 +4149,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……残念ですが、承知いたしました。ですが、この判断はお忘れなきよう。</t>
+          <t xml:space="preserve">ありがとうございます。ご期待に沿えるよう、精一杯努めます。</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.earnest.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.earnest.polite[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4181,14 +4181,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、お忙しいところ恐れ入ります。{tenure}契約について、ご相談させていただきたく…。{record}</t>
+          <t xml:space="preserve">……ありがとうございます。この額で精一杯、お応えいたします。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.earnest.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.earnest.polite[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4213,14 +4213,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……承知いたしました。ですが、このままでは…いずれ考えざるを得ません。</t>
+          <t xml:space="preserve">……残念ですが、承知いたしました。ですが、この判断はお忘れなきよう。</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.earnest.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.earnest.polite[1]</t>
+          <t xml:space="preserve">raise_open.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4245,14 +4245,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。{record}ここでの経験には心から感謝しております。ですが…新しい環境で挑戦させてください。</t>
+          <t xml:space="preserve">社長、お忙しいところ恐れ入ります。{tenure}契約について、ご相談させていただきたく…。{record}</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.earnest.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.earnest.polite[1]</t>
+          <t xml:space="preserve">raise_refuse.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4277,14 +4277,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。{tenure}大変申し訳ないのですが…退団のご相談をさせてください。</t>
+          <t xml:space="preserve">……承知いたしました。ですが、このままでは…いずれ考えざるを得ません。</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.earnest.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.earnest.polite[1]</t>
+          <t xml:space="preserve">sudden_departure.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4309,14 +4309,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……承知いたしました。{tenure_farewell}この団体での日々に、心から感謝いたします。{rivalry}</t>
+          <t xml:space="preserve">社長、長らくお世話になりました。ですが、もうここでは続けられません。</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.earnest.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.earnest.polite[2]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.earnest.polite[1]</t>
+          <t xml:space="preserve">sudden_departure.earnest.polite[2]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4341,14 +4341,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お心遣い、ありがとうございます。ですが…この決断は変わりません。申し訳ございません。</t>
+          <t xml:space="preserve">自分なりに、ずっと考えてまいりました。……退団させていただきます。</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.earnest.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.earnest.polite[1]</t>
+          <t xml:space="preserve">transfer_listen.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4373,274 +4373,274 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……社長のお気持ち、しかと受け止めました。もう一度、全力を尽くさせてください。</t>
+          <t xml:space="preserve">ありがとうございます。{record}ここでの経験には心から感謝しております。ですが…新しい環境で挑戦させてください。</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長。{tenure}大変申し訳ないのですが…退団のご相談をさせてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……承知いたしました。{tenure_farewell}この団体での日々に、心から感謝いたします。{rivalry}</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お心遣い、ありがとうございます。ですが…この決断は変わりません。申し訳ございません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……社長のお気持ち、しかと受け止めました。もう一度、全力を尽くさせてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.earnest.polite[1]</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr" s="2">
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr" s="12">
+      <c r="D126" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.earnest.polite[1]</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr" s="2">
+      <c r="E126" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr" s="3">
+      <c r="F126" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">今の仲間への責任があります。
 その気持ちがある限り、ここを離れる選択はできません</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="40" customHeight="1">
-      <c r="A123" t="inlineStr" s="15">
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.earnest.polite[1]</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr" s="2">
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr" s="12">
+      <c r="D127" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.earnest.polite[1]</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr" s="2">
+      <c r="E127" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr" s="3">
+      <c r="F127" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">皆さんを置いて行くわけにはいきません。
 …申し訳ありません</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="40" customHeight="1">
-      <c r="A124" t="inlineStr" s="15">
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.start.earnest.polite[1]</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr" s="2">
+      <c r="B128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr" s="12">
+      <c r="D128" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">start.earnest.polite[1]</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr" s="2">
+      <c r="E128" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr" s="3">
+      <c r="F128" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">この団体を離れるのは簡単ではありません。
 …でも、お聞きするだけなら</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="40" customHeight="1">
-      <c r="A125" t="inlineStr" s="15">
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.success.earnest.polite[1]</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr" s="2">
+      <c r="B129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr" s="12">
+      <c r="D129" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">success.earnest.polite[1]</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr" s="2">
+      <c r="E129" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr" s="3">
+      <c r="F129" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">新しい仲間のために…全力を尽くします。
 よろしくお願いいたします</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="40" customHeight="1">
-      <c r="A126" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.polite.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.polite.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、お忙しいところ恐縮ですが、私たちのメンバーのこと、お気遣いいただけませんでしょうか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="40" customHeight="1">
-      <c r="A127" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.polite.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.polite.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、お忙しいところ恐縮ですが、次の興行のメインを私たちにお任せいただけませんでしょうか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="40" customHeight="1">
-      <c r="A128" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.polite.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.polite.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、不躾で申し訳ありませんが、私たちのメンバーの待遇を一度ご再考いただけませんでしょうか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="40" customHeight="1">
-      <c r="A129" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.polite.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.polite.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、お忙しいところ恐縮ですが、私たちの貢献にお言葉をいただけませんでしょうか。</t>
-        </is>
-      </c>
-    </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.polite.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4665,14 +4665,14 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、本当にありがとうございます。お言葉、大切にいたします。</t>
+          <t xml:space="preserve">社長、お忙しいところ恐縮ですが、私たちのメンバーのこと、お気遣いいただけませんでしょうか。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.polite.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4697,14 +4697,14 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。お時間を取らせて、申し訳ありません。</t>
+          <t xml:space="preserve">社長、お忙しいところ恐縮ですが、次の興行のメインを私たちにお任せいただけませんでしょうか。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.polite.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4729,14 +4729,14 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、しっかり受け取ります。</t>
+          <t xml:space="preserve">社長、不躾で申し訳ありませんが、私たちのメンバーの待遇を一度ご再考いただけませんでしょうか。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.polite.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4761,14 +4761,14 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、本当にありがとうございます。お預かりしたメイン、最後まで責任持って務めます。</t>
+          <t xml:space="preserve">社長、お忙しいところ恐縮ですが、私たちの貢献にお言葉をいただけませんでしょうか。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4793,14 +4793,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。出過ぎたことを申しました。失礼いたしました。</t>
+          <t xml:space="preserve">社長、本当にありがとうございます。お言葉、大切にいたします。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4825,14 +4825,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、しっかり受け取ります。</t>
+          <t xml:space="preserve">…承知しました。お時間を取らせて、申し訳ありません。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4857,14 +4857,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、本当にありがとうございます。皆を代表してお礼申し上げます。</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、しっかり受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4889,14 +4889,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。図々しいお願いをしてしまい、申し訳ありません。</t>
+          <t xml:space="preserve">社長、本当にありがとうございます。お預かりしたメイン、最後まで責任持って務めます。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4921,14 +4921,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。お金以外で気にかけていただけるなんて、ありがたいです。</t>
+          <t xml:space="preserve">…承知しました。出過ぎたことを申しました。失礼いたしました。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4953,14 +4953,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、本当にありがとうございます。お言葉、大切にいたします。</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、しっかり受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4985,14 +4985,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。図々しいお願いをしてしまい、申し訳ありません。</t>
+          <t xml:space="preserve">社長、本当にありがとうございます。皆を代表してお礼申し上げます。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -5017,14 +5017,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。形は違っても、お気持ちは伝わりました。</t>
+          <t xml:space="preserve">…承知しました。図々しいお願いをしてしまい、申し訳ありません。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -5049,14 +5049,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。輪の外にいる子のお気持ち、見えていませんでした。</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。お金以外で気にかけていただけるなんて、ありがたいです。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -5081,14 +5081,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。寛容に甘え過ぎないように気をつけます。</t>
+          <t xml:space="preserve">社長、本当にありがとうございます。お言葉、大切にいたします。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -5113,14 +5113,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません、配慮が至りませんでした。</t>
+          <t xml:space="preserve">…承知しました。図々しいお願いをしてしまい、申し訳ありません。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -5145,14 +5145,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。形は違っても、お気持ちは伝わりました。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -5177,14 +5177,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。リングの外にまで持ち込むのは、行きすぎでした。</t>
+          <t xml:space="preserve">…申し訳ありません。輪の外にいる子のお気持ち、見えていませんでした。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5209,14 +5209,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。役柄の責任、まっとうします。</t>
+          <t xml:space="preserve">…ありがとうございます。寛容に甘え過ぎないように気をつけます。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5241,14 +5241,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。立場ある身で、本当にお恥ずかしいです。</t>
+          <t xml:space="preserve">…申し訳ありません、配慮が至りませんでした。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5273,14 +5273,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。本当に、お見逃しに甘えないようにします。</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5305,14 +5305,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。私の不在を、社長に拾っていただいて。</t>
+          <t xml:space="preserve">…申し訳ありません。リングの外にまで持ち込むのは、行きすぎでした。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5337,14 +5337,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。ご厚意に、しっかり甘えさせていただきます。</t>
+          <t xml:space="preserve">…ありがとうございます。役柄の責任、まっとうします。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5369,14 +5369,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご心配いただきありがとうございます。まだ立てます。</t>
+          <t xml:space="preserve">…申し訳ありません。立場ある身で、本当にお恥ずかしいです。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5401,14 +5401,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。チームで支えていただけるなら、持ち直せます。</t>
+          <t xml:space="preserve">…ありがとうございます。本当に、お見逃しに甘えないようにします。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5433,14 +5433,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。私が見ていれば、防げたはずです。</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。私の不在を、社長に拾っていただいて。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5465,14 +5465,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。穏便に収めるよう努めます。</t>
+          <t xml:space="preserve">…ありがとうございます。ご厚意に、しっかり甘えさせていただきます。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5497,14 +5497,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。私の力不足を、社長に補っていただいて。</t>
+          <t xml:space="preserve">…ご心配いただきありがとうございます。まだ立てます。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5529,14 +5529,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。私の振る舞いが至りませんでした。</t>
+          <t xml:space="preserve">…ありがとうございます。チームで支えていただけるなら、持ち直せます。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5561,14 +5561,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（唇を結び、深く頷いた）</t>
+          <t xml:space="preserve">…申し訳ありません。私が見ていれば、防げたはずです。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5593,14 +5593,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、しっかり受け取ります。</t>
+          <t xml:space="preserve">…ありがとうございます。穏便に収めるよう努めます。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5625,14 +5625,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。私の判断が、行きすぎていました。</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。私の力不足を、社長に補っていただいて。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5657,14 +5657,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。責任は私が持たせていただきます。</t>
+          <t xml:space="preserve">…申し訳ありません。私の振る舞いが至りませんでした。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5689,29 +5689,29 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。私が見落としていた負担を、社長に拾っていただいて。</t>
+          <t xml:space="preserve">（唇を結び、深く頷いた）</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F01_LEADER_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F01_LEADER_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5721,29 +5721,29 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みなさんのこと、必ず守ります。私、この団体で誰よりも本気ですから。</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、しっかり受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LEADER_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LEADER_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5753,14 +5753,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体のため、あえて分かれる道を選びます。中途半端には、しません。</t>
+          <t xml:space="preserve">…申し訳ありません。私の判断が、行きすぎていました。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.earnest.attack.polite</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.attack.polite</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5785,14 +5785,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">けじめを、つけさせてください</t>
+          <t xml:space="preserve">…ありがとうございます。責任は私が持たせていただきます。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.earnest.defend.polite</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.defend.polite</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5817,14 +5817,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げるつもりはありません</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。私が見落としていた負担を、社長に拾っていただいて。</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">FACTION_F01_LEADER_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES</t>
+          <t xml:space="preserve">FACTION_F01_LEADER_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
@@ -5849,14 +5849,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方がいらっしゃらない団体は、わたくしには想像もできません……。</t>
+          <t xml:space="preserve">みなさんのこと、必ず守ります。私、この団体で誰よりも本気ですから。</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">FACTION_F02_LEADER_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LEADER_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
@@ -5881,29 +5881,29 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">筋違いは承知の上で申し上げます。わたくし、あちらへ移らせていただきたく存じます。</t>
+          <t xml:space="preserve">団体のため、あえて分かれる道を選びます。中途半端には、しません。</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.earnest.attack.polite</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.attack.polite</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5913,29 +5913,29 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">申し上げにくいのですが……今のままでは、わたくしたち、息が詰まります。</t>
+          <t xml:space="preserve">けじめを、つけさせてください</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.earnest.defend.polite</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.defend.polite</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5945,14 +5945,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">きっかけがあれば、と思っておりました。今日がその日かもしれません。</t>
+          <t xml:space="preserve">逃げるつもりはありません</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES</t>
+          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
@@ -5977,14 +5977,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">畏れながら、わたくしたちの処遇について、再考いただきたく存じます。</t>
+          <t xml:space="preserve">あの方がいらっしゃらない団体は、わたくしには想像もできません……。</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">FACTION_F04_TARGET_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
+          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
@@ -6009,14 +6009,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">言葉ではもう届きません。リングで、決着をつけましょう。</t>
+          <t xml:space="preserve">筋違いは承知の上で申し上げます。わたくし、あちらへ移らせていただきたく存じます。</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.earnest.polite.hp_high[1]</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite.hp_high[1]</t>
+          <t xml:space="preserve">earnest.polite[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -6041,14 +6041,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……お見事でした。次は、こうはいきません</t>
+          <t xml:space="preserve">申し上げにくいのですが……今のままでは、わたくしたち、息が詰まります。</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.earnest.polite.high[1]</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite.high[1]</t>
+          <t xml:space="preserve">earnest.polite[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -6073,14 +6073,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">失礼いたしました。今日は、私が勝たせてもらいます</t>
+          <t xml:space="preserve">きっかけがあれば、と思っておりました。今日がその日かもしれません。</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.earnest.polite.high[1]</t>
+          <t xml:space="preserve">FACTION_F07_LEADER_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+          <t xml:space="preserve">FACTION_F07_LEADER_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite.high[1]</t>
+          <t xml:space="preserve">earnest.polite[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -6105,14 +6105,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日という日のために、私、ここまで来たんです</t>
+          <t xml:space="preserve">畏れながら、わたくしたちの処遇について、再考いただきたく存じます。</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.earnest.polite.high[2]</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite.high[2]</t>
+          <t xml:space="preserve">earnest.polite[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -6137,14 +6137,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">御免なさい。今日は手加減できません</t>
+          <t xml:space="preserve">言葉ではもう届きません。リングで、決着をつけましょう。</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.earnest.polite.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.earnest.polite.hp_high[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite.high[1]</t>
+          <t xml:space="preserve">earnest.polite.hp_high[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -6169,14 +6169,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご丁寧に、ありがとうございます。お受けいたします</t>
+          <t xml:space="preserve">……お見事でした。次は、こうはいきません</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.earnest.polite.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.earnest.polite.high[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
@@ -6201,14 +6201,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今夜の興行で、すべてを決めさせてください</t>
+          <t xml:space="preserve">失礼いたしました。今日は、私が勝たせてもらいます</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.earnest.polite.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.earnest.polite.high[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
@@ -6233,14 +6233,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お受けいたします。今夜、決着を</t>
+          <t xml:space="preserve">今日という日のために、私、ここまで来たんです</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.earnest.polite.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.earnest.polite.high[2]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite.high[1]</t>
+          <t xml:space="preserve">earnest.polite.high[2]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6265,14 +6265,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">御免なさい。今日だけは、譲れません</t>
+          <t xml:space="preserve">御免なさい。今日は手加減できません</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES.earnest.polite.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.earnest.polite.high[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
@@ -6297,142 +6297,142 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">光栄です。全力で、お相手します</t>
+          <t xml:space="preserve">ご丁寧に、ありがとうございます。お受けいたします</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.earnest.polite.high[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite.high[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習が実を結びました…！ まだ上を目指します</t>
+          <t xml:space="preserve">今夜の興行で、すべてを決めさせてください</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.earnest.polite.high[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite.high[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…あのお稽古が、今、実を結ぼうとしている——）</t>
+          <t xml:space="preserve">お受けいたします。今夜、決着を</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.earnest.polite[1]</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.earnest.polite.high[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite.high[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">限界に達しましたが…この道のりに誇りを持っています</t>
+          <t xml:space="preserve">御免なさい。今日だけは、譲れません</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.earnest.polite[1]</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES.earnest.polite.high[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite.high[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来ました。でもまだ、上を目指します</t>
+          <t xml:space="preserve">光栄です。全力で、お相手します</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.earnest.polite[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6457,14 +6457,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">日々の積み重ねが実を結んできました</t>
+          <t xml:space="preserve">練習が実を結びました…！ まだ上を目指します</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.earnest.polite[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6489,14 +6489,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全てを懸けてきた日々が…報われました</t>
+          <t xml:space="preserve">（…あのお稽古が、今、実を結ぼうとしている——）</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.earnest.polite[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.earnest.polite[1]</t>
+          <t xml:space="preserve">fresh.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6521,14 +6521,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援を力に変えて、もっと頑張ります</t>
+          <t xml:space="preserve">今日は身体が素直に動きます。学んだ分だけ、身につきます</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.earnest.polite[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6538,12 +6538,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.earnest.polite[1]</t>
+          <t xml:space="preserve">heavy.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6553,14 +6553,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この声援を力に、必ず期待に応えてみせます</t>
+          <t xml:space="preserve">同じ量をこなしても、何も積み上がりません。情けないです</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">warm.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6585,14 +6585,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日道場に来るのが…こんなに辛いとは思いませんでした</t>
+          <t xml:space="preserve">回数はこなせています。ただ、残る実感が薄くて</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">cap_reached.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6617,14 +6617,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">闘う気持ちを忘れていました…でも、もう迷いません</t>
+          <t xml:space="preserve">限界に達しましたが…この道のりに誇りを持っています</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">ovr_elite.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6649,14 +6649,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご迷惑をおかけしました…必ず、倍にしてお返しします</t>
+          <t xml:space="preserve">ここまで来ました。でもまだ、上を目指します</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.earnest.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.earnest.polite[1]</t>
+          <t xml:space="preserve">ovr_growth.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6681,14 +6681,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの試合から…自分の何が足りないのか、ずっと考えています</t>
+          <t xml:space="preserve">日々の積み重ねが実を結んできました</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.earnest.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.earnest.polite[1]</t>
+          <t xml:space="preserve">ovr_legend.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6713,14 +6713,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">復帰できたのですが…まだ全然、足りていません</t>
+          <t xml:space="preserve">全てを懸けてきた日々が…報われました</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.earnest.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.earnest.polite[1]</t>
+          <t xml:space="preserve">pop_growth.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6745,14 +6745,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">復帰できました…でも体が覚えているんです、あの痛みを</t>
+          <t xml:space="preserve">応援を力に変えて、もっと頑張ります</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.earnest.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.earnest.polite[1]</t>
+          <t xml:space="preserve">pop_star.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6777,14 +6777,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我は治りました。でも離れていた時間が…重いです</t>
+          <t xml:space="preserve">この声援を力に、必ず期待に応えてみせます</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.earnest.polite[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6794,29 +6794,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの試合は一生の宝物です。対戦相手の方に、心から感謝しています</t>
+          <t xml:space="preserve">毎日道場に来るのが…こんなに辛いとは思いませんでした</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.earnest.polite[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6826,29 +6826,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">王者としての責任を全うします。毎試合、最高の試合をお届けします</t>
+          <t xml:space="preserve">闘う気持ちを忘れていました…でも、もう迷いません</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.earnest.polite[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6858,29 +6858,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の皆さん。リングに真実があります。どうか、立ち続けてください</t>
+          <t xml:space="preserve">ご迷惑をおかけしました…必ず、倍にしてお返しします</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.earnest.polite[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6890,29 +6890,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.earnest.polite[1]</t>
+          <t xml:space="preserve">defeat.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">日々の積み重ねが実を結びました。来年も変わらず精進します</t>
+          <t xml:space="preserve">あの試合から…自分の何が足りないのか、ずっと考えています</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.earnest.polite[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6922,29 +6922,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.earnest.polite[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日の積み重ねが報われました。指導してくださった皆さん、ありがとうございます</t>
+          <t xml:space="preserve">復帰できたのですが…まだ全然、足りていません</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6954,29 +6954,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドーム大会という大役、謹んでお受けいたします</t>
+          <t xml:space="preserve">復帰できました…でも体が覚えているんです、あの痛みを</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.polite[2]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6986,29 +6986,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[2]</t>
+          <t xml:space="preserve">penalty_end.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後の最後まで、手を抜きません</t>
+          <t xml:space="preserve">怪我は治りました。でも離れていた時間が…重いです</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.polite[3]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -7018,12 +7018,12 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[3]</t>
+          <t xml:space="preserve">bestMatch.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -7033,14 +7033,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この恩に、必ず応えてみせます</t>
+          <t xml:space="preserve">あの試合は一生の宝物です。対戦相手の方に、心から感謝しています</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">champion.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -7065,14 +7065,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員のお客様、心より感謝申し上げます</t>
+          <t xml:space="preserve">王者としての責任を全うします。毎試合、最高の試合をお届けします</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.polite[2]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[2]</t>
+          <t xml:space="preserve">hallOfFame.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -7097,14 +7097,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力を尽くした甲斐がありました</t>
+          <t xml:space="preserve">後輩の皆さん。リングに真実があります。どうか、立ち続けてください</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.polite[3]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -7114,12 +7114,12 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[3]</t>
+          <t xml:space="preserve">mvp.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -7129,14 +7129,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次も、必ず期待に応えます</t>
+          <t xml:space="preserve">日々の積み重ねが実を結びました。来年も変わらず精進します</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.earnest.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -7146,29 +7146,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.earnest.polite[1]</t>
+          <t xml:space="preserve">rookie.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねが大切だと信じています。コツコツ参ります</t>
+          <t xml:space="preserve">毎日の積み重ねが報われました。指導してくださった皆さん、ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.earnest.polite[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7178,29 +7178,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にお稽古していると、自分も頑張ろうと思えます</t>
+          <t xml:space="preserve">ドーム大会という大役、謹んでお受けいたします</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.earnest.polite[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.polite[2]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7210,29 +7210,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite[2]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">申し訳ありません…少し休ませていただければ、必ず戻ります</t>
+          <t xml:space="preserve">最後の最後まで、手を抜きません</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.earnest.polite[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.polite[3]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7242,29 +7242,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite[3]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様の応援が、何よりの原動力です</t>
+          <t xml:space="preserve">この恩に、必ず応えてみせます</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.earnest.polite[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7274,29 +7274,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">裏切るつもりはございません。ただ……</t>
+          <t xml:space="preserve">満員のお客様、心より感謝申し上げます</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.earnest.polite[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.polite[2]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7306,29 +7306,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite[2]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習を重ねても、何か足りない気がいたしまして…</t>
+          <t xml:space="preserve">全力を尽くした甲斐がありました</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.earnest.polite[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.polite[3]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7338,29 +7338,29 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite[3]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…何か気に障ることをしたのでしょうか</t>
+          <t xml:space="preserve">次も、必ず期待に応えます</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.earnest.polite[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.earnest.polite[1]</t>
+          <t xml:space="preserve">N1.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7385,14 +7385,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name2}さんとご一緒できて幸せでした。…お元気で</t>
+          <t xml:space="preserve">積み重ねが大切だと信じています。コツコツ参ります</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.earnest.polite[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7402,29 +7402,29 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.earnest.polite[1]</t>
+          <t xml:space="preserve">N2.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。必ず結果でお返しいたします</t>
+          <t xml:space="preserve">一緒にお稽古していると、自分も頑張ろうと思えます</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.earnest.polite[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7434,29 +7434,29 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.earnest.polite[1]</t>
+          <t xml:space="preserve">N3.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で取り組ませていただきます。レベルアップしてみせます</t>
+          <t xml:space="preserve">申し訳ありません…少し休ませていただければ、必ず戻ります</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.earnest.polite[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7466,29 +7466,29 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.earnest.polite[1]</t>
+          <t xml:space="preserve">N4.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと見守ってくださったんですね…必ずお報いいたします</t>
+          <t xml:space="preserve">皆様の応援が、何よりの原動力です</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.earnest.polite[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7498,29 +7498,29 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.earnest.polite[1]</t>
+          <t xml:space="preserve">N5_low.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お言葉、ありがとうございます。もう一度頑張ります</t>
+          <t xml:space="preserve">裏切るつもりはございません。ただ……</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.earnest.polite[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7530,29 +7530,29 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.earnest.polite[1]</t>
+          <t xml:space="preserve">N5_warning.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">緊張いたしますが…精一杯務めます</t>
+          <t xml:space="preserve">練習を重ねても、何か足りない気がいたしまして…</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.earnest.polite[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7562,29 +7562,29 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.earnest.polite[1]</t>
+          <t xml:space="preserve">R2.voice.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様、お疲れ様でした。明日からまた頑張りましょう</t>
+          <t xml:space="preserve">…何か気に障ることをしたのでしょうか</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.earnest.polite[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7594,29 +7594,29 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.earnest.polite[1]</t>
+          <t xml:space="preserve">R3.modal.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習が気になりますが…お気遣いありがとうございます</t>
+          <t xml:space="preserve">{name2}さんとご一緒できて幸せでした。…お元気で</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.earnest.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.earnest.polite[1]</t>
+          <t xml:space="preserve">bonus.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7641,14 +7641,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご厚意に甘えます。必ず復帰してお返しいたします</t>
+          <t xml:space="preserve">ありがとうございます。必ず結果でお返しいたします</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.earnest.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.earnest.polite[1]</t>
+          <t xml:space="preserve">camp.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7673,14 +7673,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな機会をいただけて…全力でお応えいたします</t>
+          <t xml:space="preserve">全力で取り組ませていただきます。レベルアップしてみせます</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.earnest.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7690,12 +7690,12 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.earnest.polite[1]</t>
+          <t xml:space="preserve">encourage_high_trust.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7705,14 +7705,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">緊張いたしますが…精一杯務めさせていただきます</t>
+          <t xml:space="preserve">ずっと見守ってくださったんですね…必ずお報いいたします</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.earnest.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.earnest.polite[1]</t>
+          <t xml:space="preserve">encourage.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7737,14 +7737,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こちらに義理がございますので…ただ、ご報告だけは</t>
+          <t xml:space="preserve">お言葉、ありがとうございます。もう一度頑張ります</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.earnest.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.earnest.polite[1]</t>
+          <t xml:space="preserve">faction_decree.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7769,14 +7769,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大変申し訳ございません…今日はどうしても…</t>
+          <t xml:space="preserve">わたしの至らなさです。申し訳ありませんでした</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.earnest.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.earnest.polite[1]</t>
+          <t xml:space="preserve">media.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7801,14 +7801,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと準備して参りました。チャンスをいただけませんか</t>
+          <t xml:space="preserve">緊張いたしますが…精一杯務めます</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.earnest.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7818,12 +7818,12 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.earnest.polite[1]</t>
+          <t xml:space="preserve">party.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7833,14 +7833,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方との試合を組んでいただけないでしょうか</t>
+          <t xml:space="preserve">皆様、お疲れ様でした。明日からまた頑張りましょう</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.earnest.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.earnest.polite[1]</t>
+          <t xml:space="preserve">refresh_leave.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7865,14 +7865,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご迷惑をおかけしまして申し訳ございません…少しお休みをいただけますか</t>
+          <t xml:space="preserve">練習が気になりますが…お気遣いありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.earnest.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.earnest.polite[1]</t>
+          <t xml:space="preserve">special_treatment.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7897,14 +7897,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと我慢して参りましたが…このままでは限界です</t>
+          <t xml:space="preserve">…ご厚意に甘えます。必ず復帰してお返しいたします</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.earnest.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.earnest.polite[1]</t>
+          <t xml:space="preserve">trainer.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7929,14 +7929,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと強くなりたいのです。特訓をお許しいただけますか</t>
+          <t xml:space="preserve">こんな機会をいただけて…全力でお応えいたします</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.earnest.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.earnest.polite[1]</t>
+          <t xml:space="preserve">E1.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7961,14 +7961,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">培ってきたものを後輩にお伝えしたいのです</t>
+          <t xml:space="preserve">緊張いたしますが…精一杯務めさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.earnest.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.earnest.polite[1]</t>
+          <t xml:space="preserve">E6.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7993,14 +7993,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">申し訳ございません…一日も早く復帰いたします</t>
+          <t xml:space="preserve">こちらに義理がございますので…ただ、ご報告だけは</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.earnest.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -8010,12 +8010,12 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.earnest.polite[1]</t>
+          <t xml:space="preserve">S_boycott.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -8025,14 +8025,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方とは…このままではチームに影響が出ます</t>
+          <t xml:space="preserve">大変申し訳ございません…今日はどうしても…</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.earnest.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.earnest.polite[1]</t>
+          <t xml:space="preserve">S_grumble.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -8057,14 +8057,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体にご迷惑はかけたくないのですが…あの方とは…</t>
+          <t xml:space="preserve">（「わたし、このままでいいんでしょうか…」と後輩に弱音をこぼしている）</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.earnest.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.earnest.polite[1]</t>
+          <t xml:space="preserve">S_sns.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -8089,14 +8089,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ブランド様のご期待に添えるよう、精一杯取り組みます</t>
+          <t xml:space="preserve">（SNSに「わたしは本当にここで必要とされているんでしょうか」と率直な投稿）</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.earnest.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.earnest.polite[1]</t>
+          <t xml:space="preserve">S1.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -8121,14 +8121,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大切なお仕事ですね。精一杯務めさせていただきます</t>
+          <t xml:space="preserve">ずっと準備して参りました。チャンスをいただけませんか</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.earnest.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -8138,12 +8138,12 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.earnest.polite[1]</t>
+          <t xml:space="preserve">S2.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -8153,14 +8153,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">来てくださった方全員に、心から感謝を伝えたいです</t>
+          <t xml:space="preserve">あの方との試合を組んでいただけないでしょうか</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.earnest.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.earnest.polite[1]</t>
+          <t xml:space="preserve">S3.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8185,14 +8185,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に沿えるよう、歩き方から練習いたします</t>
+          <t xml:space="preserve">ご迷惑をおかけしまして申し訳ございません…少しお休みをいただけますか</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.earnest.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8202,12 +8202,12 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.earnest.polite[1]</t>
+          <t xml:space="preserve">S4_direct.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8217,14 +8217,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">精一杯きれいに撮っていただけるよう頑張ります…</t>
+          <t xml:space="preserve">ずっと我慢して参りましたが…このままでは限界です</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.earnest.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.earnest.polite[1]</t>
+          <t xml:space="preserve">S4_silent.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8249,14 +8249,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">トーク番組は緊張しますが…誠実に対応いたします</t>
+          <t xml:space="preserve">…………（何か申し上げかけて、深く頭を下げるだけだった）</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.earnest.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.earnest.polite[1]</t>
+          <t xml:space="preserve">S5.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8281,14 +8281,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私でよろしいんですか…？ 精一杯務めさせていただきます</t>
+          <t xml:space="preserve">もっと強くなりたいのです。特訓をお許しいただけますか</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8298,29 +8298,29 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">S6.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">地道に努力するのが取り柄です。信じていただけますか</t>
+          <t xml:space="preserve">培ってきたものを後輩にお伝えしたいのです</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8330,29 +8330,29 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">B1.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただき、ありがとうございます。精一杯頑張ります</t>
+          <t xml:space="preserve">申し訳ございません…一日も早く復帰いたします</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.earnest.polite[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8362,29 +8362,29 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[2]</t>
+          <t xml:space="preserve">B2_fighter1.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に応えられるよう、努力いたします</t>
+          <t xml:space="preserve">あの方とは…このままではチームに影響が出ます</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8394,29 +8394,29 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">B2_fighter2.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。期待にお応えいたします</t>
+          <t xml:space="preserve">団体にご迷惑はかけたくないのですが…あの方とは…</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8426,29 +8426,29 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">B4_brand.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日精進いたします。見ていてください</t>
+          <t xml:space="preserve">ブランド様のご期待に添えるよう、精一杯取り組みます</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8458,29 +8458,29 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">B4_cm.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に応えられず、申し訳ありません</t>
+          <t xml:space="preserve">大切なお仕事ですね。精一杯務めさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.earnest.polite[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8490,29 +8490,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[2]</t>
+          <t xml:space="preserve">B4_fan.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">必ず強くなって戻ってまいります</t>
+          <t xml:space="preserve">来てくださった方全員に、心から感謝を伝えたいです</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.earnest.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8522,29 +8522,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.earnest.polite[1]</t>
+          <t xml:space="preserve">B4_fashion.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">地道に努力するのが取り柄です。信じていただけますか</t>
+          <t xml:space="preserve">ご期待に沿えるよう、歩き方から練習いたします</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.earnest.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8554,29 +8554,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.earnest.polite[1]</t>
+          <t xml:space="preserve">B4_gravure.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただき、ありがとうございます。精一杯頑張ります</t>
+          <t xml:space="preserve">精一杯きれいに撮っていただけるよう頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.earnest.polite[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8586,29 +8586,29 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.earnest.polite[2]</t>
+          <t xml:space="preserve">B4_variety.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に応えられるよう、努力いたします</t>
+          <t xml:space="preserve">トーク番組は緊張しますが…誠実に対応いたします</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.earnest.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8618,29 +8618,29 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.earnest.polite[1]</t>
+          <t xml:space="preserve">B4.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。期待にお応えいたします</t>
+          <t xml:space="preserve">私でよろしいんですか…？ 精一杯務めさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8650,12 +8650,12 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8665,14 +8665,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日精進いたします。見ていてください</t>
+          <t xml:space="preserve">地道に努力するのが取り柄です。信じていただけますか</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8697,14 +8697,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に応えられず、申し訳ありません</t>
+          <t xml:space="preserve">お選びいただき、ありがとうございます。精一杯頑張ります</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.earnest.polite[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.earnest.polite[2]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.earnest.polite[2]</t>
+          <t xml:space="preserve">earnest.polite[2]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8729,14 +8729,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">必ず強くなって戻ってまいります</t>
+          <t xml:space="preserve">ご期待に応えられるよう、努力いたします</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8761,14 +8761,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくださった皆様に、申し訳ありません</t>
+          <t xml:space="preserve">ありがとうございます。期待にお応えいたします</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.earnest.polite[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.earnest.polite[2]</t>
+          <t xml:space="preserve">earnest.polite[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8793,14 +8793,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここでの学び、決して忘れません</t>
+          <t xml:space="preserve">毎日精進いたします。見ていてください</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8825,14 +8825,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですが、精一杯務めさせていただきます</t>
+          <t xml:space="preserve">ご期待に応えられず、申し訳ありません</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.earnest.polite[2]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite[2]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8857,14 +8857,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力が足りませんでした。もっと精進いたします</t>
+          <t xml:space="preserve">必ず強くなって戻ってまいります</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.earnest.polite[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8889,14 +8889,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛できました。でも、まだまだ精進いたします</t>
+          <t xml:space="preserve">済んだことにしたいのです。……できないだけで</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.earnest.polite[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8921,14 +8921,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">努力が足りませんでした。一から出直します</t>
+          <t xml:space="preserve">決着は……ついておりません。私の中では、まだ</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.earnest.polite[1]</t>
+          <t xml:space="preserve">draftInterest.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8953,14 +8953,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねが報われました…本当に、ありがとうございます</t>
+          <t xml:space="preserve">地道に努力するのが取り柄です。信じていただけますか</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">draftJoin.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8985,14 +8985,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくださった皆様に、申し訳ありません</t>
+          <t xml:space="preserve">お選びいただき、ありがとうございます。精一杯頑張ります</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.earnest.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.earnest.polite[2]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[2]</t>
+          <t xml:space="preserve">draftJoin.earnest.polite[2]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -9017,14 +9017,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここでの学び、決して忘れません</t>
+          <t xml:space="preserve">ご期待に応えられるよう、努力いたします</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -9034,12 +9034,12 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">faGreeting.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -9049,14 +9049,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですが、精一杯務めさせていただきます</t>
+          <t xml:space="preserve">いただいた契約の重み、忘れずにやります</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">faSigning.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -9081,14 +9081,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力が足りませんでした。もっと精進いたします</t>
+          <t xml:space="preserve">ありがとうございます。期待にお応えいたします</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -9098,12 +9098,12 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">faWelcome.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -9113,14 +9113,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛できました。でも、まだまだ精進いたします</t>
+          <t xml:space="preserve">毎日精進いたします。見ていてください</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -9130,12 +9130,12 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -9145,14 +9145,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">努力が足りませんでした。一から出直します</t>
+          <t xml:space="preserve">今日は身体が素直に動きます。学んだ分だけ、身につきます</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9177,14 +9177,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねが報われました…本当に、ありがとうございます</t>
+          <t xml:space="preserve">同じ量をこなしても、何も積み上がりません。情けないです</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9194,29 +9194,29 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.earnest.polite[1]</t>
+          <t xml:space="preserve">heatSelf.warm.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">関係を修復したいです…何とかしなければ</t>
+          <t xml:space="preserve">回数はこなせています。ただ、残る実感が薄くて</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9226,29 +9226,29 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.earnest.polite[1]</t>
+          <t xml:space="preserve">injury.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おかげで練習にも身が入ります。感謝しています</t>
+          <t xml:space="preserve">ご期待に応えられず、申し訳ありません</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.earnest.polite[2]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9258,29 +9258,29 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.earnest.polite[1]</t>
+          <t xml:space="preserve">injury.earnest.polite[2]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">共に歩めること、何よりの幸せです</t>
+          <t xml:space="preserve">必ず強くなって戻ってまいります</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9290,29 +9290,29 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.earnest.polite[1]</t>
+          <t xml:space="preserve">release.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝つために、もっと努力しなければなりません</t>
+          <t xml:space="preserve">応援してくださった皆様に、申し訳ありません</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.earnest.polite[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9322,29 +9322,29 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.earnest.polite[1]</t>
+          <t xml:space="preserve">release.earnest.polite[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">超えることが、私の覚悟です</t>
+          <t xml:space="preserve">ここでの学び、決して忘れません</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9354,29 +9354,29 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.earnest.polite[1]</t>
+          <t xml:space="preserve">rentalGreeting.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この切磋琢磨こそが、私の原動力です</t>
+          <t xml:space="preserve">短い間ですが、精一杯務めさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9386,29 +9386,29 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.earnest.polite[1]</t>
+          <t xml:space="preserve">scoutGreeting.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に添えるよう、精一杯頑張らせていただきます</t>
+          <t xml:space="preserve">お声がけに恥じないよう、努めます</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9418,29 +9418,29 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.earnest.polite[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大変申し訳ありませんが…退団を検討させていただきます</t>
+          <t xml:space="preserve">実力が足りませんでした。もっと精進いたします</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9450,29 +9450,29 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.earnest.polite[1]</t>
+          <t xml:space="preserve">titleDefense.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">恐縮ですが…少し運営に対して不安があります…</t>
+          <t xml:space="preserve">防衛できました。でも、まだまだ精進いたします</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9482,29 +9482,29 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.earnest.polite[1]</t>
+          <t xml:space="preserve">titleLoss.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不甲斐ない試合をしてしまいました。申し訳ございません</t>
+          <t xml:space="preserve">努力が足りませんでした。一から出直します</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9514,29 +9514,29 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.earnest.polite[1]</t>
+          <t xml:space="preserve">titleWin.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝利できました。引き続き精進します</t>
+          <t xml:space="preserve">積み重ねが報われました…本当に、ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9546,29 +9546,29 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">基本を怠らず、しっかり取り組みます</t>
+          <t xml:space="preserve">応援してくださった皆様に、申し訳ありません</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.earnest.polite[2]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9578,29 +9578,29 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite[2]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ともに成長できることが嬉しいです</t>
+          <t xml:space="preserve">ここでの学び、決して忘れません</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9610,29 +9610,29 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">追いつくため、日々研鑽します</t>
+          <t xml:space="preserve">短い間ですが、精一杯務めさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9642,29 +9642,29 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">出場機会をいただけるよう、より一層努力いたします</t>
+          <t xml:space="preserve">実力が足りませんでした。もっと精進いたします</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9674,29 +9674,29 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体調管理を怠りました。しっかり立て直します</t>
+          <t xml:space="preserve">防衛できました。でも、まだまだ精進いたします</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9706,29 +9706,29 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不甲斐ない結果が続いています…何とか打開しなければ</t>
+          <t xml:space="preserve">努力が足りませんでした。一から出直します</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9738,29 +9738,29 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">結果がついてきていますが、慢心せず精進します</t>
+          <t xml:space="preserve">積み重ねが報われました…本当に、ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.earnest.polite[1]</t>
+          <t xml:space="preserve">bond_39_down.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9785,14 +9785,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">復帰に向けて、今できることを精一杯やります</t>
+          <t xml:space="preserve">この関係…修復できる自信がありません…</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.polite[2]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">bond_39_down.earnest.polite[2]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9817,14 +9817,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">好調期間は終わりましたが、学びの多い日々でした</t>
+          <t xml:space="preserve">どこで間違えてしまったんでしょう…</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9834,29 +9834,29 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.earnest.polite[1]</t>
+          <t xml:space="preserve">bond_59_down.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体はぼろぼろですが…最後まで、全力でお応えします</t>
+          <t xml:space="preserve">関係を修復したいです…何とかしなければ</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.earnest.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9866,29 +9866,29 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.earnest.polite[2]</t>
+          <t xml:space="preserve">bond_60_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで繋いでくれた仲間のために、私が締めます。どんなに痛くても</t>
+          <t xml:space="preserve">おかげで練習にも身が入ります。感謝しています</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.earnest.polite[3]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9898,29 +9898,29 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.earnest.polite[3]</t>
+          <t xml:space="preserve">bond_80_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">痛みは、勝ってから数えます。今は、目の前の一戦に全部を</t>
+          <t xml:space="preserve">共に歩めること、何よりの幸せです</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9930,29 +9930,29 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.earnest.polite[1]</t>
+          <t xml:space="preserve">rivalry_29_down.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手がどなたでも、全力でお応えします。手を抜くのは失礼ですから</t>
+          <t xml:space="preserve">関係も変わりました。前に進みましょう</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.earnest.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.polite[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9962,29 +9962,29 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.earnest.polite[2]</t>
+          <t xml:space="preserve">rivalry_29_down.earnest.polite[2]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦ずつ、丁寧に。託された役目、途中で放り出せません</t>
+          <t xml:space="preserve">あの因縁から学んだことは多いです。次の目標を見つけなければ</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.earnest.polite[3]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9994,29 +9994,29 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.earnest.polite[3]</t>
+          <t xml:space="preserve">rivalry_30_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まずは目の前の一人に、心を込めて。それが私の役目ですから</t>
+          <t xml:space="preserve">勝つために、もっと努力しなければなりません</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -10026,29 +10026,29 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.earnest.polite[1]</t>
+          <t xml:space="preserve">rivalry_50_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、止めました。…息は上がってますが、退きません。次の方も、全力でお相手します</t>
+          <t xml:space="preserve">超えることが、私の覚悟です</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.earnest.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -10058,29 +10058,29 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.earnest.polite[2]</t>
+          <t xml:space="preserve">rivalry_70_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってます。仲間に繋ぐまで、このリングは渡しません。次、どうぞ</t>
+          <t xml:space="preserve">この切磋琢磨こそが、私の原動力です</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.earnest.polite[3]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -10090,29 +10090,29 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.earnest.polite[3]</t>
+          <t xml:space="preserve">trust_above_75.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、お相手しました。…はぁ、まだ立てます。繋ぐまでは、退けませんから</t>
+          <t xml:space="preserve">ご期待に添えるよう、精一杯頑張らせていただきます</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -10122,29 +10122,29 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.polite[1]</t>
+          <t xml:space="preserve">trust_below_20.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">託された順番を、最後まで全うできました。仲間に感謝しています</t>
+          <t xml:space="preserve">大変申し訳ありませんが…退団を検討させていただきます</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.earnest.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -10154,29 +10154,29 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.polite[2]</t>
+          <t xml:space="preserve">trust_below_35.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人でつないだ勝利を、団体に持ち帰れます。それが何より嬉しいです</t>
+          <t xml:space="preserve">恐縮ですが…少し運営に対して不安があります…</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10186,29 +10186,29 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.earnest.polite[1]</t>
+          <t xml:space="preserve">GL-01.loss.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">評価していただいてありがとうございます。でも、次は団体ごと勝って応えたいです</t>
+          <t xml:space="preserve">不甲斐ない試合をしてしまいました。申し訳ございません</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.earnest.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10218,29 +10218,29 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.earnest.polite[2]</t>
+          <t xml:space="preserve">GL-01.win.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間のためにもっとやれたはず。その反省を、次に生かします</t>
+          <t xml:space="preserve">勝利できました。引き続き精進します</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10250,29 +10250,29 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.earnest.polite[1]</t>
+          <t xml:space="preserve">GL-02.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で来てくださった皆さんに、全力で応えました。それだけは胸を張れます</t>
+          <t xml:space="preserve">基本を怠らず、しっかり取り組みます</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.earnest.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10282,29 +10282,29 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.earnest.polite[2]</t>
+          <t xml:space="preserve">GL-04.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何度も限界を感じました。でも、託された役割を途中で降りるわけにはいきません</t>
+          <t xml:space="preserve">ともに成長できることが嬉しいです</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10314,29 +10314,29 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.polite[1]</t>
+          <t xml:space="preserve">GL-05.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝…させていただきました。皆様のおかげです…！</t>
+          <t xml:space="preserve">追いつくため、日々研鑽します</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.earnest.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10346,29 +10346,29 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.polite[2]</t>
+          <t xml:space="preserve">GL-06.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この経験を糧に、さらに精進して参ります</t>
+          <t xml:space="preserve">出場機会をいただけるよう、より一層努力いたします</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10378,29 +10378,29 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.earnest.polite[1]</t>
+          <t xml:space="preserve">GL-07.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">力不足で申し訳ございません…。もっと精進します</t>
+          <t xml:space="preserve">体調管理を怠りました。しっかり立て直します</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.earnest.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10410,29 +10410,29 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.earnest.polite[2]</t>
+          <t xml:space="preserve">GL-08.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しゅうございます…。必ず強くなります</t>
+          <t xml:space="preserve">不甲斐ない結果が続いています…何とか打開しなければ</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10442,29 +10442,29 @@
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.earnest.polite[1]</t>
+          <t xml:space="preserve">GL-09.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝たせていただきました…。次も全力で臨みます</t>
+          <t xml:space="preserve">結果がついてきていますが、慢心せず精進します</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.earnest.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10474,29 +10474,29 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.earnest.polite[2]</t>
+          <t xml:space="preserve">GL-10.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦一戦、大切に。次もよろしくお願いいたします</t>
+          <t xml:space="preserve">復帰に向けて、今できることを精一杯やります</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10506,29 +10506,29 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.polite[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">良い経験をさせていただきました。精進して参ります</t>
+          <t xml:space="preserve">好調期間は終わりましたが、学びの多い日々でした</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.earnest.polite[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10538,12 +10538,12 @@
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.earnest.polite[2]</t>
+          <t xml:space="preserve">preFinal.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10553,14 +10553,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様のおかげで戦い抜けました。感謝いたします</t>
+          <t xml:space="preserve">身体はぼろぼろですが…最後まで、全力でお応えします</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.earnest.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.earnest.polite[2]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10570,12 +10570,12 @@
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.earnest.polite[1]</t>
+          <t xml:space="preserve">preFinal.earnest.polite[2]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10585,14 +10585,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝の舞台…身に余る光栄です。全力でお応えいたします</t>
+          <t xml:space="preserve">ここまで繋いでくれた仲間のために、私が締めます。どんなに痛くても</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.earnest.polite[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.earnest.polite[3]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10602,12 +10602,12 @@
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.earnest.polite[2]</t>
+          <t xml:space="preserve">preFinal.earnest.polite[3]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10617,14 +10617,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この一戦に、全てをお捧げいたします</t>
+          <t xml:space="preserve">痛みは、勝ってから数えます。今は、目の前の一戦に全部を</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.earnest.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10634,7 +10634,7 @@
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="12">
@@ -10649,14 +10649,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">精一杯の試合を、お見せいたします</t>
+          <t xml:space="preserve">相手がどなたでも、全力でお応えします。手を抜くのは失礼ですから</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.earnest.polite[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.earnest.polite[2]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="C318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D318" t="inlineStr" s="12">
@@ -10681,14 +10681,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ひとつひとつ丁寧に…全力で参ります</t>
+          <t xml:space="preserve">一戦ずつ、丁寧に。託された役目、途中で放り出せません</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.earnest.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.earnest.polite[3]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="C319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.earnest.polite[1]</t>
+          <t xml:space="preserve">preMatch.earnest.polite[3]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10713,14 +10713,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身に余る光栄です。一生懸命頑張ります</t>
+          <t xml:space="preserve">まずは目の前の一人に、心を込めて。それが私の役目ですから</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.earnest.polite[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10730,12 +10730,12 @@
       </c>
       <c r="C320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.earnest.polite[2]</t>
+          <t xml:space="preserve">survivor.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10745,14 +10745,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お声がけいただき感謝いたします。精一杯務めます</t>
+          <t xml:space="preserve">一人、止めました。…息は上がってますが、退きません。次の方も、全力でお相手します</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.earnest.polite[2]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10762,12 +10762,12 @@
       </c>
       <c r="C321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">survivor.earnest.polite[2]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10777,14 +10777,14 @@
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お互い全力で…よろしくお願いいたします</t>
+          <t xml:space="preserve">まだ立ってます。仲間に繋ぐまで、このリングは渡しません。次、どうぞ</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.earnest.polite[3]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="C322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">survivor.earnest.polite[3]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10809,14 +10809,14 @@
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆さまのご声援のおかげです……本当に、ありがとうございます……！</t>
+          <t xml:space="preserve">一人、お相手しました。…はぁ、まだ立てます。繋ぐまでは、退けませんから</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.earnest.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="C323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">champion.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10841,14 +10841,14 @@
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">失礼ながら、対抗戦のお申し込みをさせていただきます</t>
+          <t xml:space="preserve">託された順番を、最後まで全うできました。仲間に感謝しています</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.earnest.polite[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.earnest.polite[2]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10858,12 +10858,12 @@
       </c>
       <c r="C324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[2]</t>
+          <t xml:space="preserve">champion.earnest.polite[2]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10873,14 +10873,14 @@
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力でお相手いたしますので、覚悟なさってください</t>
+          <t xml:space="preserve">三人でつないだ勝利を、団体に持ち帰れます。それが何より嬉しいです</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.earnest.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10890,12 +10890,12 @@
       </c>
       <c r="C325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">defiant.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10905,14 +10905,14 @@
       </c>
       <c r="F325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残念ですが…いつかお受けいただけることを願っております</t>
+          <t xml:space="preserve">評価していただいてありがとうございます。でも、次は団体ごと勝って応えたいです</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.earnest.polite[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.earnest.polite[2]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="C326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[2]</t>
+          <t xml:space="preserve">defiant.earnest.polite[2]</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10937,14 +10937,14 @@
       </c>
       <c r="F326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">改めてお声がけいたします。その時はぜひ</t>
+          <t xml:space="preserve">仲間のためにもっとやれたはず。その反省を、次に生かします</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.earnest.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10954,12 +10954,12 @@
       </c>
       <c r="C327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.earnest.polite[1]</t>
+          <t xml:space="preserve">gauntlet.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10969,14 +10969,14 @@
       </c>
       <c r="F327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">完敗でした…。この悔しさを胸に、精進いたします</t>
+          <t xml:space="preserve">全力で来てくださった皆さんに、全力で応えました。それだけは胸を張れます</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.earnest.polite[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.earnest.polite[2]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="C328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.earnest.polite[2]</t>
+          <t xml:space="preserve">gauntlet.earnest.polite[2]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -11001,14 +11001,14 @@
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">申し訳ございません…。必ず成長してお返しいたします</t>
+          <t xml:space="preserve">何度も限界を感じました。でも、託された役割を途中で降りるわけにはいきません</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.earnest.polite[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -11018,12 +11018,12 @@
       </c>
       <c r="C329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.earnest.polite[1]</t>
+          <t xml:space="preserve">champion.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -11033,14 +11033,14 @@
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝たせていただきました。素晴らしい対抗戦に感謝いたします</t>
+          <t xml:space="preserve">優勝…させていただきました。皆様のおかげです…！</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.earnest.polite[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.earnest.polite[2]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -11050,12 +11050,12 @@
       </c>
       <c r="C330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.earnest.polite[2]</t>
+          <t xml:space="preserve">champion.earnest.polite[2]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -11065,14 +11065,14 @@
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様のおかげで勝利できました。ありがとうございます</t>
+          <t xml:space="preserve">この経験を糧に、さらに精進して参ります</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -11082,12 +11082,12 @@
       </c>
       <c r="C331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">postLose.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
@@ -11097,14 +11097,14 @@
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の代表として勝利できましたこと…光栄でございます</t>
+          <t xml:space="preserve">力不足で申し訳ございません…。もっと精進します</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.earnest.polite[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.earnest.polite[2]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -11114,12 +11114,12 @@
       </c>
       <c r="C332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[2]</t>
+          <t xml:space="preserve">postLose.earnest.polite[2]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -11129,14 +11129,14 @@
       </c>
       <c r="F332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の名に恥じない試合ができたのであれば…嬉しゅうございます</t>
+          <t xml:space="preserve">悔しゅうございます…。必ず強くなります</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.earnest.polite[3]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -11146,12 +11146,12 @@
       </c>
       <c r="C333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[3]</t>
+          <t xml:space="preserve">postMatchWin.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
@@ -11161,44 +11161,812 @@
       </c>
       <c r="F333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の皆様のおかげで勝利できました。心より感謝申し上げます</t>
+          <t xml:space="preserve">勝たせていただきました…。次も全力で臨みます</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.earnest.polite[2]</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.earnest.polite[2]</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一戦一戦、大切に。次もよろしくお願いいたします</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="40" customHeight="1">
+      <c r="A335" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">良い経験をさせていただきました。精進して参ります</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="40" customHeight="1">
+      <c r="A336" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.earnest.polite[2]</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.earnest.polite[2]</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">皆様のおかげで戦い抜けました。感謝いたします</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="40" customHeight="1">
+      <c r="A337" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">決勝の舞台…身に余る光栄です。全力でお応えいたします</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="40" customHeight="1">
+      <c r="A338" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.earnest.polite[2]</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.earnest.polite[2]</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この一戦に、全てをお捧げいたします</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="40" customHeight="1">
+      <c r="A339" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">精一杯の試合を、お見せいたします</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="40" customHeight="1">
+      <c r="A340" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.earnest.polite[2]</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.earnest.polite[2]</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ひとつひとつ丁寧に…全力で参ります</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="40" customHeight="1">
+      <c r="A341" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">身に余る光栄です。一生懸命頑張ります</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="40" customHeight="1">
+      <c r="A342" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.earnest.polite[2]</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.earnest.polite[2]</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お声がけいただき感謝いたします。精一杯務めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="40" customHeight="1">
+      <c r="A343" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お互い全力で…よろしくお願いいたします</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="40" customHeight="1">
+      <c r="A344" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">皆さまのご声援のおかげです……本当に、ありがとうございます……！</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="40" customHeight="1">
+      <c r="A345" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">失礼ながら、対抗戦のお申し込みをさせていただきます</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="40" customHeight="1">
+      <c r="A346" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.earnest.polite[2]</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.polite[2]</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">全力でお相手いたしますので、覚悟なさってください</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="40" customHeight="1">
+      <c r="A347" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">残念ですが…いつかお受けいただけることを願っております</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="40" customHeight="1">
+      <c r="A348" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.earnest.polite[2]</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.polite[2]</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">改めてお声がけいたします。その時はぜひ</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="40" customHeight="1">
+      <c r="A349" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">完敗でした…。この悔しさを胸に、精進いたします</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="40" customHeight="1">
+      <c r="A350" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.earnest.polite[2]</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.earnest.polite[2]</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">申し訳ございません…。必ず成長してお返しいたします</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="40" customHeight="1">
+      <c r="A351" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝たせていただきました。素晴らしい対抗戦に感謝いたします</t>
+        </is>
+      </c>
+    </row>
+    <row r="352" ht="40" customHeight="1">
+      <c r="A352" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.earnest.polite[2]</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.earnest.polite[2]</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">皆様のおかげで勝利できました。ありがとうございます</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" ht="40" customHeight="1">
+      <c r="A353" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">団体の代表として勝利できましたこと…光栄でございます</t>
+        </is>
+      </c>
+    </row>
+    <row r="354" ht="40" customHeight="1">
+      <c r="A354" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.earnest.polite[2]</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.polite[2]</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">団体の名に恥じない試合ができたのであれば…嬉しゅうございます</t>
+        </is>
+      </c>
+    </row>
+    <row r="355" ht="40" customHeight="1">
+      <c r="A355" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.earnest.polite[3]</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.polite[3]</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">団体の皆様のおかげで勝利できました。心より感謝申し上げます</t>
+        </is>
+      </c>
+    </row>
+    <row r="356" ht="40" customHeight="1">
+      <c r="A356" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">ENDING_LINES.fighter.earnest.polite[1]</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr" s="2">
+      <c r="B356" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr" s="12">
+      <c r="D356" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighter.earnest.polite[1]</t>
         </is>
       </c>
-      <c r="E334" t="inlineStr" s="2">
+      <c r="E356" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
-      <c r="F334" t="inlineStr" s="3">
+      <c r="F356" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">積み重ねてきた全てが報われました…ありがとうございます</t>
         </is>
       </c>
     </row>
+    <row r="357" ht="40" customHeight="1">
+      <c r="A357" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いただいた契約の重み、忘れずにやります</t>
+        </is>
+      </c>
+    </row>
+    <row r="358" ht="40" customHeight="1">
+      <c r="A358" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.polite[1]</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お声がけに恥じないよう、努めます</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H334"/>
+  <autoFilter ref="A1:H358"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/丁寧×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×真面目.xlsx
@@ -482,7 +482,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H358"/>
+  <dimension ref="A1:H353"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -540,7 +540,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.earnest.polite[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -555,7 +555,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.earnest.polite[1]</t>
+          <t xml:space="preserve">atk.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -572,7 +572,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.earnest.polite[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -587,7 +587,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.earnest.polite[2]</t>
+          <t xml:space="preserve">atk.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -604,7 +604,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.earnest.polite[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.polite.earnest[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -619,7 +619,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.earnest.polite[3]</t>
+          <t xml:space="preserve">atk.polite.earnest[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -636,7 +636,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.earnest.polite[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.polite.earnest[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -651,7 +651,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.earnest.polite[4]</t>
+          <t xml:space="preserve">atk.polite.earnest[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -668,7 +668,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.earnest.polite[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -683,7 +683,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.earnest.polite[1]</t>
+          <t xml:space="preserve">bigmove.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
@@ -700,7 +700,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.earnest.polite[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -715,7 +715,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.earnest.polite[2]</t>
+          <t xml:space="preserve">bigmove.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -732,7 +732,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.earnest.polite[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.polite.earnest[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -747,7 +747,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.earnest.polite[3]</t>
+          <t xml:space="preserve">bigmove.polite.earnest[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -764,7 +764,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.earnest.polite[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -779,7 +779,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.earnest.polite[1]</t>
+          <t xml:space="preserve">climax.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -796,7 +796,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.earnest.polite[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -811,7 +811,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.earnest.polite[2]</t>
+          <t xml:space="preserve">climax.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -828,7 +828,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -843,7 +843,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -860,7 +860,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.earnest.polite[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -875,7 +875,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[2]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -892,7 +892,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.earnest.polite[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.polite.earnest[3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -907,7 +907,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[3]</t>
+          <t xml:space="preserve">polite.earnest[3]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -924,7 +924,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.earnest.polite[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -939,7 +939,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.earnest.polite[1]</t>
+          <t xml:space="preserve">badWinner.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -956,7 +956,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.earnest.polite[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -971,7 +971,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.earnest.polite[1]</t>
+          <t xml:space="preserve">goodWinner.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -988,7 +988,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -1020,7 +1020,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.earnest.polite[2]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[2]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -1052,7 +1052,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.earnest.polite[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest.polite[1]</t>
+          <t xml:space="preserve">loser.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -1084,7 +1084,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.earnest.polite[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.earnest.polite[1]</t>
+          <t xml:space="preserve">winner.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -1116,7 +1116,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.earnest.polite[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.earnest.polite[1]</t>
+          <t xml:space="preserve">competition_won.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -1148,7 +1148,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.earnest.polite[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.earnest.polite[2]</t>
+          <t xml:space="preserve">competition_won.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -1180,7 +1180,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.earnest.polite[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.earnest.polite[1]</t>
+          <t xml:space="preserve">direct.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -1212,7 +1212,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.earnest.polite[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.earnest.polite[2]</t>
+          <t xml:space="preserve">direct.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -1244,7 +1244,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.earnest.polite[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.earnest.polite[1]</t>
+          <t xml:space="preserve">fa_signing.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -1276,7 +1276,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.earnest.polite[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.earnest.polite[2]</t>
+          <t xml:space="preserve">fa_signing.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -1308,7 +1308,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.earnest.polite.hit[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.polite.earnest.hit[1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite.hit[1]</t>
+          <t xml:space="preserve">polite.earnest.hit[1]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -1340,7 +1340,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.earnest.polite.hit[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.polite.earnest.hit[2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite.hit[2]</t>
+          <t xml:space="preserve">polite.earnest.hit[2]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -1372,7 +1372,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.earnest.polite.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.polite.earnest.win[1]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite.win[1]</t>
+          <t xml:space="preserve">polite.earnest.win[1]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -1404,7 +1404,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.earnest.polite.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.polite.earnest.win[2]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite.win[2]</t>
+          <t xml:space="preserve">polite.earnest.win[2]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
@@ -1436,7 +1436,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -1468,7 +1468,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.earnest.polite[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[2]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1500,7 +1500,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.earnest.polite[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.polite.earnest[3]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[3]</t>
+          <t xml:space="preserve">polite.earnest[3]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -1532,7 +1532,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1564,7 +1564,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.earnest.polite[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[2]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
@@ -1596,7 +1596,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.earnest.polite[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.polite.earnest[3]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[3]</t>
+          <t xml:space="preserve">polite.earnest[3]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
@@ -1628,7 +1628,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1660,7 +1660,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.earnest.polite[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[2]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1692,7 +1692,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.earnest.polite[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.polite.earnest[3]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[3]</t>
+          <t xml:space="preserve">polite.earnest[3]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1724,7 +1724,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
@@ -1756,7 +1756,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.earnest.polite[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[2]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1788,7 +1788,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.earnest.polite[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.polite.earnest[3]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[3]</t>
+          <t xml:space="preserve">polite.earnest[3]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1820,7 +1820,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1852,7 +1852,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.earnest.polite[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[2]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1884,7 +1884,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1916,7 +1916,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.earnest.polite[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[2]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1948,7 +1948,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.earnest.polite[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ahead.earnest.polite[1]</t>
+          <t xml:space="preserve">ahead.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1980,7 +1980,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.earnest.polite[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">behind.earnest.polite[1]</t>
+          <t xml:space="preserve">behind.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -2012,7 +2012,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.earnest.polite[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest.polite[1]</t>
+          <t xml:space="preserve">loser.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -2044,7 +2044,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.earnest.polite[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.earnest.polite[1]</t>
+          <t xml:space="preserve">winner.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -2076,7 +2076,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.earnest.polite[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest.polite[1]</t>
+          <t xml:space="preserve">loser.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -2108,7 +2108,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.earnest.polite[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.earnest.polite[1]</t>
+          <t xml:space="preserve">winner.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -2140,7 +2140,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.earnest.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.earnest.polite[1]</t>
+          <t xml:space="preserve">attacker.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -2172,7 +2172,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.earnest.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.earnest.polite[1]</t>
+          <t xml:space="preserve">defender.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2204,7 +2204,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.earnest.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.earnest.polite[1]</t>
+          <t xml:space="preserve">attacker.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2236,7 +2236,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.earnest.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.earnest.polite[1]</t>
+          <t xml:space="preserve">defender.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2268,7 +2268,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.earnest.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.earnest.polite[1]</t>
+          <t xml:space="preserve">attacker.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2300,7 +2300,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.earnest.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.earnest.polite[1]</t>
+          <t xml:space="preserve">defender.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2332,7 +2332,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.earnest.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.earnest.polite[1]</t>
+          <t xml:space="preserve">loserLines.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2364,7 +2364,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.earnest.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.earnest.polite[1]</t>
+          <t xml:space="preserve">winnerLines.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2396,7 +2396,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.earnest.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest.polite[1]</t>
+          <t xml:space="preserve">loser.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -2428,7 +2428,7 @@
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.earnest.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.earnest.polite[1]</t>
+          <t xml:space="preserve">winner.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -2460,7 +2460,7 @@
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.earnest.polite[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.earnest.polite[1]</t>
+          <t xml:space="preserve">loserLines.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
@@ -2492,7 +2492,7 @@
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.earnest.polite[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.earnest.polite[1]</t>
+          <t xml:space="preserve">winnerLines.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
@@ -2524,7 +2524,7 @@
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.earnest.polite[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.earnest.polite[1]</t>
+          <t xml:space="preserve">awakening.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr" s="2">
@@ -3324,7 +3324,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.earnest.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.earnest.polite[1]</t>
+          <t xml:space="preserve">accepted.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3356,7 +3356,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.earnest.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.earnest.polite[1]</t>
+          <t xml:space="preserve">defended.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3388,7 +3388,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.earnest.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.earnest.polite[1]</t>
+          <t xml:space="preserve">defense_failed.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3420,7 +3420,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.earnest.polite[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.earnest.polite[1]</t>
+          <t xml:space="preserve">default.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3452,7 +3452,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.earnest.polite[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.earnest.polite[1]</t>
+          <t xml:space="preserve">former_champ.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3484,7 +3484,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.earnest.polite[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.earnest.polite[1]</t>
+          <t xml:space="preserve">heel.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3516,7 +3516,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.earnest.polite[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.earnest.polite[1]</t>
+          <t xml:space="preserve">high_trust.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3548,7 +3548,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.earnest.polite[1]</t>
+          <t xml:space="preserve">accept_former_champ.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3580,7 +3580,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.earnest.polite[1]</t>
+          <t xml:space="preserve">accept_heel.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3612,7 +3612,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.earnest.polite[1]</t>
+          <t xml:space="preserve">accept_no_title.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3644,7 +3644,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.earnest.polite[1]</t>
+          <t xml:space="preserve">accept_terminal.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3676,7 +3676,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.earnest.polite[1]</t>
+          <t xml:space="preserve">accept_winless.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3708,7 +3708,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.earnest.polite[1]</t>
+          <t xml:space="preserve">refuse_champ.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3740,7 +3740,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.earnest.polite[1]</t>
+          <t xml:space="preserve">refuse_distrust.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3772,7 +3772,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.earnest.polite[1]</t>
+          <t xml:space="preserve">refuse_fighting.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3804,7 +3804,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.earnest.polite[1]</t>
+          <t xml:space="preserve">refuse_heel.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3836,7 +3836,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.earnest.polite[1]</t>
+          <t xml:space="preserve">A1_champion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3868,7 +3868,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.earnest.polite[1]</t>
+          <t xml:space="preserve">A2_uncrowned.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3900,7 +3900,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.earnest.polite[1]</t>
+          <t xml:space="preserve">A3_heel.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3932,7 +3932,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.earnest.polite[1]</t>
+          <t xml:space="preserve">A4_veteran.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3964,7 +3964,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.earnest.polite[1]</t>
+          <t xml:space="preserve">B1_young.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3996,7 +3996,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.earnest.polite[1]</t>
+          <t xml:space="preserve">B2_prime.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -4028,7 +4028,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.earnest.polite[1]</t>
+          <t xml:space="preserve">B3_older.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -4060,7 +4060,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.earnest.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.earnest.polite[1]</t>
+          <t xml:space="preserve">B4_champion_injury.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -4092,7 +4092,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -4124,7 +4124,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.earnest.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.earnest.polite[1]</t>
+          <t xml:space="preserve">raise_accept.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -4156,7 +4156,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.earnest.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.earnest.polite[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4188,7 +4188,7 @@
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.earnest.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.earnest.polite[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4220,7 +4220,7 @@
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.earnest.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.earnest.polite[1]</t>
+          <t xml:space="preserve">raise_open.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4252,7 +4252,7 @@
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.earnest.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.earnest.polite[1]</t>
+          <t xml:space="preserve">raise_refuse.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4284,7 +4284,7 @@
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.earnest.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.earnest.polite[1]</t>
+          <t xml:space="preserve">sudden_departure.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4316,7 +4316,7 @@
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.earnest.polite[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.earnest.polite[2]</t>
+          <t xml:space="preserve">sudden_departure.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4348,7 +4348,7 @@
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.earnest.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.earnest.polite[1]</t>
+          <t xml:space="preserve">transfer_listen.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4380,7 +4380,7 @@
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.earnest.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.earnest.polite[1]</t>
+          <t xml:space="preserve">transfer_open.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4412,7 +4412,7 @@
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.earnest.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.earnest.polite[1]</t>
+          <t xml:space="preserve">transfer_release.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4444,7 +4444,7 @@
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.earnest.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.earnest.polite[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4476,7 +4476,7 @@
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.earnest.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.earnest.polite[1]</t>
+          <t xml:space="preserve">transfer_retain_success.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4508,7 +4508,7 @@
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.earnest.polite[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.earnest.polite[1]</t>
+          <t xml:space="preserve">blocked.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4541,7 +4541,7 @@
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.earnest.polite[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.earnest.polite[1]</t>
+          <t xml:space="preserve">fail.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4574,7 +4574,7 @@
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.earnest.polite[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.earnest.polite[1]</t>
+          <t xml:space="preserve">start.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4607,7 +4607,7 @@
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.earnest.polite[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.earnest.polite[1]</t>
+          <t xml:space="preserve">success.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -5824,22 +5824,22 @@
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F01_LEADER_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.earnest.attack.polite</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F01_LEADER_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.attack.polite</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5849,29 +5849,29 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みなさんのこと、必ず守ります。私、この団体で誰よりも本気ですから。</t>
+          <t xml:space="preserve">けじめを、つけさせてください</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LEADER_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.earnest.defend.polite</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LEADER_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">earnest.defend.polite</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5881,29 +5881,29 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体のため、あえて分かれる道を選びます。中途半端には、しません。</t>
+          <t xml:space="preserve">逃げるつもりはありません</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.earnest.attack.polite</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.attack.polite</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5913,29 +5913,29 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">けじめを、つけさせてください</t>
+          <t xml:space="preserve">申し上げにくいのですが……今のままでは、わたくしたち、息が詰まります。</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.earnest.defend.polite</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.defend.polite</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5945,14 +5945,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げるつもりはありません</t>
+          <t xml:space="preserve">きっかけがあれば、と思っておりました。今日がその日かもしれません。</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5962,12 +5962,12 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5977,14 +5977,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方がいらっしゃらない団体は、わたくしには想像もできません……。</t>
+          <t xml:space="preserve">言葉ではもう届きません。リングで、決着をつけましょう。</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.polite.earnest.hp_high[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5994,12 +5994,12 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest.hp_high[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -6009,14 +6009,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">筋違いは承知の上で申し上げます。わたくし、あちらへ移らせていただきたく存じます。</t>
+          <t xml:space="preserve">……お見事でした。次は、こうはいきません</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.polite.earnest.high[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest.high[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -6041,14 +6041,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">申し上げにくいのですが……今のままでは、わたくしたち、息が詰まります。</t>
+          <t xml:space="preserve">失礼いたしました。今日は、私が勝たせてもらいます</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.polite.earnest.high[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest.high[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -6073,14 +6073,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">きっかけがあれば、と思っておりました。今日がその日かもしれません。</t>
+          <t xml:space="preserve">今日という日のために、私、ここまで来たんです</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.polite.earnest.high[2]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest.high[2]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -6105,14 +6105,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">畏れながら、わたくしたちの処遇について、再考いただきたく存じます。</t>
+          <t xml:space="preserve">御免なさい。今日は手加減できません</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.polite.earnest.high[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest.high[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -6137,14 +6137,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">言葉ではもう届きません。リングで、決着をつけましょう。</t>
+          <t xml:space="preserve">ご丁寧に、ありがとうございます。お受けいたします</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.earnest.polite.hp_high[1]</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.polite.earnest.high[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite.hp_high[1]</t>
+          <t xml:space="preserve">polite.earnest.high[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -6169,14 +6169,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……お見事でした。次は、こうはいきません</t>
+          <t xml:space="preserve">今夜の興行で、すべてを決めさせてください</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.earnest.polite.high[1]</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.polite.earnest.high[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite.high[1]</t>
+          <t xml:space="preserve">polite.earnest.high[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6201,14 +6201,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">失礼いたしました。今日は、私が勝たせてもらいます</t>
+          <t xml:space="preserve">お受けいたします。今夜、決着を</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.earnest.polite.high[1]</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.polite.earnest.high[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6218,12 +6218,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite.high[1]</t>
+          <t xml:space="preserve">polite.earnest.high[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6233,14 +6233,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日という日のために、私、ここまで来たんです</t>
+          <t xml:space="preserve">御免なさい。今日だけは、譲れません</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.earnest.polite.high[2]</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES.polite.earnest.high[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite.high[2]</t>
+          <t xml:space="preserve">polite.earnest.high[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6265,174 +6265,174 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">御免なさい。今日は手加減できません</t>
+          <t xml:space="preserve">光栄です。全力で、お相手します</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.earnest.polite.high[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite.high[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご丁寧に、ありがとうございます。お受けいたします</t>
+          <t xml:space="preserve">練習が実を結びました…！ まだ上を目指します</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.earnest.polite.high[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite.high[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今夜の興行で、すべてを決めさせてください</t>
+          <t xml:space="preserve">（…あのお稽古が、今、実を結ぼうとしている——）</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.earnest.polite.high[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite.high[1]</t>
+          <t xml:space="preserve">fresh.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お受けいたします。今夜、決着を</t>
+          <t xml:space="preserve">今日は身体が素直に動きます。学んだ分だけ、身につきます</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.earnest.polite.high[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite.high[1]</t>
+          <t xml:space="preserve">heavy.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">御免なさい。今日だけは、譲れません</t>
+          <t xml:space="preserve">同じ量をこなしても、何も積み上がりません。情けないです</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES.earnest.polite.high[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite.high[1]</t>
+          <t xml:space="preserve">warm.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">光栄です。全力で、お相手します</t>
+          <t xml:space="preserve">回数はこなせています。ただ、残る実感が薄くて</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">cap_reached.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6457,14 +6457,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習が実を結びました…！ まだ上を目指します</t>
+          <t xml:space="preserve">限界に達しましたが…この道のりに誇りを持っています</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">ovr_elite.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6489,14 +6489,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…あのお稽古が、今、実を結ぼうとしている——）</t>
+          <t xml:space="preserve">ここまで来ました。でもまだ、上を目指します</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.earnest.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.earnest.polite[1]</t>
+          <t xml:space="preserve">ovr_growth.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6521,14 +6521,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は身体が素直に動きます。学んだ分だけ、身につきます</t>
+          <t xml:space="preserve">日々の積み重ねが実を結んできました</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.earnest.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6538,12 +6538,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.earnest.polite[1]</t>
+          <t xml:space="preserve">ovr_legend.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6553,14 +6553,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">同じ量をこなしても、何も積み上がりません。情けないです</t>
+          <t xml:space="preserve">全てを懸けてきた日々が…報われました</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.earnest.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.earnest.polite[1]</t>
+          <t xml:space="preserve">pop_growth.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6585,14 +6585,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">回数はこなせています。ただ、残る実感が薄くて</t>
+          <t xml:space="preserve">応援を力に変えて、もっと頑張ります</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.earnest.polite[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.earnest.polite[1]</t>
+          <t xml:space="preserve">pop_star.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6617,14 +6617,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">限界に達しましたが…この道のりに誇りを持っています</t>
+          <t xml:space="preserve">この声援を力に、必ず期待に応えてみせます</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.earnest.polite[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6649,14 +6649,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来ました。でもまだ、上を目指します</t>
+          <t xml:space="preserve">毎日道場に来るのが…こんなに辛いとは思いませんでした</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.earnest.polite[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6681,14 +6681,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">日々の積み重ねが実を結んできました</t>
+          <t xml:space="preserve">闘う気持ちを忘れていました…でも、もう迷いません</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.earnest.polite[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6713,14 +6713,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全てを懸けてきた日々が…報われました</t>
+          <t xml:space="preserve">ご迷惑をおかけしました…必ず、倍にしてお返しします</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.earnest.polite[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.earnest.polite[1]</t>
+          <t xml:space="preserve">defeat.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6745,14 +6745,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援を力に変えて、もっと頑張ります</t>
+          <t xml:space="preserve">あの試合から…自分の何が足りないのか、ずっと考えています</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.earnest.polite[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.earnest.polite[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6777,14 +6777,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この声援を力に、必ず期待に応えてみせます</t>
+          <t xml:space="preserve">復帰できたのですが…まだ全然、足りていません</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6809,14 +6809,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日道場に来るのが…こんなに辛いとは思いませんでした</t>
+          <t xml:space="preserve">復帰できました…でも体が覚えているんです、あの痛みを</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6826,12 +6826,12 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">penalty_end.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6841,14 +6841,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">闘う気持ちを忘れていました…でも、もう迷いません</t>
+          <t xml:space="preserve">怪我は治りました。でも離れていた時間が…重いです</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6858,29 +6858,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">bestMatch.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご迷惑をおかけしました…必ず、倍にしてお返しします</t>
+          <t xml:space="preserve">あの試合は一生の宝物です。対戦相手の方に、心から感謝しています</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.earnest.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6890,29 +6890,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.earnest.polite[1]</t>
+          <t xml:space="preserve">champion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの試合から…自分の何が足りないのか、ずっと考えています</t>
+          <t xml:space="preserve">王者としての責任を全うします。毎試合、最高の試合をお届けします</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.earnest.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6922,29 +6922,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.earnest.polite[1]</t>
+          <t xml:space="preserve">hallOfFame.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">復帰できたのですが…まだ全然、足りていません</t>
+          <t xml:space="preserve">後輩の皆さん。リングに真実があります。どうか、立ち続けてください</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.earnest.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6954,29 +6954,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.earnest.polite[1]</t>
+          <t xml:space="preserve">mvp.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">復帰できました…でも体が覚えているんです、あの痛みを</t>
+          <t xml:space="preserve">日々の積み重ねが実を結びました。来年も変わらず精進します</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.earnest.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6986,29 +6986,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.earnest.polite[1]</t>
+          <t xml:space="preserve">rookie.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我は治りました。でも離れていた時間が…重いです</t>
+          <t xml:space="preserve">毎日の積み重ねが報われました。指導してくださった皆さん、ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.earnest.polite[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -7018,12 +7018,12 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -7033,14 +7033,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの試合は一生の宝物です。対戦相手の方に、心から感謝しています</t>
+          <t xml:space="preserve">ドーム大会という大役、謹んでお受けいたします</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.earnest.polite[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -7065,14 +7065,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">王者としての責任を全うします。毎試合、最高の試合をお届けします</t>
+          <t xml:space="preserve">最後の最後まで、手を抜きません</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.earnest.polite[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.earnest[3]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[3]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -7097,14 +7097,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の皆さん。リングに真実があります。どうか、立ち続けてください</t>
+          <t xml:space="preserve">この恩に、必ず応えてみせます</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.earnest.polite[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -7114,12 +7114,12 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -7129,14 +7129,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">日々の積み重ねが実を結びました。来年も変わらず精進します</t>
+          <t xml:space="preserve">満員のお客様、心より感謝申し上げます</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.earnest.polite[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -7161,14 +7161,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日の積み重ねが報われました。指導してくださった皆さん、ありがとうございます</t>
+          <t xml:space="preserve">全力を尽くした甲斐がありました</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.earnest[3]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[3]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7193,14 +7193,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドーム大会という大役、謹んでお受けいたします</t>
+          <t xml:space="preserve">次も、必ず期待に応えます</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.polite[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7210,29 +7210,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[2]</t>
+          <t xml:space="preserve">N1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後の最後まで、手を抜きません</t>
+          <t xml:space="preserve">積み重ねが大切だと信じています。コツコツ参ります</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.polite[3]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7242,29 +7242,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[3]</t>
+          <t xml:space="preserve">N2.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この恩に、必ず応えてみせます</t>
+          <t xml:space="preserve">一緒にお稽古していると、自分も頑張ろうと思えます</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7274,29 +7274,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">N3.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員のお客様、心より感謝申し上げます</t>
+          <t xml:space="preserve">申し訳ありません…少し休ませていただければ、必ず戻ります</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.polite[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7306,29 +7306,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[2]</t>
+          <t xml:space="preserve">N4.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力を尽くした甲斐がありました</t>
+          <t xml:space="preserve">皆様の応援が、何よりの原動力です</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.polite[3]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7338,29 +7338,29 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[3]</t>
+          <t xml:space="preserve">N5_low.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次も、必ず期待に応えます</t>
+          <t xml:space="preserve">裏切るつもりはございません。ただ……</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.earnest.polite[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.earnest.polite[1]</t>
+          <t xml:space="preserve">N5_warning.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7385,14 +7385,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねが大切だと信じています。コツコツ参ります</t>
+          <t xml:space="preserve">練習を重ねても、何か足りない気がいたしまして…</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.earnest.polite[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.earnest.polite[1]</t>
+          <t xml:space="preserve">R2.voice.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7417,14 +7417,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にお稽古していると、自分も頑張ろうと思えます</t>
+          <t xml:space="preserve">…何か気に障ることをしたのでしょうか</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.earnest.polite[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7434,12 +7434,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.earnest.polite[1]</t>
+          <t xml:space="preserve">R3.modal.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7449,14 +7449,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">申し訳ありません…少し休ませていただければ、必ず戻ります</t>
+          <t xml:space="preserve">{name2}さんとご一緒できて幸せでした。…お元気で</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.earnest.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7466,29 +7466,29 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.earnest.polite[1]</t>
+          <t xml:space="preserve">bonus.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様の応援が、何よりの原動力です</t>
+          <t xml:space="preserve">ありがとうございます。必ず結果でお返しいたします</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.earnest.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7498,29 +7498,29 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.earnest.polite[1]</t>
+          <t xml:space="preserve">camp.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">裏切るつもりはございません。ただ……</t>
+          <t xml:space="preserve">全力で取り組ませていただきます。レベルアップしてみせます</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.earnest.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7530,29 +7530,29 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.earnest.polite[1]</t>
+          <t xml:space="preserve">encourage_high_trust.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習を重ねても、何か足りない気がいたしまして…</t>
+          <t xml:space="preserve">ずっと見守ってくださったんですね…必ずお報いいたします</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.earnest.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7562,29 +7562,29 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.earnest.polite[1]</t>
+          <t xml:space="preserve">encourage.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…何か気に障ることをしたのでしょうか</t>
+          <t xml:space="preserve">お言葉、ありがとうございます。もう一度頑張ります</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.earnest.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7594,29 +7594,29 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.earnest.polite[1]</t>
+          <t xml:space="preserve">faction_decree.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name2}さんとご一緒できて幸せでした。…お元気で</t>
+          <t xml:space="preserve">わたしの至らなさです。申し訳ありませんでした</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.earnest.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.earnest.polite[1]</t>
+          <t xml:space="preserve">media.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7641,14 +7641,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。必ず結果でお返しいたします</t>
+          <t xml:space="preserve">緊張いたしますが…精一杯務めます</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.earnest.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.earnest.polite[1]</t>
+          <t xml:space="preserve">party.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7673,14 +7673,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で取り組ませていただきます。レベルアップしてみせます</t>
+          <t xml:space="preserve">皆様、お疲れ様でした。明日からまた頑張りましょう</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.earnest.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.earnest.polite[1]</t>
+          <t xml:space="preserve">refresh_leave.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7705,14 +7705,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと見守ってくださったんですね…必ずお報いいたします</t>
+          <t xml:space="preserve">練習が気になりますが…お気遣いありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.earnest.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.earnest.polite[1]</t>
+          <t xml:space="preserve">special_treatment.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7737,14 +7737,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お言葉、ありがとうございます。もう一度頑張ります</t>
+          <t xml:space="preserve">…ご厚意に甘えます。必ず復帰してお返しいたします</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.earnest.polite[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.earnest.polite[1]</t>
+          <t xml:space="preserve">trainer.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7769,14 +7769,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしの至らなさです。申し訳ありませんでした</t>
+          <t xml:space="preserve">こんな機会をいただけて…全力でお応えいたします</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.earnest.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.earnest.polite[1]</t>
+          <t xml:space="preserve">E1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7801,14 +7801,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">緊張いたしますが…精一杯務めます</t>
+          <t xml:space="preserve">緊張いたしますが…精一杯務めさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.earnest.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7818,12 +7818,12 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.earnest.polite[1]</t>
+          <t xml:space="preserve">E6.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7833,14 +7833,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様、お疲れ様でした。明日からまた頑張りましょう</t>
+          <t xml:space="preserve">こちらに義理がございますので…ただ、ご報告だけは</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.earnest.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.earnest.polite[1]</t>
+          <t xml:space="preserve">S_boycott.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7865,14 +7865,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習が気になりますが…お気遣いありがとうございます</t>
+          <t xml:space="preserve">大変申し訳ございません…今日はどうしても…</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.earnest.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.earnest.polite[1]</t>
+          <t xml:space="preserve">S_grumble.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7897,14 +7897,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご厚意に甘えます。必ず復帰してお返しいたします</t>
+          <t xml:space="preserve">（「わたし、このままでいいんでしょうか…」と後輩に弱音をこぼしている）</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.earnest.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.earnest.polite[1]</t>
+          <t xml:space="preserve">S_sns.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7929,14 +7929,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな機会をいただけて…全力でお応えいたします</t>
+          <t xml:space="preserve">（SNSに「わたしは本当にここで必要とされているんでしょうか」と率直な投稿）</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.earnest.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.earnest.polite[1]</t>
+          <t xml:space="preserve">S1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7961,14 +7961,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">緊張いたしますが…精一杯務めさせていただきます</t>
+          <t xml:space="preserve">ずっと準備して参りました。チャンスをいただけませんか</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.earnest.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.earnest.polite[1]</t>
+          <t xml:space="preserve">S2.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7993,14 +7993,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こちらに義理がございますので…ただ、ご報告だけは</t>
+          <t xml:space="preserve">あの方との試合を組んでいただけないでしょうか</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.earnest.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.earnest.polite[1]</t>
+          <t xml:space="preserve">S3.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -8025,14 +8025,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大変申し訳ございません…今日はどうしても…</t>
+          <t xml:space="preserve">ご迷惑をおかけしまして申し訳ございません…少しお休みをいただけますか</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.earnest.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.earnest.polite[1]</t>
+          <t xml:space="preserve">S4_direct.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -8057,14 +8057,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「わたし、このままでいいんでしょうか…」と後輩に弱音をこぼしている）</t>
+          <t xml:space="preserve">ずっと我慢して参りましたが…このままでは限界です</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.earnest.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.earnest.polite[1]</t>
+          <t xml:space="preserve">S4_silent.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -8089,14 +8089,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「わたしは本当にここで必要とされているんでしょうか」と率直な投稿）</t>
+          <t xml:space="preserve">…………（何か申し上げかけて、深く頭を下げるだけだった）</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.earnest.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.earnest.polite[1]</t>
+          <t xml:space="preserve">S5.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -8121,14 +8121,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと準備して参りました。チャンスをいただけませんか</t>
+          <t xml:space="preserve">もっと強くなりたいのです。特訓をお許しいただけますか</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.earnest.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -8143,7 +8143,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.earnest.polite[1]</t>
+          <t xml:space="preserve">S6.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -8153,14 +8153,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方との試合を組んでいただけないでしょうか</t>
+          <t xml:space="preserve">培ってきたものを後輩にお伝えしたいのです</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.earnest.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.earnest.polite[1]</t>
+          <t xml:space="preserve">B1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8185,14 +8185,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご迷惑をおかけしまして申し訳ございません…少しお休みをいただけますか</t>
+          <t xml:space="preserve">申し訳ございません…一日も早く復帰いたします</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.earnest.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8202,12 +8202,12 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.earnest.polite[1]</t>
+          <t xml:space="preserve">B2_fighter1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8217,14 +8217,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと我慢して参りましたが…このままでは限界です</t>
+          <t xml:space="preserve">あの方とは…このままではチームに影響が出ます</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.earnest.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.earnest.polite[1]</t>
+          <t xml:space="preserve">B2_fighter2.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8249,14 +8249,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（何か申し上げかけて、深く頭を下げるだけだった）</t>
+          <t xml:space="preserve">団体にご迷惑はかけたくないのですが…あの方とは…</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.earnest.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.earnest.polite[1]</t>
+          <t xml:space="preserve">B4_brand.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8281,14 +8281,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと強くなりたいのです。特訓をお許しいただけますか</t>
+          <t xml:space="preserve">ブランド様のご期待に添えるよう、精一杯取り組みます</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.earnest.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8298,12 +8298,12 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.earnest.polite[1]</t>
+          <t xml:space="preserve">B4_cm.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8313,14 +8313,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">培ってきたものを後輩にお伝えしたいのです</t>
+          <t xml:space="preserve">大切なお仕事ですね。精一杯務めさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.earnest.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.earnest.polite[1]</t>
+          <t xml:space="preserve">B4_fan.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8345,14 +8345,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">申し訳ございません…一日も早く復帰いたします</t>
+          <t xml:space="preserve">来てくださった方全員に、心から感謝を伝えたいです</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.earnest.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.earnest.polite[1]</t>
+          <t xml:space="preserve">B4_fashion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8377,14 +8377,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方とは…このままではチームに影響が出ます</t>
+          <t xml:space="preserve">ご期待に沿えるよう、歩き方から練習いたします</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.earnest.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.earnest.polite[1]</t>
+          <t xml:space="preserve">B4_gravure.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8409,14 +8409,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体にご迷惑はかけたくないのですが…あの方とは…</t>
+          <t xml:space="preserve">精一杯きれいに撮っていただけるよう頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.earnest.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.earnest.polite[1]</t>
+          <t xml:space="preserve">B4_variety.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8441,14 +8441,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ブランド様のご期待に添えるよう、精一杯取り組みます</t>
+          <t xml:space="preserve">トーク番組は緊張しますが…誠実に対応いたします</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.earnest.polite[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.earnest.polite[1]</t>
+          <t xml:space="preserve">B4.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8473,14 +8473,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大切なお仕事ですね。精一杯務めさせていただきます</t>
+          <t xml:space="preserve">私でよろしいんですか…？ 精一杯務めさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8490,29 +8490,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">来てくださった方全員に、心から感謝を伝えたいです</t>
+          <t xml:space="preserve">地道に努力するのが取り柄です。信じていただけますか</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8522,29 +8522,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に沿えるよう、歩き方から練習いたします</t>
+          <t xml:space="preserve">お選びいただき、ありがとうございます。精一杯頑張ります</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8554,29 +8554,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">精一杯きれいに撮っていただけるよう頑張ります…</t>
+          <t xml:space="preserve">ご期待に応えられるよう、努力いたします</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8586,29 +8586,29 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">トーク番組は緊張しますが…誠実に対応いたします</t>
+          <t xml:space="preserve">ありがとうございます。期待にお応えいたします</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8618,29 +8618,29 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私でよろしいんですか…？ 精一杯務めさせていただきます</t>
+          <t xml:space="preserve">毎日精進いたします。見ていてください</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8650,12 +8650,12 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8665,14 +8665,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">地道に努力するのが取り柄です。信じていただけますか</t>
+          <t xml:space="preserve">ご期待に応えられず、申し訳ありません</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8697,14 +8697,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただき、ありがとうございます。精一杯頑張ります</t>
+          <t xml:space="preserve">必ず強くなって戻ってまいります</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.earnest.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[2]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8729,14 +8729,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に応えられるよう、努力いたします</t>
+          <t xml:space="preserve">済んだことにしたいのです。……できないだけで</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8761,14 +8761,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。期待にお応えいたします</t>
+          <t xml:space="preserve">決着は……ついておりません。私の中では、まだ</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">draftInterest.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8793,14 +8793,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日精進いたします。見ていてください</t>
+          <t xml:space="preserve">地道に努力するのが取り柄です。信じていただけますか</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">draftJoin.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8825,14 +8825,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に応えられず、申し訳ありません</t>
+          <t xml:space="preserve">お選びいただき、ありがとうございます。精一杯頑張ります</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.earnest.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[2]</t>
+          <t xml:space="preserve">draftJoin.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8857,14 +8857,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">必ず強くなって戻ってまいります</t>
+          <t xml:space="preserve">ご期待に応えられるよう、努力いたします</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.earnest.polite[1]</t>
+          <t xml:space="preserve">faGreeting.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8889,14 +8889,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">済んだことにしたいのです。……できないだけで</t>
+          <t xml:space="preserve">いただいた契約の重み、忘れずにやります</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.earnest.polite[1]</t>
+          <t xml:space="preserve">faSigning.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8921,14 +8921,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着は……ついておりません。私の中では、まだ</t>
+          <t xml:space="preserve">ありがとうございます。期待にお応えいたします</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.earnest.polite[1]</t>
+          <t xml:space="preserve">faWelcome.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8953,14 +8953,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">地道に努力するのが取り柄です。信じていただけますか</t>
+          <t xml:space="preserve">毎日精進いたします。見ていてください</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.earnest.polite[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8985,14 +8985,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただき、ありがとうございます。精一杯頑張ります</t>
+          <t xml:space="preserve">今日は身体が素直に動きます。学んだ分だけ、身につきます</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.earnest.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.earnest.polite[2]</t>
+          <t xml:space="preserve">heatSelf.heavy.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -9017,14 +9017,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に応えられるよう、努力いたします</t>
+          <t xml:space="preserve">同じ量をこなしても、何も積み上がりません。情けないです</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.earnest.polite[1]</t>
+          <t xml:space="preserve">heatSelf.warm.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -9049,14 +9049,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いただいた契約の重み、忘れずにやります</t>
+          <t xml:space="preserve">回数はこなせています。ただ、残る実感が薄くて</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.earnest.polite[1]</t>
+          <t xml:space="preserve">injury.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -9081,14 +9081,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。期待にお応えいたします</t>
+          <t xml:space="preserve">ご期待に応えられず、申し訳ありません</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.earnest.polite[1]</t>
+          <t xml:space="preserve">injury.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -9113,14 +9113,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日精進いたします。見ていてください</t>
+          <t xml:space="preserve">必ず強くなって戻ってまいります</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -9135,7 +9135,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.earnest.polite[1]</t>
+          <t xml:space="preserve">release.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -9145,14 +9145,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は身体が素直に動きます。学んだ分だけ、身につきます</t>
+          <t xml:space="preserve">応援してくださった皆様に、申し訳ありません</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.earnest.polite[1]</t>
+          <t xml:space="preserve">release.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9177,14 +9177,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">同じ量をこなしても、何も積み上がりません。情けないです</t>
+          <t xml:space="preserve">ここでの学び、決して忘れません</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.earnest.polite[1]</t>
+          <t xml:space="preserve">rentalGreeting.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9209,14 +9209,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">回数はこなせています。ただ、残る実感が薄くて</t>
+          <t xml:space="preserve">短い間ですが、精一杯務めさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.earnest.polite[1]</t>
+          <t xml:space="preserve">scoutGreeting.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9241,14 +9241,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に応えられず、申し訳ありません</t>
+          <t xml:space="preserve">お声がけに恥じないよう、努めます</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.earnest.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.earnest.polite[2]</t>
+          <t xml:space="preserve">titleChallengeLoss.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9273,14 +9273,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">必ず強くなって戻ってまいります</t>
+          <t xml:space="preserve">実力が足りませんでした。もっと精進いたします</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.earnest.polite[1]</t>
+          <t xml:space="preserve">titleDefense.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9305,14 +9305,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくださった皆様に、申し訳ありません</t>
+          <t xml:space="preserve">防衛できました。でも、まだまだ精進いたします</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.earnest.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.earnest.polite[2]</t>
+          <t xml:space="preserve">titleLoss.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9337,14 +9337,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここでの学び、決して忘れません</t>
+          <t xml:space="preserve">努力が足りませんでした。一から出直します</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.earnest.polite[1]</t>
+          <t xml:space="preserve">titleWin.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9369,14 +9369,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですが、精一杯務めさせていただきます</t>
+          <t xml:space="preserve">積み重ねが報われました…本当に、ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9386,12 +9386,12 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9401,14 +9401,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お声がけに恥じないよう、努めます</t>
+          <t xml:space="preserve">応援してくださった皆様に、申し訳ありません</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9418,12 +9418,12 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9433,14 +9433,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力が足りませんでした。もっと精進いたします</t>
+          <t xml:space="preserve">ここでの学び、決して忘れません</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9465,14 +9465,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛できました。でも、まだまだ精進いたします</t>
+          <t xml:space="preserve">短い間ですが、精一杯務めさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9482,12 +9482,12 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9497,14 +9497,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">努力が足りませんでした。一から出直します</t>
+          <t xml:space="preserve">実力が足りませんでした。もっと精進いたします</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9514,12 +9514,12 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9529,14 +9529,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねが報われました…本当に、ありがとうございます</t>
+          <t xml:space="preserve">防衛できました。でも、まだまだ精進いたします</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9561,14 +9561,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくださった皆様に、申し訳ありません</t>
+          <t xml:space="preserve">努力が足りませんでした。一から出直します</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.earnest.polite[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[2]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9593,14 +9593,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここでの学び、決して忘れません</t>
+          <t xml:space="preserve">積み重ねが報われました…本当に、ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9610,29 +9610,29 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">bond_39_down.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですが、精一杯務めさせていただきます</t>
+          <t xml:space="preserve">この関係…修復できる自信がありません…</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.polite[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9642,29 +9642,29 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">bond_39_down.earnest.polite[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力が足りませんでした。もっと精進いたします</t>
+          <t xml:space="preserve">どこで間違えてしまったんでしょう…</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9674,29 +9674,29 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">bond_59_down.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛できました。でも、まだまだ精進いたします</t>
+          <t xml:space="preserve">関係を修復したいです…何とかしなければ</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9706,29 +9706,29 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">bond_60_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">努力が足りませんでした。一から出直します</t>
+          <t xml:space="preserve">おかげで練習にも身が入ります。感謝しています</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9738,29 +9738,29 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">bond_80_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねが報われました…本当に、ありがとうございます</t>
+          <t xml:space="preserve">共に歩めること、何よりの幸せです</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.earnest.polite[1]</t>
+          <t xml:space="preserve">rivalry_29_down.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9785,14 +9785,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この関係…修復できる自信がありません…</t>
+          <t xml:space="preserve">関係も変わりました。前に進みましょう</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.polite[2]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9807,7 +9807,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.earnest.polite[2]</t>
+          <t xml:space="preserve">rivalry_29_down.earnest.polite[2]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9817,14 +9817,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どこで間違えてしまったんでしょう…</t>
+          <t xml:space="preserve">あの因縁から学んだことは多いです。次の目標を見つけなければ</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.earnest.polite[1]</t>
+          <t xml:space="preserve">rivalry_30_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9849,14 +9849,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">関係を修復したいです…何とかしなければ</t>
+          <t xml:space="preserve">勝つために、もっと努力しなければなりません</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.earnest.polite[1]</t>
+          <t xml:space="preserve">rivalry_50_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9881,14 +9881,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おかげで練習にも身が入ります。感謝しています</t>
+          <t xml:space="preserve">超えることが、私の覚悟です</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.earnest.polite[1]</t>
+          <t xml:space="preserve">rivalry_70_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9913,14 +9913,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">共に歩めること、何よりの幸せです</t>
+          <t xml:space="preserve">この切磋琢磨こそが、私の原動力です</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9935,7 +9935,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.earnest.polite[1]</t>
+          <t xml:space="preserve">trust_above_75.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9945,14 +9945,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">関係も変わりました。前に進みましょう</t>
+          <t xml:space="preserve">ご期待に添えるよう、精一杯頑張らせていただきます</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.earnest.polite[2]</t>
+          <t xml:space="preserve">trust_below_20.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9977,14 +9977,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの因縁から学んだことは多いです。次の目標を見つけなければ</t>
+          <t xml:space="preserve">大変申し訳ありませんが…退団を検討させていただきます</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.earnest.polite[1]</t>
+          <t xml:space="preserve">trust_below_35.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -10009,14 +10009,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝つために、もっと努力しなければなりません</t>
+          <t xml:space="preserve">恐縮ですが…少し運営に対して不安があります…</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -10026,12 +10026,12 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.earnest.polite[1]</t>
+          <t xml:space="preserve">GL-01.loss.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -10041,14 +10041,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">超えることが、私の覚悟です</t>
+          <t xml:space="preserve">不甲斐ない試合をしてしまいました。申し訳ございません</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -10058,12 +10058,12 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.earnest.polite[1]</t>
+          <t xml:space="preserve">GL-01.win.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -10073,14 +10073,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この切磋琢磨こそが、私の原動力です</t>
+          <t xml:space="preserve">勝利できました。引き続き精進します</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.earnest.polite[1]</t>
+          <t xml:space="preserve">GL-02.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -10105,14 +10105,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に添えるよう、精一杯頑張らせていただきます</t>
+          <t xml:space="preserve">基本を怠らず、しっかり取り組みます</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -10122,12 +10122,12 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.earnest.polite[1]</t>
+          <t xml:space="preserve">GL-04.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -10137,14 +10137,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大変申し訳ありませんが…退団を検討させていただきます</t>
+          <t xml:space="preserve">ともに成長できることが嬉しいです</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -10154,12 +10154,12 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.earnest.polite[1]</t>
+          <t xml:space="preserve">GL-05.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -10169,14 +10169,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">恐縮ですが…少し運営に対して不安があります…</t>
+          <t xml:space="preserve">追いつくため、日々研鑽します</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.earnest.polite[1]</t>
+          <t xml:space="preserve">GL-06.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10201,14 +10201,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不甲斐ない試合をしてしまいました。申し訳ございません</t>
+          <t xml:space="preserve">出場機会をいただけるよう、より一層努力いたします</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.earnest.polite[1]</t>
+          <t xml:space="preserve">GL-07.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10233,14 +10233,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝利できました。引き続き精進します</t>
+          <t xml:space="preserve">体調管理を怠りました。しっかり立て直します</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10255,7 +10255,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.earnest.polite[1]</t>
+          <t xml:space="preserve">GL-08.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10265,14 +10265,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">基本を怠らず、しっかり取り組みます</t>
+          <t xml:space="preserve">不甲斐ない結果が続いています…何とか打開しなければ</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10287,7 +10287,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.earnest.polite[1]</t>
+          <t xml:space="preserve">GL-09.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10297,14 +10297,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ともに成長できることが嬉しいです</t>
+          <t xml:space="preserve">結果がついてきていますが、慢心せず精進します</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10319,7 +10319,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.earnest.polite[1]</t>
+          <t xml:space="preserve">GL-10.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10329,14 +10329,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">追いつくため、日々研鑽します</t>
+          <t xml:space="preserve">復帰に向けて、今できることを精一杯やります</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10346,12 +10346,12 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10361,14 +10361,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">出場機会をいただけるよう、より一層努力いたします</t>
+          <t xml:space="preserve">好調期間は終わりましたが、学びの多い日々でした</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.earnest.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10378,29 +10378,29 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.earnest.polite[1]</t>
+          <t xml:space="preserve">preFinal.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体調管理を怠りました。しっかり立て直します</t>
+          <t xml:space="preserve">身体はぼろぼろですが…最後まで、全力でお応えします</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.earnest.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10410,29 +10410,29 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.earnest.polite[1]</t>
+          <t xml:space="preserve">preFinal.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不甲斐ない結果が続いています…何とか打開しなければ</t>
+          <t xml:space="preserve">ここまで繋いでくれた仲間のために、私が締めます。どんなに痛くても</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.earnest.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.earnest[3]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10442,29 +10442,29 @@
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.earnest.polite[1]</t>
+          <t xml:space="preserve">preFinal.polite.earnest[3]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">結果がついてきていますが、慢心せず精進します</t>
+          <t xml:space="preserve">痛みは、勝ってから数えます。今は、目の前の一戦に全部を</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.earnest.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10474,29 +10474,29 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.earnest.polite[1]</t>
+          <t xml:space="preserve">preMatch.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">復帰に向けて、今できることを精一杯やります</t>
+          <t xml:space="preserve">相手がどなたでも、全力でお応えします。手を抜くのは失礼ですから</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10506,29 +10506,29 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">preMatch.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">好調期間は終わりましたが、学びの多い日々でした</t>
+          <t xml:space="preserve">一戦ずつ、丁寧に。託された役目、途中で放り出せません</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.earnest.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.earnest[3]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10543,7 +10543,7 @@
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.earnest.polite[1]</t>
+          <t xml:space="preserve">preMatch.polite.earnest[3]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10553,14 +10553,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体はぼろぼろですが…最後まで、全力でお応えします</t>
+          <t xml:space="preserve">まずは目の前の一人に、心を込めて。それが私の役目ですから</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.earnest.polite[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.earnest.polite[2]</t>
+          <t xml:space="preserve">survivor.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10585,14 +10585,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで繋いでくれた仲間のために、私が締めます。どんなに痛くても</t>
+          <t xml:space="preserve">一人、止めました。…息は上がってますが、退きません。次の方も、全力でお相手します</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.earnest.polite[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10607,7 +10607,7 @@
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.earnest.polite[3]</t>
+          <t xml:space="preserve">survivor.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10617,14 +10617,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">痛みは、勝ってから数えます。今は、目の前の一戦に全部を</t>
+          <t xml:space="preserve">まだ立ってます。仲間に繋ぐまで、このリングは渡しません。次、どうぞ</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.earnest.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.earnest[3]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.earnest.polite[1]</t>
+          <t xml:space="preserve">survivor.polite.earnest[3]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10649,14 +10649,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手がどなたでも、全力でお応えします。手を抜くのは失礼ですから</t>
+          <t xml:space="preserve">一人、お相手しました。…はぁ、まだ立てます。繋ぐまでは、退けませんから</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.earnest.polite[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="C318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.earnest.polite[2]</t>
+          <t xml:space="preserve">champion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10681,14 +10681,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦ずつ、丁寧に。託された役目、途中で放り出せません</t>
+          <t xml:space="preserve">託された順番を、最後まで全うできました。仲間に感謝しています</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.earnest.polite[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="C319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.earnest.polite[3]</t>
+          <t xml:space="preserve">champion.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10713,14 +10713,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まずは目の前の一人に、心を込めて。それが私の役目ですから</t>
+          <t xml:space="preserve">三人でつないだ勝利を、団体に持ち帰れます。それが何より嬉しいです</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.earnest.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10730,12 +10730,12 @@
       </c>
       <c r="C320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.earnest.polite[1]</t>
+          <t xml:space="preserve">defiant.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10745,14 +10745,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、止めました。…息は上がってますが、退きません。次の方も、全力でお相手します</t>
+          <t xml:space="preserve">評価していただいてありがとうございます。でも、次は団体ごと勝って応えたいです</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.earnest.polite[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10762,12 +10762,12 @@
       </c>
       <c r="C321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.earnest.polite[2]</t>
+          <t xml:space="preserve">defiant.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10777,14 +10777,14 @@
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってます。仲間に繋ぐまで、このリングは渡しません。次、どうぞ</t>
+          <t xml:space="preserve">仲間のためにもっとやれたはず。その反省を、次に生かします</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.earnest.polite[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="C322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.earnest.polite[3]</t>
+          <t xml:space="preserve">gauntlet.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10809,14 +10809,14 @@
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、お相手しました。…はぁ、まだ立てます。繋ぐまでは、退けませんから</t>
+          <t xml:space="preserve">全力で来てくださった皆さんに、全力で応えました。それだけは胸を張れます</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.earnest.polite[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.polite[1]</t>
+          <t xml:space="preserve">gauntlet.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10841,14 +10841,14 @@
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">託された順番を、最後まで全うできました。仲間に感謝しています</t>
+          <t xml:space="preserve">何度も限界を感じました。でも、託された役割を途中で降りるわけにはいきません</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.earnest.polite[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10858,12 +10858,12 @@
       </c>
       <c r="C324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.polite[2]</t>
+          <t xml:space="preserve">champion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10873,14 +10873,14 @@
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人でつないだ勝利を、団体に持ち帰れます。それが何より嬉しいです</t>
+          <t xml:space="preserve">優勝…させていただきました。皆様のおかげです…！</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.earnest.polite[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10890,12 +10890,12 @@
       </c>
       <c r="C325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.earnest.polite[1]</t>
+          <t xml:space="preserve">champion.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10905,14 +10905,14 @@
       </c>
       <c r="F325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">評価していただいてありがとうございます。でも、次は団体ごと勝って応えたいです</t>
+          <t xml:space="preserve">この経験を糧に、さらに精進して参ります</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.earnest.polite[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="C326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.earnest.polite[2]</t>
+          <t xml:space="preserve">postLose.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10937,14 +10937,14 @@
       </c>
       <c r="F326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間のためにもっとやれたはず。その反省を、次に生かします</t>
+          <t xml:space="preserve">力不足で申し訳ございません…。もっと精進します</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.earnest.polite[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10954,12 +10954,12 @@
       </c>
       <c r="C327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.earnest.polite[1]</t>
+          <t xml:space="preserve">postLose.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10969,14 +10969,14 @@
       </c>
       <c r="F327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で来てくださった皆さんに、全力で応えました。それだけは胸を張れます</t>
+          <t xml:space="preserve">悔しゅうございます…。必ず強くなります</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.earnest.polite[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="C328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.earnest.polite[2]</t>
+          <t xml:space="preserve">postMatchWin.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -11001,14 +11001,14 @@
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何度も限界を感じました。でも、託された役割を途中で降りるわけにはいきません</t>
+          <t xml:space="preserve">勝たせていただきました…。次も全力で臨みます</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.earnest.polite[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.polite[1]</t>
+          <t xml:space="preserve">postMatchWin.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -11033,14 +11033,14 @@
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝…させていただきました。皆様のおかげです…！</t>
+          <t xml:space="preserve">一戦一戦、大切に。次もよろしくお願いいたします</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.earnest.polite[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.polite[2]</t>
+          <t xml:space="preserve">postWin.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -11065,14 +11065,14 @@
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この経験を糧に、さらに精進して参ります</t>
+          <t xml:space="preserve">良い経験をさせていただきました。精進して参ります</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.earnest.polite[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.earnest.polite[1]</t>
+          <t xml:space="preserve">postWin.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
@@ -11097,14 +11097,14 @@
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">力不足で申し訳ございません…。もっと精進します</t>
+          <t xml:space="preserve">皆様のおかげで戦い抜けました。感謝いたします</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.earnest.polite[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.earnest.polite[2]</t>
+          <t xml:space="preserve">preFinal.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -11129,14 +11129,14 @@
       </c>
       <c r="F332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しゅうございます…。必ず強くなります</t>
+          <t xml:space="preserve">決勝の舞台…身に余る光栄です。全力でお応えいたします</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.earnest.polite[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.earnest.polite[1]</t>
+          <t xml:space="preserve">preFinal.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
@@ -11161,14 +11161,14 @@
       </c>
       <c r="F333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝たせていただきました…。次も全力で臨みます</t>
+          <t xml:space="preserve">この一戦に、全てをお捧げいたします</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.earnest.polite[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -11183,7 +11183,7 @@
       </c>
       <c r="D334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.earnest.polite[2]</t>
+          <t xml:space="preserve">preMatch.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E334" t="inlineStr" s="2">
@@ -11193,14 +11193,14 @@
       </c>
       <c r="F334" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦一戦、大切に。次もよろしくお願いいたします</t>
+          <t xml:space="preserve">精一杯の試合を、お見せいたします</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.earnest.polite[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -11215,7 +11215,7 @@
       </c>
       <c r="D335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.earnest.polite[1]</t>
+          <t xml:space="preserve">preMatch.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
@@ -11225,14 +11225,14 @@
       </c>
       <c r="F335" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">良い経験をさせていただきました。精進して参ります</t>
+          <t xml:space="preserve">ひとつひとつ丁寧に…全力で参ります</t>
         </is>
       </c>
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.earnest.polite[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -11247,7 +11247,7 @@
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.earnest.polite[2]</t>
+          <t xml:space="preserve">summon.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E336" t="inlineStr" s="2">
@@ -11257,14 +11257,14 @@
       </c>
       <c r="F336" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様のおかげで戦い抜けました。感謝いたします</t>
+          <t xml:space="preserve">身に余る光栄です。一生懸命頑張ります</t>
         </is>
       </c>
     </row>
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.earnest.polite[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -11279,7 +11279,7 @@
       </c>
       <c r="D337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.earnest.polite[1]</t>
+          <t xml:space="preserve">summon.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E337" t="inlineStr" s="2">
@@ -11289,14 +11289,14 @@
       </c>
       <c r="F337" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝の舞台…身に余る光栄です。全力でお応えいたします</t>
+          <t xml:space="preserve">お声がけいただき感謝いたします。精一杯務めます</t>
         </is>
       </c>
     </row>
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.earnest.polite[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -11306,12 +11306,12 @@
       </c>
       <c r="C338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.earnest.polite[2]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E338" t="inlineStr" s="2">
@@ -11321,14 +11321,14 @@
       </c>
       <c r="F338" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この一戦に、全てをお捧げいたします</t>
+          <t xml:space="preserve">お互い全力で…よろしくお願いいたします</t>
         </is>
       </c>
     </row>
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.earnest.polite[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -11338,12 +11338,12 @@
       </c>
       <c r="C339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E339" t="inlineStr" s="2">
@@ -11353,14 +11353,14 @@
       </c>
       <c r="F339" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">精一杯の試合を、お見せいたします</t>
+          <t xml:space="preserve">皆さまのご声援のおかげです……本当に、ありがとうございます……！</t>
         </is>
       </c>
     </row>
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.earnest.polite[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -11370,12 +11370,12 @@
       </c>
       <c r="C340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D340" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.earnest.polite[2]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E340" t="inlineStr" s="2">
@@ -11385,14 +11385,14 @@
       </c>
       <c r="F340" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ひとつひとつ丁寧に…全力で参ります</t>
+          <t xml:space="preserve">失礼ながら、対抗戦のお申し込みをさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="341" ht="40" customHeight="1">
       <c r="A341" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.earnest.polite[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -11402,12 +11402,12 @@
       </c>
       <c r="C341" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D341" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E341" t="inlineStr" s="2">
@@ -11417,14 +11417,14 @@
       </c>
       <c r="F341" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身に余る光栄です。一生懸命頑張ります</t>
+          <t xml:space="preserve">全力でお相手いたしますので、覚悟なさってください</t>
         </is>
       </c>
     </row>
     <row r="342" ht="40" customHeight="1">
       <c r="A342" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.earnest.polite[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -11434,12 +11434,12 @@
       </c>
       <c r="C342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D342" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.earnest.polite[2]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E342" t="inlineStr" s="2">
@@ -11449,14 +11449,14 @@
       </c>
       <c r="F342" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お声がけいただき感謝いたします。精一杯務めます</t>
+          <t xml:space="preserve">残念ですが…いつかお受けいただけることを願っております</t>
         </is>
       </c>
     </row>
     <row r="343" ht="40" customHeight="1">
       <c r="A343" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -11466,12 +11466,12 @@
       </c>
       <c r="C343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D343" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E343" t="inlineStr" s="2">
@@ -11481,14 +11481,14 @@
       </c>
       <c r="F343" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お互い全力で…よろしくお願いいたします</t>
+          <t xml:space="preserve">改めてお声がけいたします。その時はぜひ</t>
         </is>
       </c>
     </row>
     <row r="344" ht="40" customHeight="1">
       <c r="A344" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="C344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D344" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">result_lose.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E344" t="inlineStr" s="2">
@@ -11513,14 +11513,14 @@
       </c>
       <c r="F344" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆さまのご声援のおかげです……本当に、ありがとうございます……！</t>
+          <t xml:space="preserve">完敗でした…。この悔しさを胸に、精進いたします</t>
         </is>
       </c>
     </row>
     <row r="345" ht="40" customHeight="1">
       <c r="A345" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.earnest.polite[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -11530,12 +11530,12 @@
       </c>
       <c r="C345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D345" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">result_lose.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E345" t="inlineStr" s="2">
@@ -11545,14 +11545,14 @@
       </c>
       <c r="F345" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">失礼ながら、対抗戦のお申し込みをさせていただきます</t>
+          <t xml:space="preserve">申し訳ございません…。必ず成長してお返しいたします</t>
         </is>
       </c>
     </row>
     <row r="346" ht="40" customHeight="1">
       <c r="A346" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.earnest.polite[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
@@ -11562,12 +11562,12 @@
       </c>
       <c r="C346" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D346" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[2]</t>
+          <t xml:space="preserve">result_win.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E346" t="inlineStr" s="2">
@@ -11577,14 +11577,14 @@
       </c>
       <c r="F346" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力でお相手いたしますので、覚悟なさってください</t>
+          <t xml:space="preserve">勝たせていただきました。素晴らしい対抗戦に感謝いたします</t>
         </is>
       </c>
     </row>
     <row r="347" ht="40" customHeight="1">
       <c r="A347" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.earnest.polite[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -11594,12 +11594,12 @@
       </c>
       <c r="C347" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D347" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">result_win.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E347" t="inlineStr" s="2">
@@ -11609,14 +11609,14 @@
       </c>
       <c r="F347" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残念ですが…いつかお受けいただけることを願っております</t>
+          <t xml:space="preserve">皆様のおかげで勝利できました。ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="348" ht="40" customHeight="1">
       <c r="A348" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.earnest.polite[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -11626,12 +11626,12 @@
       </c>
       <c r="C348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D348" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[2]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E348" t="inlineStr" s="2">
@@ -11641,14 +11641,14 @@
       </c>
       <c r="F348" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">改めてお声がけいたします。その時はぜひ</t>
+          <t xml:space="preserve">団体の代表として勝利できましたこと…光栄でございます</t>
         </is>
       </c>
     </row>
     <row r="349" ht="40" customHeight="1">
       <c r="A349" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.earnest.polite[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -11658,12 +11658,12 @@
       </c>
       <c r="C349" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D349" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E349" t="inlineStr" s="2">
@@ -11673,14 +11673,14 @@
       </c>
       <c r="F349" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">完敗でした…。この悔しさを胸に、精進いたします</t>
+          <t xml:space="preserve">団体の名に恥じない試合ができたのであれば…嬉しゅうございます</t>
         </is>
       </c>
     </row>
     <row r="350" ht="40" customHeight="1">
       <c r="A350" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.earnest.polite[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.earnest[3]</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
@@ -11690,12 +11690,12 @@
       </c>
       <c r="C350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D350" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.earnest.polite[2]</t>
+          <t xml:space="preserve">polite.earnest[3]</t>
         </is>
       </c>
       <c r="E350" t="inlineStr" s="2">
@@ -11705,14 +11705,14 @@
       </c>
       <c r="F350" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">申し訳ございません…。必ず成長してお返しいたします</t>
+          <t xml:space="preserve">団体の皆様のおかげで勝利できました。心より感謝申し上げます</t>
         </is>
       </c>
     </row>
     <row r="351" ht="40" customHeight="1">
       <c r="A351" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.earnest.polite[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
@@ -11722,29 +11722,29 @@
       </c>
       <c r="C351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D351" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.earnest.polite[1]</t>
+          <t xml:space="preserve">fighter.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F351" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝たせていただきました。素晴らしい対抗戦に感謝いたします</t>
+          <t xml:space="preserve">積み重ねてきた全てが報われました…ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="352" ht="40" customHeight="1">
       <c r="A352" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.earnest.polite[2]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -11754,29 +11754,29 @@
       </c>
       <c r="C352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D352" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.earnest.polite[2]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
       <c r="F352" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様のおかげで勝利できました。ありがとうございます</t>
+          <t xml:space="preserve">いただいた契約の重み、忘れずにやります</t>
         </is>
       </c>
     </row>
     <row r="353" ht="40" customHeight="1">
       <c r="A353" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.earnest.polite[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -11786,187 +11786,27 @@
       </c>
       <c r="C353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
       <c r="D353" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
       <c r="F353" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の代表として勝利できましたこと…光栄でございます</t>
-        </is>
-      </c>
-    </row>
-    <row r="354" ht="40" customHeight="1">
-      <c r="A354" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.earnest.polite[2]</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">earnest.polite[2]</t>
-        </is>
-      </c>
-      <c r="E354" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F354" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">団体の名に恥じない試合ができたのであれば…嬉しゅうございます</t>
-        </is>
-      </c>
-    </row>
-    <row r="355" ht="40" customHeight="1">
-      <c r="A355" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.earnest.polite[3]</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">earnest.polite[3]</t>
-        </is>
-      </c>
-      <c r="E355" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F355" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">団体の皆様のおかげで勝利できました。心より感謝申し上げます</t>
-        </is>
-      </c>
-    </row>
-    <row r="356" ht="40" customHeight="1">
-      <c r="A356" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.earnest.polite[1]</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ENDING_LINES</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">fighter.earnest.polite[1]</t>
-        </is>
-      </c>
-      <c r="E356" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
-        </is>
-      </c>
-      <c r="F356" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">積み重ねてきた全てが報われました…ありがとうございます</t>
-        </is>
-      </c>
-    </row>
-    <row r="357" ht="40" customHeight="1">
-      <c r="A357" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FA_GREETING_LINES.earnest.polite[1]</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
-        </is>
-      </c>
-      <c r="E357" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
-        </is>
-      </c>
-      <c r="F357" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">いただいた契約の重み、忘れずにやります</t>
-        </is>
-      </c>
-    </row>
-    <row r="358" ht="40" customHeight="1">
-      <c r="A358" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.earnest.polite[1]</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">earnest.polite[1]</t>
-        </is>
-      </c>
-      <c r="E358" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
-        </is>
-      </c>
-      <c r="F358" t="inlineStr" s="3">
-        <is>
           <t xml:space="preserve">お声がけに恥じないよう、努めます</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H358"/>
+  <autoFilter ref="A1:H353"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/丁寧×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×真面目.xlsx
@@ -193,7 +193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -205,7 +205,7 @@
     <row r="1">
       <c r="A1" t="inlineStr" s="11">
         <is>
-          <t xml:space="preserve">このタイプ(丁寧×真面目)に該当するキャラクター: 11名</t>
+          <t xml:space="preserve">このタイプ(丁寧×真面目)に該当するキャラクター: 12名</t>
         </is>
       </c>
     </row>
@@ -323,7 +323,7 @@
     <row r="8">
       <c r="A8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">高橋まゆみ</t>
+          <t xml:space="preserve">白銀麗子</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -338,14 +338,14 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ファンサービス、名���負製造機、華</t>
+          <t xml:space="preserve">不屈、華、頑丈さ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">伊勢原文奈</t>
+          <t xml:space="preserve">高橋まゆみ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -360,14 +360,14 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">忠誠心</t>
+          <t xml:space="preserve">ファンサービス、名���負製造機、華</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">富士見ヶ丘遥</t>
+          <t xml:space="preserve">伊勢原文奈</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -382,63 +382,63 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ファンサービス</t>
+          <t xml:space="preserve">忠誠心</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">栗林あかり</t>
+          <t xml:space="preserve">富士見ヶ丘遥</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Striker</t>
+          <t xml:space="preserve">Allround</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Neutral</t>
+          <t xml:space="preserve">Babyface</t>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ライバル体質、負けず嫌い</t>
+          <t xml:space="preserve">ファンサービス</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">財津琴美</t>
+          <t xml:space="preserve">栗林あかり</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Allround</t>
+          <t xml:space="preserve">Striker</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Babyface</t>
+          <t xml:space="preserve">Neutral</t>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">努力家</t>
+          <t xml:space="preserve">ライバル体質、負けず嫌い</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">豊田いすず</t>
+          <t xml:space="preserve">財津琴美</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grappler</t>
+          <t xml:space="preserve">Allround</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
@@ -448,27 +448,49 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">引き出し上手</t>
+          <t xml:space="preserve">努力家</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr" s="12">
         <is>
+          <t xml:space="preserve">豊田いすず</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Grappler</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Babyface</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">引き出し上手</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr" s="12">
+        <is>
           <t xml:space="preserve">榊原菜摘</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr" s="2">
+      <c r="B15" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Allround</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr" s="2">
+      <c r="C15" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Neutral</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr" s="12">
+      <c r="D15" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">努力家、晩成</t>
         </is>
@@ -482,7 +504,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H353"/>
+  <dimension ref="A1:H355"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1301,7 +1323,7 @@
       </c>
       <c r="F25" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ようやくお世話になれる場所が。全力で恩返しいたします</t>
+          <t xml:space="preserve">お声がけ、ありがとうございます。積んできたもの、全力でお見せします。</t>
         </is>
       </c>
     </row>
@@ -2997,7 +3019,7 @@
       </c>
       <c r="F78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしを選んだのなら、その責任は果たします。</t>
+          <t xml:space="preserve">私を選んだのなら、その責任は果たします。</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3243,7 @@
       </c>
       <c r="F85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしの力不足です。……この負けは、忘れません。</t>
+          <t xml:space="preserve">私の力不足です。……この負けは、忘れません。</t>
         </is>
       </c>
     </row>
@@ -5913,7 +5935,7 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">申し上げにくいのですが……今のままでは、わたくしたち、息が詰まります。</t>
+          <t xml:space="preserve">申し上げにくいのですが……今のままでは、私たち、息が詰まります。</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6351,7 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…あのお稽古が、今、実を結ぼうとしている——）</t>
+          <t xml:space="preserve">（…あの練習が、今、実を結ぼうとしている——）</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6870,7 @@
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.polite.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6863,7 +6885,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.polite.earnest[1]</t>
+          <t xml:space="preserve">autumnWarChampion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6873,14 +6895,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの試合は一生の宝物です。対戦相手の方に、心から感謝しています</t>
+          <t xml:space="preserve">仲間を信じ、仲間に応える。その思いで戦い抜きました。</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.polite.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6895,7 +6917,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.earnest[1]</t>
+          <t xml:space="preserve">bestMatch.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6905,14 +6927,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">王者としての責任を全うします。毎試合、最高の試合をお届けします</t>
+          <t xml:space="preserve">あの試合は一生の宝物です。対戦相手の方に、心から感謝しています</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.polite.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6927,7 +6949,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.polite.earnest[1]</t>
+          <t xml:space="preserve">champion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6937,14 +6959,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の皆さん。リングに真実があります。どうか、立ち続けてください</t>
+          <t xml:space="preserve">王者としての責任を全うします。毎試合、最高の試合をお届けします</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.polite.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6959,7 +6981,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.polite.earnest[1]</t>
+          <t xml:space="preserve">hallOfFame.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6969,14 +6991,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">日々の積み重ねが実を結びました。来年も変わらず精進します</t>
+          <t xml:space="preserve">後輩の皆さん。リングに真実があります。どうか、立ち続けてください</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.polite.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6991,7 +7013,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.polite.earnest[1]</t>
+          <t xml:space="preserve">mvp.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -7001,14 +7023,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日の積み重ねが報われました。指導してくださった皆さん、ありがとうございます</t>
+          <t xml:space="preserve">日々の積み重ねが実を結びました。来年も変わらず精進します</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -7018,12 +7040,12 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">rookie.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -7033,14 +7055,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドーム大会という大役、謹んでお受けいたします</t>
+          <t xml:space="preserve">毎日の積み重ねが報われました。指導してくださった皆さん、ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.earnest[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -7050,12 +7072,12 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[2]</t>
+          <t xml:space="preserve">springTagChampion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -7065,14 +7087,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後の最後まで、手を抜きません</t>
+          <t xml:space="preserve">互いを信じ続けたことが、この結果につながりました。</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.earnest[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -7087,7 +7109,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[3]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -7097,14 +7119,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この恩に、必ず応えてみせます</t>
+          <t xml:space="preserve">ドーム大会という大役、謹んでお受けいたします</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -7114,12 +7136,12 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -7129,14 +7151,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員のお客様、心より感謝申し上げます</t>
+          <t xml:space="preserve">最後の最後まで、手を抜きません</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.earnest[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.earnest[3]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -7146,12 +7168,12 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[2]</t>
+          <t xml:space="preserve">polite.earnest[3]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -7161,14 +7183,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力を尽くした甲斐がありました</t>
+          <t xml:space="preserve">この恩に、必ず応えてみせます</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.earnest[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7183,7 +7205,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[3]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7193,14 +7215,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次も、必ず期待に応えます</t>
+          <t xml:space="preserve">満員のお客様、心より感謝申し上げます</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.polite.earnest[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7210,29 +7232,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねが大切だと信じています。コツコツ参ります</t>
+          <t xml:space="preserve">全力を尽くした甲斐がありました</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.polite.earnest[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.earnest[3]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7242,29 +7264,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[3]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にお稽古していると、自分も頑張ろうと思えます</t>
+          <t xml:space="preserve">次も、必ず期待に応えます</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.polite.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7279,7 +7301,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.polite.earnest[1]</t>
+          <t xml:space="preserve">N1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7289,14 +7311,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">申し訳ありません…少し休ませていただければ、必ず戻ります</t>
+          <t xml:space="preserve">積み重ねが大切だと信じています。コツコツ参ります</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.polite.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7311,7 +7333,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.polite.earnest[1]</t>
+          <t xml:space="preserve">N2.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7321,14 +7343,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様の応援が、何よりの原動力です</t>
+          <t xml:space="preserve">一緒に練習していると、自分も頑張ろうと思えます</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.polite.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7343,7 +7365,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.polite.earnest[1]</t>
+          <t xml:space="preserve">N3.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7353,14 +7375,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">裏切るつもりはございません。ただ……</t>
+          <t xml:space="preserve">申し訳ありません…少し休ませていただければ、必ず戻ります</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.polite.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7375,7 +7397,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.polite.earnest[1]</t>
+          <t xml:space="preserve">N4.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7385,14 +7407,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習を重ねても、何か足りない気がいたしまして…</t>
+          <t xml:space="preserve">皆様の応援が、何よりの原動力です</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.polite.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7402,12 +7424,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.polite.earnest[1]</t>
+          <t xml:space="preserve">N5_low.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7417,14 +7439,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…何か気に障ることをしたのでしょうか</t>
+          <t xml:space="preserve">裏切るつもりはございません。ただ……</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.polite.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7434,12 +7456,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.polite.earnest[1]</t>
+          <t xml:space="preserve">N5_warning.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7449,14 +7471,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name2}さんとご一緒できて幸せでした。…お元気で</t>
+          <t xml:space="preserve">練習を重ねても、何か足りない気がいたしまして…</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.polite.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7466,29 +7488,29 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.polite.earnest[1]</t>
+          <t xml:space="preserve">R2.voice.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。必ず結果でお返しいたします</t>
+          <t xml:space="preserve">…何か気に障ることをしたのでしょうか</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.polite.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7498,29 +7520,29 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.polite.earnest[1]</t>
+          <t xml:space="preserve">R3.modal.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で取り組ませていただきます。レベルアップしてみせます</t>
+          <t xml:space="preserve">{name2}さんとご一緒できて幸せでした。…お元気で</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.polite.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7535,7 +7557,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.polite.earnest[1]</t>
+          <t xml:space="preserve">bonus.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7545,14 +7567,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと見守ってくださったんですね…必ずお報いいたします</t>
+          <t xml:space="preserve">ありがとうございます。必ず結果でお返しいたします</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.polite.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7567,7 +7589,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.polite.earnest[1]</t>
+          <t xml:space="preserve">camp.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7577,14 +7599,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お言葉、ありがとうございます。もう一度頑張ります</t>
+          <t xml:space="preserve">全力で取り組ませていただきます。レベルアップしてみせます</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.polite.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7599,7 +7621,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.polite.earnest[1]</t>
+          <t xml:space="preserve">encourage_high_trust.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7609,14 +7631,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしの至らなさです。申し訳ありませんでした</t>
+          <t xml:space="preserve">ずっと見守ってくださったんですね…必ずお報いいたします</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.polite.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7631,7 +7653,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.polite.earnest[1]</t>
+          <t xml:space="preserve">encourage.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7641,14 +7663,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">緊張いたしますが…精一杯務めます</t>
+          <t xml:space="preserve">お言葉、ありがとうございます。もう一度頑張ります</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.polite.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7663,7 +7685,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.polite.earnest[1]</t>
+          <t xml:space="preserve">faction_decree.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7673,14 +7695,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様、お疲れ様でした。明日からまた頑張りましょう</t>
+          <t xml:space="preserve">私の至らなさです。申し訳ありませんでした</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.polite.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7695,7 +7717,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.polite.earnest[1]</t>
+          <t xml:space="preserve">media.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7705,14 +7727,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習が気になりますが…お気遣いありがとうございます</t>
+          <t xml:space="preserve">緊張いたしますが…精一杯務めます</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.polite.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7727,7 +7749,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.polite.earnest[1]</t>
+          <t xml:space="preserve">party.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7737,14 +7759,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご厚意に甘えます。必ず復帰してお返しいたします</t>
+          <t xml:space="preserve">皆様、お疲れ様でした。明日からまた頑張りましょう</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.polite.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7759,7 +7781,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.polite.earnest[1]</t>
+          <t xml:space="preserve">refresh_leave.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7769,14 +7791,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな機会をいただけて…全力でお応えいたします</t>
+          <t xml:space="preserve">練習が気になりますが…お気遣いありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7786,12 +7808,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.polite.earnest[1]</t>
+          <t xml:space="preserve">special_treatment.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7801,14 +7823,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">緊張いたしますが…精一杯務めさせていただきます</t>
+          <t xml:space="preserve">…ご厚意に甘えます。必ず復帰してお返しいたします</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.polite.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7818,12 +7840,12 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.polite.earnest[1]</t>
+          <t xml:space="preserve">trainer.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7833,14 +7855,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こちらに義理がございますので…ただ、ご報告だけは</t>
+          <t xml:space="preserve">こんな機会をいただけて…全力でお応えいたします</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.polite.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7855,7 +7877,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.polite.earnest[1]</t>
+          <t xml:space="preserve">E1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7865,14 +7887,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大変申し訳ございません…今日はどうしても…</t>
+          <t xml:space="preserve">緊張いたしますが…精一杯務めさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.polite.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7887,7 +7909,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.polite.earnest[1]</t>
+          <t xml:space="preserve">E6.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7897,14 +7919,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「わたし、このままでいいんでしょうか…」と後輩に弱音をこぼしている）</t>
+          <t xml:space="preserve">こちらに義理がございますので…ただ、ご報告だけは</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.polite.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7919,7 +7941,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.polite.earnest[1]</t>
+          <t xml:space="preserve">S_boycott.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7929,14 +7951,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「わたしは本当にここで必要とされているんでしょうか」と率直な投稿）</t>
+          <t xml:space="preserve">大変申し訳ございません…今日はどうしても…</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.polite.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7951,7 +7973,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.polite.earnest[1]</t>
+          <t xml:space="preserve">S_grumble.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7961,14 +7983,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと準備して参りました。チャンスをいただけませんか</t>
+          <t xml:space="preserve">（「私、このままでいいんでしょうか…」と後輩に弱音をこぼしている）</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.polite.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7983,7 +8005,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.polite.earnest[1]</t>
+          <t xml:space="preserve">S_sns.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7993,14 +8015,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方との試合を組んでいただけないでしょうか</t>
+          <t xml:space="preserve">（SNSに「私は本当にここで必要とされているんでしょうか」と率直な投稿）</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.polite.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -8015,7 +8037,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.polite.earnest[1]</t>
+          <t xml:space="preserve">S1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -8025,14 +8047,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご迷惑をおかけしまして申し訳ございません…少しお休みをいただけますか</t>
+          <t xml:space="preserve">ずっと準備して参りました。チャンスをいただけませんか</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.polite.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -8047,7 +8069,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.polite.earnest[1]</t>
+          <t xml:space="preserve">S2.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -8057,14 +8079,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと我慢して参りましたが…このままでは限界です</t>
+          <t xml:space="preserve">あの方との試合を組んでいただけないでしょうか</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.polite.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -8079,7 +8101,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.polite.earnest[1]</t>
+          <t xml:space="preserve">S3.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -8089,14 +8111,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（何か申し上げかけて、深く頭を下げるだけだった）</t>
+          <t xml:space="preserve">ご迷惑をおかけしまして申し訳ございません…少しお休みをいただけますか</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.polite.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -8111,7 +8133,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.polite.earnest[1]</t>
+          <t xml:space="preserve">S4_direct.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -8121,14 +8143,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと強くなりたいのです。特訓をお許しいただけますか</t>
+          <t xml:space="preserve">ずっと我慢して参りましたが…このままでは限界です</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.polite.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -8143,7 +8165,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.polite.earnest[1]</t>
+          <t xml:space="preserve">S4_silent.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -8153,14 +8175,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">培ってきたものを後輩にお伝えしたいのです</t>
+          <t xml:space="preserve">…………（何か申し上げかけて、深く頭を下げるだけだった）</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.polite.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8170,12 +8192,12 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.polite.earnest[1]</t>
+          <t xml:space="preserve">S5.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8185,14 +8207,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">申し訳ございません…一日も早く復帰いたします</t>
+          <t xml:space="preserve">もっと強くなりたいのです。特訓をお許しいただけますか</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.polite.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8202,12 +8224,12 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.polite.earnest[1]</t>
+          <t xml:space="preserve">S6.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8217,14 +8239,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方とは…このままではチームに影響が出ます</t>
+          <t xml:space="preserve">培ってきたものを後輩にお伝えしたいのです</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.polite.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8239,7 +8261,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.polite.earnest[1]</t>
+          <t xml:space="preserve">B1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8249,14 +8271,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体にご迷惑はかけたくないのですが…あの方とは…</t>
+          <t xml:space="preserve">申し訳ございません…一日も早く復帰いたします</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.polite.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8271,7 +8293,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.polite.earnest[1]</t>
+          <t xml:space="preserve">B2_fighter1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8281,14 +8303,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ブランド様のご期待に添えるよう、精一杯取り組みます</t>
+          <t xml:space="preserve">あの方とは…このままではチームに影響が出ます</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.polite.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8303,7 +8325,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.polite.earnest[1]</t>
+          <t xml:space="preserve">B2_fighter2.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8313,14 +8335,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大切なお仕事ですね。精一杯務めさせていただきます</t>
+          <t xml:space="preserve">団体にご迷惑はかけたくないのですが…あの方とは…</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.polite.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8335,7 +8357,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.polite.earnest[1]</t>
+          <t xml:space="preserve">B4_brand.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8345,14 +8367,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">来てくださった方全員に、心から感謝を伝えたいです</t>
+          <t xml:space="preserve">ブランド様のご期待に添えるよう、精一杯取り組みます</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.polite.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8367,7 +8389,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.polite.earnest[1]</t>
+          <t xml:space="preserve">B4_cm.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8377,14 +8399,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に沿えるよう、歩き方から練習いたします</t>
+          <t xml:space="preserve">大切なお仕事ですね。精一杯務めさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.polite.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8399,7 +8421,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.polite.earnest[1]</t>
+          <t xml:space="preserve">B4_fan.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8409,14 +8431,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">精一杯きれいに撮っていただけるよう頑張ります…</t>
+          <t xml:space="preserve">来てくださった方全員に、心から感謝を伝えたいです</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.polite.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8431,7 +8453,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.polite.earnest[1]</t>
+          <t xml:space="preserve">B4_fashion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8441,14 +8463,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">トーク番組は緊張しますが…誠実に対応いたします</t>
+          <t xml:space="preserve">ご期待に沿えるよう、歩き方から練習いたします</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.polite.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8463,7 +8485,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.polite.earnest[1]</t>
+          <t xml:space="preserve">B4_gravure.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8473,14 +8495,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私でよろしいんですか…？ 精一杯務めさせていただきます</t>
+          <t xml:space="preserve">精一杯きれいに撮っていただけるよう頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8490,29 +8512,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">B4_variety.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">地道に努力するのが取り柄です。信じていただけますか</t>
+          <t xml:space="preserve">トーク番組は緊張しますが…誠実に対応いたします</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8522,29 +8544,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">B4.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただき、ありがとうございます。精一杯頑張ります</t>
+          <t xml:space="preserve">私でよろしいんですか…？ 精一杯務めさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.earnest[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8554,12 +8576,12 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[2]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8569,14 +8591,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に応えられるよう、努力いたします</t>
+          <t xml:space="preserve">地道に努力するのが取り柄です。信じていただけますか</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8586,7 +8608,7 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
@@ -8601,14 +8623,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。期待にお応えいたします</t>
+          <t xml:space="preserve">お選びいただき、ありがとうございます。精一杯頑張ります</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8618,12 +8640,12 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8633,14 +8655,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日精進いたします。見ていてください</t>
+          <t xml:space="preserve">ご期待に応えられるよう、努力いたします</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8650,7 +8672,7 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
@@ -8665,14 +8687,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に応えられず、申し訳ありません</t>
+          <t xml:space="preserve">ありがとうございます。期待にお応えいたします</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.polite.earnest[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8682,12 +8704,12 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[2]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8697,14 +8719,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">必ず強くなって戻ってまいります</t>
+          <t xml:space="preserve">毎日精進いたします。見ていてください</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8714,12 +8736,12 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8729,14 +8751,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">済んだことにしたいのです。……できないだけで</t>
+          <t xml:space="preserve">ご期待に応えられず、申し訳ありません</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8746,12 +8768,12 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8761,14 +8783,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着は……ついておりません。私の中では、まだ</t>
+          <t xml:space="preserve">必ず強くなって戻ってまいります</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8783,7 +8805,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.polite.earnest[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8793,14 +8815,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">地道に努力するのが取り柄です。信じていただけますか</t>
+          <t xml:space="preserve">済んだことにしたいのです。……できないだけで</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8815,7 +8837,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.polite.earnest[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8825,14 +8847,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただき、ありがとうございます。精一杯頑張ります</t>
+          <t xml:space="preserve">決着は……ついておりません。私の中では、まだ</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.earnest[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8847,7 +8869,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.polite.earnest[2]</t>
+          <t xml:space="preserve">draftInterest.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8857,14 +8879,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に応えられるよう、努力いたします</t>
+          <t xml:space="preserve">地道に努力するのが取り柄です。信じていただけますか</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8879,7 +8901,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.polite.earnest[1]</t>
+          <t xml:space="preserve">draftJoin.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8889,14 +8911,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いただいた契約の重み、忘れずにやります</t>
+          <t xml:space="preserve">お選びいただき、ありがとうございます。精一杯頑張ります</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8911,7 +8933,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.polite.earnest[1]</t>
+          <t xml:space="preserve">draftJoin.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8921,14 +8943,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。期待にお応えいたします</t>
+          <t xml:space="preserve">ご期待に応えられるよう、努力いたします</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8943,7 +8965,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.polite.earnest[1]</t>
+          <t xml:space="preserve">faGreeting.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8953,14 +8975,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日精進いたします。見ていてください</t>
+          <t xml:space="preserve">いただいた契約の重み、忘れずにやります</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8975,7 +8997,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.polite.earnest[1]</t>
+          <t xml:space="preserve">faSigning.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8985,14 +9007,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は身体が素直に動きます。学んだ分だけ、身につきます</t>
+          <t xml:space="preserve">ありがとうございます。期待にお応えいたします</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -9007,7 +9029,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.polite.earnest[1]</t>
+          <t xml:space="preserve">faWelcome.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -9017,14 +9039,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">同じ量をこなしても、何も積み上がりません。情けないです</t>
+          <t xml:space="preserve">毎日精進いたします。見ていてください</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -9039,7 +9061,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.polite.earnest[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -9049,14 +9071,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">回数はこなせています。ただ、残る実感が薄くて</t>
+          <t xml:space="preserve">今日は身体が素直に動きます。学んだ分だけ、身につきます</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -9071,7 +9093,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.polite.earnest[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -9081,14 +9103,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に応えられず、申し訳ありません</t>
+          <t xml:space="preserve">同じ量をこなしても、何も積み上がりません。情けないです</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.earnest[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -9103,7 +9125,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.polite.earnest[2]</t>
+          <t xml:space="preserve">heatSelf.warm.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -9113,14 +9135,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">必ず強くなって戻ってまいります</t>
+          <t xml:space="preserve">回数はこなせています。ただ、残る実感が薄くて</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -9135,7 +9157,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.polite.earnest[1]</t>
+          <t xml:space="preserve">injury.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -9145,14 +9167,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくださった皆様に、申し訳ありません</t>
+          <t xml:space="preserve">ご期待に応えられず、申し訳ありません</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.earnest[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9167,7 +9189,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.polite.earnest[2]</t>
+          <t xml:space="preserve">injury.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9177,14 +9199,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここでの学び、決して忘れません</t>
+          <t xml:space="preserve">必ず強くなって戻ってまいります</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9199,7 +9221,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.polite.earnest[1]</t>
+          <t xml:space="preserve">release.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9209,14 +9231,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですが、精一杯務めさせていただきます</t>
+          <t xml:space="preserve">応援してくださった皆様に、申し訳ありません</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9231,7 +9253,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.polite.earnest[1]</t>
+          <t xml:space="preserve">release.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9241,14 +9263,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お声がけに恥じないよう、努めます</t>
+          <t xml:space="preserve">ここでの学び、決して忘れません</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9263,7 +9285,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.polite.earnest[1]</t>
+          <t xml:space="preserve">rentalGreeting.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9273,14 +9295,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力が足りませんでした。もっと精進いたします</t>
+          <t xml:space="preserve">短い間ですが、精一杯務めさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9295,7 +9317,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.polite.earnest[1]</t>
+          <t xml:space="preserve">scoutGreeting.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9305,14 +9327,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛できました。でも、まだまだ精進いたします</t>
+          <t xml:space="preserve">お声がけに恥じないよう、努めます</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9327,7 +9349,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.polite.earnest[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9337,14 +9359,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">努力が足りませんでした。一から出直します</t>
+          <t xml:space="preserve">実力が足りませんでした。もっと精進いたします</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9359,7 +9381,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.polite.earnest[1]</t>
+          <t xml:space="preserve">titleDefense.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9369,14 +9391,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねが報われました…本当に、ありがとうございます</t>
+          <t xml:space="preserve">防衛できました。でも、まだまだ精進いたします</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9386,12 +9408,12 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">titleLoss.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9401,14 +9423,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくださった皆様に、申し訳ありません</t>
+          <t xml:space="preserve">努力が足りませんでした。一から出直します</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.earnest[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9418,12 +9440,12 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[2]</t>
+          <t xml:space="preserve">titleWin.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9433,14 +9455,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここでの学び、決して忘れません</t>
+          <t xml:space="preserve">積み重ねが報われました…本当に、ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9450,7 +9472,7 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
@@ -9465,14 +9487,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですが、精一杯務めさせていただきます</t>
+          <t xml:space="preserve">応援してくださった皆様に、申し訳ありません</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9482,12 +9504,12 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9497,14 +9519,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力が足りませんでした。もっと精進いたします</t>
+          <t xml:space="preserve">ここでの学び、決して忘れません</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9514,7 +9536,7 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
@@ -9529,14 +9551,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛できました。でも、まだまだ精進いたします</t>
+          <t xml:space="preserve">短い間ですが、精一杯務めさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9546,7 +9568,7 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
@@ -9561,14 +9583,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">努力が足りませんでした。一から出直します</t>
+          <t xml:space="preserve">実力が足りませんでした。もっと精進いたします</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9578,7 +9600,7 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
@@ -9593,14 +9615,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねが報われました…本当に、ありがとうございます</t>
+          <t xml:space="preserve">防衛できました。でも、まだまだ精進いたします</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9610,29 +9632,29 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この関係…修復できる自信がありません…</t>
+          <t xml:space="preserve">努力が足りませんでした。一から出直します</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.polite[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9642,29 +9664,29 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.earnest.polite[2]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どこで間違えてしまったんでしょう…</t>
+          <t xml:space="preserve">積み重ねが報われました…本当に、ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9679,7 +9701,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.earnest.polite[1]</t>
+          <t xml:space="preserve">bond_39_down.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9689,14 +9711,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">関係を修復したいです…何とかしなければ</t>
+          <t xml:space="preserve">この関係…修復できる自信がありません…</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.polite[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9711,7 +9733,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.earnest.polite[1]</t>
+          <t xml:space="preserve">bond_39_down.earnest.polite[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9721,14 +9743,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おかげで練習にも身が入ります。感謝しています</t>
+          <t xml:space="preserve">どこで間違えてしまったんでしょう…</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9743,7 +9765,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.earnest.polite[1]</t>
+          <t xml:space="preserve">bond_59_down.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9753,14 +9775,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">共に歩めること、何よりの幸せです</t>
+          <t xml:space="preserve">関係を修復したいです…何とかしなければ</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9775,7 +9797,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.earnest.polite[1]</t>
+          <t xml:space="preserve">bond_60_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9785,14 +9807,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">関係も変わりました。前に進みましょう</t>
+          <t xml:space="preserve">おかげで練習にも身が入ります。感謝しています</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9807,7 +9829,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.earnest.polite[2]</t>
+          <t xml:space="preserve">bond_80_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9817,14 +9839,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの因縁から学んだことは多いです。次の目標を見つけなければ</t>
+          <t xml:space="preserve">共に歩めること、何よりの幸せです</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9839,7 +9861,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.earnest.polite[1]</t>
+          <t xml:space="preserve">rivalry_29_down.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9849,14 +9871,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝つために、もっと努力しなければなりません</t>
+          <t xml:space="preserve">関係も変わりました。前に進みましょう</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.polite[2]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9871,7 +9893,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.earnest.polite[1]</t>
+          <t xml:space="preserve">rivalry_29_down.earnest.polite[2]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9881,14 +9903,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">超えることが、私の覚悟です</t>
+          <t xml:space="preserve">あの因縁から学んだことは多いです。次の目標を見つけなければ</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9903,7 +9925,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.earnest.polite[1]</t>
+          <t xml:space="preserve">rivalry_30_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9913,14 +9935,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この切磋琢磨こそが、私の原動力です</t>
+          <t xml:space="preserve">勝つために、もっと努力しなければなりません</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9935,7 +9957,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.earnest.polite[1]</t>
+          <t xml:space="preserve">rivalry_50_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9945,14 +9967,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に添えるよう、精一杯頑張らせていただきます</t>
+          <t xml:space="preserve">超えることが、私の覚悟です</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9967,7 +9989,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.earnest.polite[1]</t>
+          <t xml:space="preserve">rivalry_70_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9977,14 +9999,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大変申し訳ありませんが…退団を検討させていただきます</t>
+          <t xml:space="preserve">この切磋琢磨こそが、私の原動力です</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9999,7 +10021,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.earnest.polite[1]</t>
+          <t xml:space="preserve">trust_above_75.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -10009,14 +10031,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">恐縮ですが…少し運営に対して不安があります…</t>
+          <t xml:space="preserve">ご期待に添えるよう、精一杯頑張らせていただきます</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.polite.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -10026,12 +10048,12 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.polite.earnest[1]</t>
+          <t xml:space="preserve">trust_below_20.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -10041,14 +10063,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不甲斐ない試合をしてしまいました。申し訳ございません</t>
+          <t xml:space="preserve">大変申し訳ありませんが…退団を検討させていただきます</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.polite.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -10058,12 +10080,12 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.polite.earnest[1]</t>
+          <t xml:space="preserve">trust_below_35.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -10073,14 +10095,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝利できました。引き続き精進します</t>
+          <t xml:space="preserve">恐縮ですが…少し運営に対して不安があります…</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.polite.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -10095,7 +10117,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.polite.earnest[1]</t>
+          <t xml:space="preserve">GL-01.loss.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -10105,14 +10127,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">基本を怠らず、しっかり取り組みます</t>
+          <t xml:space="preserve">不甲斐ない試合をしてしまいました。申し訳ございません</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.polite.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -10127,7 +10149,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.polite.earnest[1]</t>
+          <t xml:space="preserve">GL-01.win.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -10137,14 +10159,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ともに成長できることが嬉しいです</t>
+          <t xml:space="preserve">勝利できました。引き続き精進します</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.polite.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -10159,7 +10181,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.polite.earnest[1]</t>
+          <t xml:space="preserve">GL-02.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -10169,14 +10191,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">追いつくため、日々研鑽します</t>
+          <t xml:space="preserve">基本を怠らず、しっかり取り組みます</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.polite.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10191,7 +10213,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.polite.earnest[1]</t>
+          <t xml:space="preserve">GL-04.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10201,14 +10223,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">出場機会をいただけるよう、より一層努力いたします</t>
+          <t xml:space="preserve">ともに成長できることが嬉しいです</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.polite.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10223,7 +10245,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.polite.earnest[1]</t>
+          <t xml:space="preserve">GL-05.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10233,14 +10255,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体調管理を怠りました。しっかり立て直します</t>
+          <t xml:space="preserve">追いつくため、日々研鑽します</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.polite.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10255,7 +10277,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.polite.earnest[1]</t>
+          <t xml:space="preserve">GL-06.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10265,14 +10287,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不甲斐ない結果が続いています…何とか打開しなければ</t>
+          <t xml:space="preserve">出場機会をいただけるよう、より一層努力いたします</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.polite.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10287,7 +10309,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.polite.earnest[1]</t>
+          <t xml:space="preserve">GL-07.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10297,14 +10319,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">結果がついてきていますが、慢心せず精進します</t>
+          <t xml:space="preserve">体調管理を怠りました。しっかり立て直します</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.polite.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10319,7 +10341,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.polite.earnest[1]</t>
+          <t xml:space="preserve">GL-08.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10329,14 +10351,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">復帰に向けて、今できることを精一杯やります</t>
+          <t xml:space="preserve">不甲斐ない結果が続いています…何とか打開しなければ</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10346,12 +10368,12 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">GL-09.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10361,14 +10383,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">好調期間は終わりましたが、学びの多い日々でした</t>
+          <t xml:space="preserve">結果がついてきていますが、慢心せず精進します</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10378,29 +10400,29 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.earnest[1]</t>
+          <t xml:space="preserve">GL-10.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体はぼろぼろですが…最後まで、全力でお応えします</t>
+          <t xml:space="preserve">復帰に向けて、今できることを精一杯やります</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10410,29 +10432,29 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.earnest[2]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで繋いでくれた仲間のために、私が締めます。どんなに痛くても</t>
+          <t xml:space="preserve">好調期間は終わりましたが、学びの多い日々でした</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.earnest[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10447,7 +10469,7 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.earnest[3]</t>
+          <t xml:space="preserve">preFinal.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10457,14 +10479,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">痛みは、勝ってから数えます。今は、目の前の一戦に全部を</t>
+          <t xml:space="preserve">身体はぼろぼろですが…最後まで、全力でお応えします</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10479,7 +10501,7 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.earnest[1]</t>
+          <t xml:space="preserve">preFinal.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10489,14 +10511,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手がどなたでも、全力でお応えします。手を抜くのは失礼ですから</t>
+          <t xml:space="preserve">ここまで繋いでくれた仲間のために、私が締めます。どんなに痛くても</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.earnest[3]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10511,7 +10533,7 @@
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.earnest[2]</t>
+          <t xml:space="preserve">preFinal.polite.earnest[3]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10521,14 +10543,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦ずつ、丁寧に。託された役目、途中で放り出せません</t>
+          <t xml:space="preserve">痛みは、勝ってから数えます。今は、目の前の一戦に全部を</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.earnest[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10543,7 +10565,7 @@
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.earnest[3]</t>
+          <t xml:space="preserve">preMatch.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10553,14 +10575,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まずは目の前の一人に、心を込めて。それが私の役目ですから</t>
+          <t xml:space="preserve">相手がどなたでも、全力でお応えします。手を抜くのは失礼ですから</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10575,7 +10597,7 @@
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.earnest[1]</t>
+          <t xml:space="preserve">preMatch.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10585,14 +10607,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、止めました。…息は上がってますが、退きません。次の方も、全力でお相手します</t>
+          <t xml:space="preserve">一戦ずつ、丁寧に。託された役目、途中で放り出せません</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.earnest[3]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10607,7 +10629,7 @@
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.earnest[2]</t>
+          <t xml:space="preserve">preMatch.polite.earnest[3]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10617,14 +10639,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってます。仲間に繋ぐまで、このリングは渡しません。次、どうぞ</t>
+          <t xml:space="preserve">まずは目の前の一人に、心を込めて。それが私の役目ですから</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.earnest[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10639,7 +10661,7 @@
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.earnest[3]</t>
+          <t xml:space="preserve">survivor.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10649,14 +10671,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、お相手しました。…はぁ、まだ立てます。繋ぐまでは、退けませんから</t>
+          <t xml:space="preserve">一人、止めました。…息は上がってますが、退きません。次の方も、全力でお相手します</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10666,12 +10688,12 @@
       </c>
       <c r="C318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.earnest[1]</t>
+          <t xml:space="preserve">survivor.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10681,14 +10703,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">託された順番を、最後まで全うできました。仲間に感謝しています</t>
+          <t xml:space="preserve">まだ立ってます。仲間に繋ぐまで、このリングは渡しません。次、どうぞ</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.earnest[3]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10698,12 +10720,12 @@
       </c>
       <c r="C319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.earnest[2]</t>
+          <t xml:space="preserve">survivor.polite.earnest[3]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10713,14 +10735,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人でつないだ勝利を、団体に持ち帰れます。それが何より嬉しいです</t>
+          <t xml:space="preserve">一人、お相手しました。…はぁ、まだ立てます。繋ぐまでは、退けませんから</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10735,7 +10757,7 @@
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.polite.earnest[1]</t>
+          <t xml:space="preserve">champion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10745,14 +10767,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">評価していただいてありがとうございます。でも、次は団体ごと勝って応えたいです</t>
+          <t xml:space="preserve">託された順番を、最後まで全うできました。仲間に感謝しています</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10767,7 +10789,7 @@
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.polite.earnest[2]</t>
+          <t xml:space="preserve">champion.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10777,14 +10799,14 @@
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間のためにもっとやれたはず。その反省を、次に生かします</t>
+          <t xml:space="preserve">三人でつないだ勝利を、団体に持ち帰れます。それが何より嬉しいです</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10799,7 +10821,7 @@
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.polite.earnest[1]</t>
+          <t xml:space="preserve">defiant.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10809,14 +10831,14 @@
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で来てくださった皆さんに、全力で応えました。それだけは胸を張れます</t>
+          <t xml:space="preserve">評価していただいてありがとうございます。でも、次は団体ごと勝って応えたいです</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10831,7 +10853,7 @@
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.polite.earnest[2]</t>
+          <t xml:space="preserve">defiant.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10841,14 +10863,14 @@
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何度も限界を感じました。でも、託された役割を途中で降りるわけにはいきません</t>
+          <t xml:space="preserve">仲間のためにもっとやれたはず。その反省を、次に生かします</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.polite.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10858,12 +10880,12 @@
       </c>
       <c r="C324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.earnest[1]</t>
+          <t xml:space="preserve">gauntlet.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10873,14 +10895,14 @@
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝…させていただきました。皆様のおかげです…！</t>
+          <t xml:space="preserve">全力で来てくださった皆さんに、全力で応えました。それだけは胸を張れます</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.polite.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10890,12 +10912,12 @@
       </c>
       <c r="C325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.earnest[2]</t>
+          <t xml:space="preserve">gauntlet.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10905,14 +10927,14 @@
       </c>
       <c r="F325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この経験を糧に、さらに精進して参ります</t>
+          <t xml:space="preserve">何度も限界を感じました。でも、託された役割を途中で降りるわけにはいきません</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.polite.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10927,7 +10949,7 @@
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.polite.earnest[1]</t>
+          <t xml:space="preserve">champion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10937,14 +10959,14 @@
       </c>
       <c r="F326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">力不足で申し訳ございません…。もっと精進します</t>
+          <t xml:space="preserve">優勝…させていただきました。皆様のおかげです…！</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.polite.earnest[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10959,7 +10981,7 @@
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.polite.earnest[2]</t>
+          <t xml:space="preserve">champion.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10969,14 +10991,14 @@
       </c>
       <c r="F327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しゅうございます…。必ず強くなります</t>
+          <t xml:space="preserve">この経験を糧に、さらに精進して参ります</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.polite.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10991,7 +11013,7 @@
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.polite.earnest[1]</t>
+          <t xml:space="preserve">postLose.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -11001,14 +11023,14 @@
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝たせていただきました…。次も全力で臨みます</t>
+          <t xml:space="preserve">力不足で申し訳ございません…。もっと精進します</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.polite.earnest[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -11023,7 +11045,7 @@
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.polite.earnest[2]</t>
+          <t xml:space="preserve">postLose.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -11033,14 +11055,14 @@
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦一戦、大切に。次もよろしくお願いいたします</t>
+          <t xml:space="preserve">悔しゅうございます…。必ず強くなります</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.polite.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -11055,7 +11077,7 @@
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.polite.earnest[1]</t>
+          <t xml:space="preserve">postMatchWin.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -11065,14 +11087,14 @@
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">良い経験をさせていただきました。精進して参ります</t>
+          <t xml:space="preserve">勝たせていただきました…。次も全力で臨みます</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.polite.earnest[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -11087,7 +11109,7 @@
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.polite.earnest[2]</t>
+          <t xml:space="preserve">postMatchWin.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
@@ -11097,14 +11119,14 @@
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様のおかげで戦い抜けました。感謝いたします</t>
+          <t xml:space="preserve">一戦一戦、大切に。次もよろしくお願いいたします</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.polite.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -11119,7 +11141,7 @@
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.earnest[1]</t>
+          <t xml:space="preserve">postWin.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -11129,14 +11151,14 @@
       </c>
       <c r="F332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝の舞台…身に余る光栄です。全力でお応えいたします</t>
+          <t xml:space="preserve">良い経験をさせていただきました。精進して参ります</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.polite.earnest[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -11151,7 +11173,7 @@
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.earnest[2]</t>
+          <t xml:space="preserve">postWin.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
@@ -11161,14 +11183,14 @@
       </c>
       <c r="F333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この一戦に、全てをお捧げいたします</t>
+          <t xml:space="preserve">皆様のおかげで戦い抜けました。感謝いたします</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.polite.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -11183,7 +11205,7 @@
       </c>
       <c r="D334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.earnest[1]</t>
+          <t xml:space="preserve">preFinal.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E334" t="inlineStr" s="2">
@@ -11193,14 +11215,14 @@
       </c>
       <c r="F334" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">精一杯の試合を、お見せいたします</t>
+          <t xml:space="preserve">決勝の舞台…身に余る光栄です。全力でお応えいたします</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.polite.earnest[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -11215,7 +11237,7 @@
       </c>
       <c r="D335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.earnest[2]</t>
+          <t xml:space="preserve">preFinal.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
@@ -11225,14 +11247,14 @@
       </c>
       <c r="F335" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ひとつひとつ丁寧に…全力で参ります</t>
+          <t xml:space="preserve">この一戦に、全てをお捧げいたします</t>
         </is>
       </c>
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.polite.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -11247,7 +11269,7 @@
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.polite.earnest[1]</t>
+          <t xml:space="preserve">preMatch.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E336" t="inlineStr" s="2">
@@ -11257,14 +11279,14 @@
       </c>
       <c r="F336" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身に余る光栄です。一生懸命頑張ります</t>
+          <t xml:space="preserve">精一杯の試合を、お見せいたします</t>
         </is>
       </c>
     </row>
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.polite.earnest[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -11279,7 +11301,7 @@
       </c>
       <c r="D337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.polite.earnest[2]</t>
+          <t xml:space="preserve">preMatch.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E337" t="inlineStr" s="2">
@@ -11289,14 +11311,14 @@
       </c>
       <c r="F337" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お声がけいただき感謝いたします。精一杯務めます</t>
+          <t xml:space="preserve">ひとつひとつ丁寧に…全力で参ります</t>
         </is>
       </c>
     </row>
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -11306,12 +11328,12 @@
       </c>
       <c r="C338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">summon.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E338" t="inlineStr" s="2">
@@ -11321,14 +11343,14 @@
       </c>
       <c r="F338" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お互い全力で…よろしくお願いいたします</t>
+          <t xml:space="preserve">身に余る光栄です。一生懸命頑張ります</t>
         </is>
       </c>
     </row>
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -11338,12 +11360,12 @@
       </c>
       <c r="C339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">summon.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E339" t="inlineStr" s="2">
@@ -11353,14 +11375,14 @@
       </c>
       <c r="F339" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆さまのご声援のおかげです……本当に、ありがとうございます……！</t>
+          <t xml:space="preserve">お声がけいただき感謝いたします。精一杯務めます</t>
         </is>
       </c>
     </row>
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.polite.earnest[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -11370,7 +11392,7 @@
       </c>
       <c r="C340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D340" t="inlineStr" s="12">
@@ -11385,14 +11407,14 @@
       </c>
       <c r="F340" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">失礼ながら、対抗戦のお申し込みをさせていただきます</t>
+          <t xml:space="preserve">お互い全力で…よろしくお願いいたします</t>
         </is>
       </c>
     </row>
     <row r="341" ht="40" customHeight="1">
       <c r="A341" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.polite.earnest[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -11402,12 +11424,12 @@
       </c>
       <c r="C341" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D341" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[2]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E341" t="inlineStr" s="2">
@@ -11417,14 +11439,14 @@
       </c>
       <c r="F341" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力でお相手いたしますので、覚悟なさってください</t>
+          <t xml:space="preserve">皆さまのご声援のおかげです……本当に、ありがとうございます……！</t>
         </is>
       </c>
     </row>
     <row r="342" ht="40" customHeight="1">
       <c r="A342" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.polite.earnest[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -11434,7 +11456,7 @@
       </c>
       <c r="C342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D342" t="inlineStr" s="12">
@@ -11449,14 +11471,14 @@
       </c>
       <c r="F342" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残念ですが…いつかお受けいただけることを願っております</t>
+          <t xml:space="preserve">失礼ながら、対抗戦のお申し込みをさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="343" ht="40" customHeight="1">
       <c r="A343" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.polite.earnest[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -11466,7 +11488,7 @@
       </c>
       <c r="C343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D343" t="inlineStr" s="12">
@@ -11481,14 +11503,14 @@
       </c>
       <c r="F343" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">改めてお声がけいたします。その時はぜひ</t>
+          <t xml:space="preserve">全力でお相手いたしますので、覚悟なさってください</t>
         </is>
       </c>
     </row>
     <row r="344" ht="40" customHeight="1">
       <c r="A344" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.polite.earnest[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -11498,12 +11520,12 @@
       </c>
       <c r="C344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D344" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E344" t="inlineStr" s="2">
@@ -11513,14 +11535,14 @@
       </c>
       <c r="F344" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">完敗でした…。この悔しさを胸に、精進いたします</t>
+          <t xml:space="preserve">残念ですが…いつかお受けいただけることを願っております</t>
         </is>
       </c>
     </row>
     <row r="345" ht="40" customHeight="1">
       <c r="A345" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.polite.earnest[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -11530,12 +11552,12 @@
       </c>
       <c r="C345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D345" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.polite.earnest[2]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E345" t="inlineStr" s="2">
@@ -11545,14 +11567,14 @@
       </c>
       <c r="F345" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">申し訳ございません…。必ず成長してお返しいたします</t>
+          <t xml:space="preserve">改めてお声がけいたします。その時はぜひ</t>
         </is>
       </c>
     </row>
     <row r="346" ht="40" customHeight="1">
       <c r="A346" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.polite.earnest[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
@@ -11567,7 +11589,7 @@
       </c>
       <c r="D346" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.polite.earnest[1]</t>
+          <t xml:space="preserve">result_lose.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E346" t="inlineStr" s="2">
@@ -11577,14 +11599,14 @@
       </c>
       <c r="F346" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝たせていただきました。素晴らしい対抗戦に感謝いたします</t>
+          <t xml:space="preserve">完敗でした…。この悔しさを胸に、精進いたします</t>
         </is>
       </c>
     </row>
     <row r="347" ht="40" customHeight="1">
       <c r="A347" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.polite.earnest[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -11599,7 +11621,7 @@
       </c>
       <c r="D347" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.polite.earnest[2]</t>
+          <t xml:space="preserve">result_lose.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E347" t="inlineStr" s="2">
@@ -11609,14 +11631,14 @@
       </c>
       <c r="F347" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様のおかげで勝利できました。ありがとうございます</t>
+          <t xml:space="preserve">申し訳ございません…。必ず成長してお返しいたします</t>
         </is>
       </c>
     </row>
     <row r="348" ht="40" customHeight="1">
       <c r="A348" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -11626,12 +11648,12 @@
       </c>
       <c r="C348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D348" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">result_win.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E348" t="inlineStr" s="2">
@@ -11641,14 +11663,14 @@
       </c>
       <c r="F348" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の代表として勝利できましたこと…光栄でございます</t>
+          <t xml:space="preserve">勝たせていただきました。素晴らしい対抗戦に感謝いたします</t>
         </is>
       </c>
     </row>
     <row r="349" ht="40" customHeight="1">
       <c r="A349" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.polite.earnest[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -11658,12 +11680,12 @@
       </c>
       <c r="C349" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D349" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[2]</t>
+          <t xml:space="preserve">result_win.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E349" t="inlineStr" s="2">
@@ -11673,14 +11695,14 @@
       </c>
       <c r="F349" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の名に恥じない試合ができたのであれば…嬉しゅうございます</t>
+          <t xml:space="preserve">皆様のおかげで勝利できました。ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="350" ht="40" customHeight="1">
       <c r="A350" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.polite.earnest[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
@@ -11695,7 +11717,7 @@
       </c>
       <c r="D350" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[3]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E350" t="inlineStr" s="2">
@@ -11705,14 +11727,14 @@
       </c>
       <c r="F350" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の皆様のおかげで勝利できました。心より感謝申し上げます</t>
+          <t xml:space="preserve">団体の代表として勝利できましたこと…光栄でございます</t>
         </is>
       </c>
     </row>
     <row r="351" ht="40" customHeight="1">
       <c r="A351" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.polite.earnest[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
@@ -11722,29 +11744,29 @@
       </c>
       <c r="C351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D351" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F351" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねてきた全てが報われました…ありがとうございます</t>
+          <t xml:space="preserve">団体の名に恥じない試合ができたのであれば…嬉しゅうございます</t>
         </is>
       </c>
     </row>
     <row r="352" ht="40" customHeight="1">
       <c r="A352" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.earnest[3]</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -11754,59 +11776,123 @@
       </c>
       <c r="C352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D352" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[3]</t>
         </is>
       </c>
       <c r="E352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F352" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いただいた契約の重み、忘れずにやります</t>
+          <t xml:space="preserve">団体の皆様のおかげで勝利できました。心より感謝申し上げます</t>
         </is>
       </c>
     </row>
     <row r="353" ht="40" customHeight="1">
       <c r="A353" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.polite.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.polite.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">積み重ねてきた全てが報われました…ありがとうございます</t>
+        </is>
+      </c>
+    </row>
+    <row r="354" ht="40" customHeight="1">
+      <c r="A354" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.polite.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いただいた契約の重み、忘れずにやります</t>
+        </is>
+      </c>
+    </row>
+    <row r="355" ht="40" customHeight="1">
+      <c r="A355" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.polite.earnest[1]</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr" s="2">
+      <c r="B355" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr" s="12">
+      <c r="D355" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
-      <c r="E353" t="inlineStr" s="2">
+      <c r="E355" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F353" t="inlineStr" s="3">
+      <c r="F355" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">お声がけに恥じないよう、努めます</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H353"/>
+  <autoFilter ref="A1:H355"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/丁寧×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×真面目.xlsx
@@ -504,7 +504,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H355"/>
+  <dimension ref="A1:H362"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -4146,7 +4146,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.polite.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.polite.earnest[1]</t>
+          <t xml:space="preserve">decline_accept.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -4171,14 +4171,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。ご期待に沿えるよう、精一杯努めます。</t>
+          <t xml:space="preserve">承知しました。数字が下がった年をどう過ごすかで、次が決まるんだと思います。</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.polite.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.polite.earnest[1]</t>
+          <t xml:space="preserve">decline_hold.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4203,14 +4203,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとうございます。この額で精一杯、お応えいたします。</t>
+          <t xml:space="preserve">……それは、私の数字ではありません。お借りしたぶんとして、来年の身体で返させてください。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.polite.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.polite.earnest[1]</t>
+          <t xml:space="preserve">decline_open.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4235,14 +4235,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……残念ですが、承知いたしました。ですが、この判断はお忘れなきよう。</t>
+          <t xml:space="preserve">はい、伺います。……練習の量は落としていないつもりでした。足りないのは、そこじゃなかったんですね。</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.polite.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.polite.earnest[1]</t>
+          <t xml:space="preserve">decline_strict.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4267,14 +4267,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、お忙しいところ恐れ入ります。{tenure}契約について、ご相談させていただきたく…。{record}</t>
+          <t xml:space="preserve">……承知しました。査定は仕事ですから。ただ、あの上乗せまで戻されるとは思いませんでした。</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.polite.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.polite.earnest[1]</t>
+          <t xml:space="preserve">decline_voluntary_accept.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4299,14 +4299,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……承知いたしました。ですが、このままでは…いずれ考えざるを得ません。</t>
+          <t xml:space="preserve">そうしていただけて安心しました。身の丈の数字から、もう一度積み直します。</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.polite.earnest[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4331,14 +4331,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、長らくお世話になりました。ですが、もうここでは続けられません。</t>
+          <t xml:space="preserve">……お言葉に甘えます。据え置いてよかったと、来年の暮れに思っていただきます。</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.earnest[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.polite.earnest[2]</t>
+          <t xml:space="preserve">decline_voluntary_open.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4363,14 +4363,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">自分なりに、ずっと考えてまいりました。……退団させていただきます。</t>
+          <t xml:space="preserve">先に申し上げます。全盛期の数字を、いまの身体でもらい続けるのは筋が通りません。下げてください。</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.polite.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.polite.earnest[1]</t>
+          <t xml:space="preserve">raise_accept.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4395,14 +4395,14 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。{record}ここでの経験には心から感謝しております。ですが…新しい環境で挑戦させてください。</t>
+          <t xml:space="preserve">ありがとうございます。ご期待に沿えるよう、精一杯努めます。</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.polite.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.polite.earnest[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4427,14 +4427,14 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。{tenure}大変申し訳ないのですが…退団のご相談をさせてください。</t>
+          <t xml:space="preserve">……ありがとうございます。この額で精一杯、お応えいたします。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.polite.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.polite.earnest[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4459,14 +4459,14 @@
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……承知いたしました。{tenure_farewell}この団体での日々に、心から感謝いたします。{rivalry}</t>
+          <t xml:space="preserve">……残念ですが、承知いたしました。ですが、この判断はお忘れなきよう。</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.polite.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.polite.earnest[1]</t>
+          <t xml:space="preserve">raise_open.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4491,14 +4491,14 @@
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お心遣い、ありがとうございます。ですが…この決断は変わりません。申し訳ございません。</t>
+          <t xml:space="preserve">社長、お忙しいところ恐れ入ります。{tenure}契約について、ご相談させていただきたく…。{record}</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.polite.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.polite.earnest[1]</t>
+          <t xml:space="preserve">raise_refuse.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4523,370 +4523,370 @@
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……社長のお気持ち、しかと受け止めました。もう一度、全力を尽くさせてください。</t>
+          <t xml:space="preserve">……承知いたしました。ですが、このままでは…いずれ考えざるを得ません。</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.polite.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、長らくお世話になりました。ですが、もうここでは続けられません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.earnest[2]</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.polite.earnest[2]</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">自分なりに、ずっと考えてまいりました。……退団させていただきます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.polite.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.polite.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ありがとうございます。{record}ここでの経験には心から感謝しております。ですが…新しい環境で挑戦させてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.polite.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.polite.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長。{tenure}大変申し訳ないのですが…退団のご相談をさせてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.polite.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.polite.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……承知いたしました。{tenure_farewell}この団体での日々に、心から感謝いたします。{rivalry}</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.polite.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.polite.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お心遣い、ありがとうございます。ですが…この決断は変わりません。申し訳ございません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.polite.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.polite.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……社長のお気持ち、しかと受け止めました。もう一度、全力を尽くさせてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.polite.earnest[1]</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr" s="2">
+      <c r="B133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr" s="12">
+      <c r="D133" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.polite.earnest[1]</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr" s="2">
+      <c r="E133" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr" s="3">
+      <c r="F133" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">今の仲間への責任があります。
 その気持ちがある限り、ここを離れる選択はできません</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="40" customHeight="1">
-      <c r="A127" t="inlineStr" s="15">
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.polite.earnest[1]</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr" s="2">
+      <c r="B134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr" s="12">
+      <c r="D134" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.polite.earnest[1]</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr" s="2">
+      <c r="E134" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr" s="3">
+      <c r="F134" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">皆さんを置いて行くわけにはいきません。
 …申し訳ありません</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="40" customHeight="1">
-      <c r="A128" t="inlineStr" s="15">
+    <row r="135" ht="40" customHeight="1">
+      <c r="A135" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.start.polite.earnest[1]</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr" s="2">
+      <c r="B135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr" s="12">
+      <c r="D135" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">start.polite.earnest[1]</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr" s="2">
+      <c r="E135" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr" s="3">
+      <c r="F135" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">この団体を離れるのは簡単ではありません。
 …でも、お聞きするだけなら</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="40" customHeight="1">
-      <c r="A129" t="inlineStr" s="15">
+    <row r="136" ht="40" customHeight="1">
+      <c r="A136" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.success.polite.earnest[1]</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr" s="2">
+      <c r="B136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr" s="12">
+      <c r="D136" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">success.polite.earnest[1]</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr" s="2">
+      <c r="E136" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr" s="3">
+      <c r="F136" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">新しい仲間のために…全力を尽くします。
 よろしくお願いいたします</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="40" customHeight="1">
-      <c r="A130" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.polite.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.polite.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、お忙しいところ恐縮ですが、私たちのメンバーのこと、お気遣いいただけませんでしょうか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="40" customHeight="1">
-      <c r="A131" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.polite.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.polite.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、お忙しいところ恐縮ですが、次の興行のメインを私たちにお任せいただけませんでしょうか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="40" customHeight="1">
-      <c r="A132" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.polite.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.polite.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、不躾で申し訳ありませんが、私たちのメンバーの待遇を一度ご再考いただけませんでしょうか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="40" customHeight="1">
-      <c r="A133" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.polite.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.polite.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、お忙しいところ恐縮ですが、私たちの貢献にお言葉をいただけませんでしょうか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="40" customHeight="1">
-      <c r="A134" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.polite.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.polite.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、本当にありがとうございます。お言葉、大切にいたします。</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="40" customHeight="1">
-      <c r="A135" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.polite.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.polite.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…承知しました。お時間を取らせて、申し訳ありません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="40" customHeight="1">
-      <c r="A136" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.polite.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.polite.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、しっかり受け取ります。</t>
-        </is>
-      </c>
-    </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.polite.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4911,14 +4911,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、本当にありがとうございます。お預かりしたメイン、最後まで責任持って務めます。</t>
+          <t xml:space="preserve">社長、お忙しいところ恐縮ですが、私たちのメンバーのこと、お気遣いいただけませんでしょうか。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.polite.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4943,14 +4943,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。出過ぎたことを申しました。失礼いたしました。</t>
+          <t xml:space="preserve">社長、お忙しいところ恐縮ですが、次の興行のメインを私たちにお任せいただけませんでしょうか。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.polite.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4975,14 +4975,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、しっかり受け取ります。</t>
+          <t xml:space="preserve">社長、不躾で申し訳ありませんが、私たちのメンバーの待遇を一度ご再考いただけませんでしょうか。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.polite.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -5007,14 +5007,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、本当にありがとうございます。皆を代表してお礼申し上げます。</t>
+          <t xml:space="preserve">社長、お忙しいところ恐縮ですが、私たちの貢献にお言葉をいただけませんでしょうか。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -5039,14 +5039,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。図々しいお願いをしてしまい、申し訳ありません。</t>
+          <t xml:space="preserve">社長、本当にありがとうございます。お言葉、大切にいたします。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -5071,14 +5071,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。お金以外で気にかけていただけるなんて、ありがたいです。</t>
+          <t xml:space="preserve">…承知しました。お時間を取らせて、申し訳ありません。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -5103,14 +5103,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、本当にありがとうございます。お言葉、大切にいたします。</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、しっかり受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -5135,14 +5135,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。図々しいお願いをしてしまい、申し訳ありません。</t>
+          <t xml:space="preserve">社長、本当にありがとうございます。お預かりしたメイン、最後まで責任持って務めます。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -5167,14 +5167,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。形は違っても、お気持ちは伝わりました。</t>
+          <t xml:space="preserve">…承知しました。出過ぎたことを申しました。失礼いたしました。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -5199,14 +5199,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。輪の外にいる子のお気持ち、見えていませんでした。</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、しっかり受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5231,14 +5231,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。寛容に甘え過ぎないように気をつけます。</t>
+          <t xml:space="preserve">社長、本当にありがとうございます。皆を代表してお礼申し上げます。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5263,14 +5263,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません、配慮が至りませんでした。</t>
+          <t xml:space="preserve">…承知しました。図々しいお願いをしてしまい、申し訳ありません。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5295,14 +5295,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。お金以外で気にかけていただけるなんて、ありがたいです。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5327,14 +5327,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。リングの外にまで持ち込むのは、行きすぎでした。</t>
+          <t xml:space="preserve">社長、本当にありがとうございます。お言葉、大切にいたします。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5359,14 +5359,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。役柄の責任、まっとうします。</t>
+          <t xml:space="preserve">…承知しました。図々しいお願いをしてしまい、申し訳ありません。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5391,14 +5391,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。立場ある身で、本当にお恥ずかしいです。</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。形は違っても、お気持ちは伝わりました。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5423,14 +5423,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。本当に、お見逃しに甘えないようにします。</t>
+          <t xml:space="preserve">…申し訳ありません。輪の外にいる子のお気持ち、見えていませんでした。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5455,14 +5455,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。私の不在を、社長に拾っていただいて。</t>
+          <t xml:space="preserve">…ありがとうございます。寛容に甘え過ぎないように気をつけます。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5487,14 +5487,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。ご厚意に、しっかり甘えさせていただきます。</t>
+          <t xml:space="preserve">…申し訳ありません、配慮が至りませんでした。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5519,14 +5519,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご心配いただきありがとうございます。まだ立てます。</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5551,14 +5551,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。チームで支えていただけるなら、持ち直せます。</t>
+          <t xml:space="preserve">…申し訳ありません。リングの外にまで持ち込むのは、行きすぎでした。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5583,14 +5583,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。私が見ていれば、防げたはずです。</t>
+          <t xml:space="preserve">…ありがとうございます。役柄の責任、まっとうします。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5615,14 +5615,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。穏便に収めるよう努めます。</t>
+          <t xml:space="preserve">…申し訳ありません。立場ある身で、本当にお恥ずかしいです。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5647,14 +5647,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。私の力不足を、社長に補っていただいて。</t>
+          <t xml:space="preserve">…ありがとうございます。本当に、お見逃しに甘えないようにします。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5679,14 +5679,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。私の振る舞いが至りませんでした。</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。私の不在を、社長に拾っていただいて。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5711,14 +5711,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（唇を結び、深く頷いた）</t>
+          <t xml:space="preserve">…ありがとうございます。ご厚意に、しっかり甘えさせていただきます。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5743,14 +5743,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、しっかり受け取ります。</t>
+          <t xml:space="preserve">…ご心配いただきありがとうございます。まだ立てます。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5775,14 +5775,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。私の判断が、行きすぎていました。</t>
+          <t xml:space="preserve">…ありがとうございます。チームで支えていただけるなら、持ち直せます。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5807,14 +5807,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。責任は私が持たせていただきます。</t>
+          <t xml:space="preserve">…申し訳ありません。私が見ていれば、防げたはずです。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5839,14 +5839,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。私が見落としていた負担を、社長に拾っていただいて。</t>
+          <t xml:space="preserve">…ありがとうございます。穏便に収めるよう努めます。</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.earnest.attack.polite</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.attack.polite</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5871,14 +5871,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">けじめを、つけさせてください</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。私の力不足を、社長に補っていただいて。</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.earnest.defend.polite</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.defend.polite</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5903,29 +5903,29 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げるつもりはありません</t>
+          <t xml:space="preserve">…申し訳ありません。私の振る舞いが至りませんでした。</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5935,29 +5935,29 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">申し上げにくいのですが……今のままでは、私たち、息が詰まります。</t>
+          <t xml:space="preserve">（唇を結び、深く頷いた）</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5967,29 +5967,29 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">きっかけがあれば、と思っておりました。今日がその日かもしれません。</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、しっかり受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5999,29 +5999,29 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">言葉ではもう届きません。リングで、決着をつけましょう。</t>
+          <t xml:space="preserve">…申し訳ありません。私の判断が、行きすぎていました。</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.polite.earnest.hp_high[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest.hp_high[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -6031,29 +6031,29 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……お見事でした。次は、こうはいきません</t>
+          <t xml:space="preserve">…ありがとうございます。責任は私が持たせていただきます。</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.polite.earnest.high[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest.high[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -6063,29 +6063,29 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">失礼いたしました。今日は、私が勝たせてもらいます</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。私が見落としていた負担を、社長に拾っていただいて。</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.polite.earnest.high[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.earnest.attack.polite</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest.high[1]</t>
+          <t xml:space="preserve">earnest.attack.polite</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -6095,29 +6095,29 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日という日のために、私、ここまで来たんです</t>
+          <t xml:space="preserve">けじめを、つけさせてください</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.polite.earnest.high[2]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.earnest.defend.polite</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest.high[2]</t>
+          <t xml:space="preserve">earnest.defend.polite</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -6127,14 +6127,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">御免なさい。今日は手加減できません</t>
+          <t xml:space="preserve">逃げるつもりはありません</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.polite.earnest.high[1]</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -6144,12 +6144,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest.high[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -6159,14 +6159,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご丁寧に、ありがとうございます。お受けいたします</t>
+          <t xml:space="preserve">申し上げにくいのですが……今のままでは、私たち、息が詰まります。</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.polite.earnest.high[1]</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -6176,12 +6176,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest.high[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -6191,14 +6191,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今夜の興行で、すべてを決めさせてください</t>
+          <t xml:space="preserve">きっかけがあれば、と思っておりました。今日がその日かもしれません。</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.polite.earnest.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6208,12 +6208,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest.high[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6223,14 +6223,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お受けいたします。今夜、決着を</t>
+          <t xml:space="preserve">言葉ではもう届きません。リングで、決着をつけましょう。</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.polite.earnest.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.polite.earnest.hp_high[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest.high[1]</t>
+          <t xml:space="preserve">polite.earnest.hp_high[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6255,14 +6255,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">御免なさい。今日だけは、譲れません</t>
+          <t xml:space="preserve">……お見事でした。次は、こうはいきません</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES.polite.earnest.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.polite.earnest.high[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
@@ -6287,238 +6287,238 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">光栄です。全力で、お相手します</t>
+          <t xml:space="preserve">失礼いたしました。今日は、私が勝たせてもらいます</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.polite.earnest.high[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest.high[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習が実を結びました…！ まだ上を目指します</t>
+          <t xml:space="preserve">今日という日のために、私、ここまで来たんです</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.polite.earnest.high[2]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest.high[2]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…あの練習が、今、実を結ぼうとしている——）</t>
+          <t xml:space="preserve">御免なさい。今日は手加減できません</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.polite.earnest[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.polite.earnest.high[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest.high[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は身体が素直に動きます。学んだ分だけ、身につきます</t>
+          <t xml:space="preserve">ご丁寧に、ありがとうございます。お受けいたします</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.polite.earnest[1]</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.polite.earnest.high[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest.high[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">同じ量をこなしても、何も積み上がりません。情けないです</t>
+          <t xml:space="preserve">今夜の興行で、すべてを決めさせてください</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.polite.earnest[1]</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.polite.earnest.high[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest.high[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">回数はこなせています。ただ、残る実感が薄くて</t>
+          <t xml:space="preserve">お受けいたします。今夜、決着を</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.polite.earnest[1]</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.polite.earnest.high[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest.high[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">限界に達しましたが…この道のりに誇りを持っています</t>
+          <t xml:space="preserve">御免なさい。今日だけは、譲れません</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.polite.earnest[1]</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES.polite.earnest.high[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest.high[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来ました。でもまだ、上を目指します</t>
+          <t xml:space="preserve">光栄です。全力で、お相手します</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.polite.earnest[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6543,14 +6543,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">日々の積み重ねが実を結んできました</t>
+          <t xml:space="preserve">練習が実を結びました…！ まだ上を目指します</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.polite.earnest[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6575,14 +6575,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全てを懸けてきた日々が…報われました</t>
+          <t xml:space="preserve">（…あの練習が、今、実を結ぼうとしている——）</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.polite.earnest[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.polite.earnest[1]</t>
+          <t xml:space="preserve">fresh.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6607,14 +6607,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援を力に変えて、もっと頑張ります</t>
+          <t xml:space="preserve">今日は身体が素直に動きます。学んだ分だけ、身につきます</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.polite.earnest[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.polite.earnest[1]</t>
+          <t xml:space="preserve">heavy.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6639,14 +6639,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この声援を力に、必ず期待に応えてみせます</t>
+          <t xml:space="preserve">同じ量をこなしても、何も積み上がりません。情けないです</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">warm.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6671,14 +6671,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日道場に来るのが…こんなに辛いとは思いませんでした</t>
+          <t xml:space="preserve">回数はこなせています。ただ、残る実感が薄くて</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">cap_reached.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6703,14 +6703,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">闘う気持ちを忘れていました…でも、もう迷いません</t>
+          <t xml:space="preserve">限界に達しましたが…この道のりに誇りを持っています</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">ovr_elite.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6735,14 +6735,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご迷惑をおかけしました…必ず、倍にしてお返しします</t>
+          <t xml:space="preserve">ここまで来ました。でもまだ、上を目指します</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.polite.earnest[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.polite.earnest[1]</t>
+          <t xml:space="preserve">ovr_growth.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6767,14 +6767,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの試合から…自分の何が足りないのか、ずっと考えています</t>
+          <t xml:space="preserve">日々の積み重ねが実を結んできました</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.polite.earnest[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.polite.earnest[1]</t>
+          <t xml:space="preserve">ovr_legend.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6799,14 +6799,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">復帰できたのですが…まだ全然、足りていません</t>
+          <t xml:space="preserve">全てを懸けてきた日々が…報われました</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.polite.earnest[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.polite.earnest[1]</t>
+          <t xml:space="preserve">pop_growth.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6831,14 +6831,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">復帰できました…でも体が覚えているんです、あの痛みを</t>
+          <t xml:space="preserve">応援を力に変えて、もっと頑張ります</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.polite.earnest[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.polite.earnest[1]</t>
+          <t xml:space="preserve">pop_star.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6863,14 +6863,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我は治りました。でも離れていた時間が…重いです</t>
+          <t xml:space="preserve">この声援を力に、必ず期待に応えてみせます</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.polite.earnest[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6880,29 +6880,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間を信じ、仲間に応える。その思いで戦い抜きました。</t>
+          <t xml:space="preserve">毎日道場に来るのが…こんなに辛いとは思いませんでした</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.polite.earnest[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6912,29 +6912,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの試合は一生の宝物です。対戦相手の方に、心から感謝しています</t>
+          <t xml:space="preserve">闘う気持ちを忘れていました…でも、もう迷いません</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.polite.earnest[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6944,29 +6944,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">王者としての責任を全うします。毎試合、最高の試合をお届けします</t>
+          <t xml:space="preserve">ご迷惑をおかけしました…必ず、倍にしてお返しします</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.polite.earnest[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6976,29 +6976,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.polite.earnest[1]</t>
+          <t xml:space="preserve">defeat.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の皆さん。リングに真実があります。どうか、立ち続けてください</t>
+          <t xml:space="preserve">あの試合から…自分の何が足りないのか、ずっと考えています</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.polite.earnest[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -7008,29 +7008,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.polite.earnest[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">日々の積み重ねが実を結びました。来年も変わらず精進します</t>
+          <t xml:space="preserve">復帰できたのですが…まだ全然、足りていません</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.polite.earnest[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -7040,29 +7040,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.polite.earnest[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日の積み重ねが報われました。指導してくださった皆さん、ありがとうございます</t>
+          <t xml:space="preserve">復帰できました…でも体が覚えているんです、あの痛みを</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.polite.earnest[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -7072,29 +7072,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.polite.earnest[1]</t>
+          <t xml:space="preserve">penalty_end.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">互いを信じ続けたことが、この結果につながりました。</t>
+          <t xml:space="preserve">怪我は治りました。でも離れていた時間が…重いです</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">autumnWarChampion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -7119,14 +7119,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドーム大会という大役、謹んでお受けいたします</t>
+          <t xml:space="preserve">仲間を信じ、仲間に応える。その思いで戦い抜きました。</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.earnest[2]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[2]</t>
+          <t xml:space="preserve">bestMatch.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -7151,14 +7151,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後の最後まで、手を抜きません</t>
+          <t xml:space="preserve">あの試合は一生の宝物です。対戦相手の方に、心から感謝しています</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.earnest[3]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -7168,12 +7168,12 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[3]</t>
+          <t xml:space="preserve">champion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -7183,14 +7183,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この恩に、必ず応えてみせます</t>
+          <t xml:space="preserve">王者としての責任を全うします。毎試合、最高の試合をお届けします</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7200,12 +7200,12 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">hallOfFame.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7215,14 +7215,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員のお客様、心より感謝申し上げます</t>
+          <t xml:space="preserve">後輩の皆さん。リングに真実があります。どうか、立ち続けてください</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.earnest[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[2]</t>
+          <t xml:space="preserve">mvp.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7247,14 +7247,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力を尽くした甲斐がありました</t>
+          <t xml:space="preserve">日々の積み重ねが実を結びました。来年も変わらず精進します</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.earnest[3]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[3]</t>
+          <t xml:space="preserve">rookie.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7279,14 +7279,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次も、必ず期待に応えます</t>
+          <t xml:space="preserve">毎日の積み重ねが報われました。指導してくださった皆さん、ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.polite.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7296,29 +7296,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.polite.earnest[1]</t>
+          <t xml:space="preserve">springTagChampion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねが大切だと信じています。コツコツ参ります</t>
+          <t xml:space="preserve">互いを信じ続けたことが、この結果につながりました。</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.polite.earnest[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7328,29 +7328,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒に練習していると、自分も頑張ろうと思えます</t>
+          <t xml:space="preserve">ドーム大会という大役、謹んでお受けいたします</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.polite.earnest[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7360,29 +7360,29 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">申し訳ありません…少し休ませていただければ、必ず戻ります</t>
+          <t xml:space="preserve">最後の最後まで、手を抜きません</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.polite.earnest[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.earnest[3]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7392,29 +7392,29 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[3]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様の応援が、何よりの原動力です</t>
+          <t xml:space="preserve">この恩に、必ず応えてみせます</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.polite.earnest[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7424,29 +7424,29 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">裏切るつもりはございません。ただ……</t>
+          <t xml:space="preserve">満員のお客様、心より感謝申し上げます</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.polite.earnest[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7456,29 +7456,29 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習を重ねても、何か足りない気がいたしまして…</t>
+          <t xml:space="preserve">全力を尽くした甲斐がありました</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.polite.earnest[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.earnest[3]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7488,29 +7488,29 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[3]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…何か気に障ることをしたのでしょうか</t>
+          <t xml:space="preserve">次も、必ず期待に応えます</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.polite.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7520,12 +7520,12 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.polite.earnest[1]</t>
+          <t xml:space="preserve">N1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7535,14 +7535,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name2}さんとご一緒できて幸せでした。…お元気で</t>
+          <t xml:space="preserve">積み重ねが大切だと信じています。コツコツ参ります</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.polite.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7552,29 +7552,29 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.polite.earnest[1]</t>
+          <t xml:space="preserve">N2.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。必ず結果でお返しいたします</t>
+          <t xml:space="preserve">一緒に練習していると、自分も頑張ろうと思えます</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.polite.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7584,29 +7584,29 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.polite.earnest[1]</t>
+          <t xml:space="preserve">N3.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で取り組ませていただきます。レベルアップしてみせます</t>
+          <t xml:space="preserve">申し訳ありません…少し休ませていただければ、必ず戻ります</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.polite.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7616,29 +7616,29 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.polite.earnest[1]</t>
+          <t xml:space="preserve">N4.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと見守ってくださったんですね…必ずお報いいたします</t>
+          <t xml:space="preserve">皆様の応援が、何よりの原動力です</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.polite.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7648,29 +7648,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.polite.earnest[1]</t>
+          <t xml:space="preserve">N5_low.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お言葉、ありがとうございます。もう一度頑張ります</t>
+          <t xml:space="preserve">裏切るつもりはございません。ただ……</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.polite.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7680,29 +7680,29 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.polite.earnest[1]</t>
+          <t xml:space="preserve">N5_warning.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私の至らなさです。申し訳ありませんでした</t>
+          <t xml:space="preserve">練習を重ねても、何か足りない気がいたしまして…</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.polite.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7712,29 +7712,29 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.polite.earnest[1]</t>
+          <t xml:space="preserve">R2.voice.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">緊張いたしますが…精一杯務めます</t>
+          <t xml:space="preserve">…何か気に障ることをしたのでしょうか</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.polite.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7744,29 +7744,29 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.polite.earnest[1]</t>
+          <t xml:space="preserve">R3.modal.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様、お疲れ様でした。明日からまた頑張りましょう</t>
+          <t xml:space="preserve">{name2}さんとご一緒できて幸せでした。…お元気で</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.polite.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.polite.earnest[1]</t>
+          <t xml:space="preserve">bonus.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7791,14 +7791,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習が気になりますが…お気遣いありがとうございます</t>
+          <t xml:space="preserve">ありがとうございます。必ず結果でお返しいたします</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.polite.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.polite.earnest[1]</t>
+          <t xml:space="preserve">camp.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7823,14 +7823,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご厚意に甘えます。必ず復帰してお返しいたします</t>
+          <t xml:space="preserve">全力で取り組ませていただきます。レベルアップしてみせます</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.polite.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.polite.earnest[1]</t>
+          <t xml:space="preserve">encourage_high_trust.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7855,14 +7855,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな機会をいただけて…全力でお応えいたします</t>
+          <t xml:space="preserve">ずっと見守ってくださったんですね…必ずお報いいたします</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.polite.earnest[1]</t>
+          <t xml:space="preserve">encourage.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7887,14 +7887,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">緊張いたしますが…精一杯務めさせていただきます</t>
+          <t xml:space="preserve">お言葉、ありがとうございます。もう一度頑張ります</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.polite.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.polite.earnest[1]</t>
+          <t xml:space="preserve">faction_decree.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7919,14 +7919,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こちらに義理がございますので…ただ、ご報告だけは</t>
+          <t xml:space="preserve">私の至らなさです。申し訳ありませんでした</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.polite.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.polite.earnest[1]</t>
+          <t xml:space="preserve">media.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7951,14 +7951,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大変申し訳ございません…今日はどうしても…</t>
+          <t xml:space="preserve">緊張いたしますが…精一杯務めます</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.polite.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7968,12 +7968,12 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.polite.earnest[1]</t>
+          <t xml:space="preserve">party.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7983,14 +7983,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「私、このままでいいんでしょうか…」と後輩に弱音をこぼしている）</t>
+          <t xml:space="preserve">皆様、お疲れ様でした。明日からまた頑張りましょう</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.polite.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -8000,12 +8000,12 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.polite.earnest[1]</t>
+          <t xml:space="preserve">refresh_leave.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -8015,14 +8015,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「私は本当にここで必要とされているんでしょうか」と率直な投稿）</t>
+          <t xml:space="preserve">練習が気になりますが…お気遣いありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.polite.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.polite.earnest[1]</t>
+          <t xml:space="preserve">special_treatment.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -8047,14 +8047,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと準備して参りました。チャンスをいただけませんか</t>
+          <t xml:space="preserve">…ご厚意に甘えます。必ず復帰してお返しいたします</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.polite.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.polite.earnest[1]</t>
+          <t xml:space="preserve">trainer.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -8079,14 +8079,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方との試合を組んでいただけないでしょうか</t>
+          <t xml:space="preserve">こんな機会をいただけて…全力でお応えいたします</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.polite.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.polite.earnest[1]</t>
+          <t xml:space="preserve">E1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -8111,14 +8111,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご迷惑をおかけしまして申し訳ございません…少しお休みをいただけますか</t>
+          <t xml:space="preserve">緊張いたしますが…精一杯務めさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.polite.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -8133,7 +8133,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.polite.earnest[1]</t>
+          <t xml:space="preserve">E6.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -8143,14 +8143,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと我慢して参りましたが…このままでは限界です</t>
+          <t xml:space="preserve">こちらに義理がございますので…ただ、ご報告だけは</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.polite.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.polite.earnest[1]</t>
+          <t xml:space="preserve">S_boycott.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -8175,14 +8175,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（何か申し上げかけて、深く頭を下げるだけだった）</t>
+          <t xml:space="preserve">大変申し訳ございません…今日はどうしても…</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.polite.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.polite.earnest[1]</t>
+          <t xml:space="preserve">S_grumble.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8207,14 +8207,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと強くなりたいのです。特訓をお許しいただけますか</t>
+          <t xml:space="preserve">（「私、このままでいいんでしょうか…」と後輩に弱音をこぼしている）</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.polite.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.polite.earnest[1]</t>
+          <t xml:space="preserve">S_sns.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8239,14 +8239,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">培ってきたものを後輩にお伝えしたいのです</t>
+          <t xml:space="preserve">（SNSに「私は本当にここで必要とされているんでしょうか」と率直な投稿）</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.polite.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.polite.earnest[1]</t>
+          <t xml:space="preserve">S1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8271,14 +8271,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">申し訳ございません…一日も早く復帰いたします</t>
+          <t xml:space="preserve">ずっと準備して参りました。チャンスをいただけませんか</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.polite.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.polite.earnest[1]</t>
+          <t xml:space="preserve">S2.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8303,14 +8303,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方とは…このままではチームに影響が出ます</t>
+          <t xml:space="preserve">あの方との試合を組んでいただけないでしょうか</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.polite.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8320,12 +8320,12 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.polite.earnest[1]</t>
+          <t xml:space="preserve">S3.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8335,14 +8335,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体にご迷惑はかけたくないのですが…あの方とは…</t>
+          <t xml:space="preserve">ご迷惑をおかけしまして申し訳ございません…少しお休みをいただけますか</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.polite.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.polite.earnest[1]</t>
+          <t xml:space="preserve">S4_direct.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8367,14 +8367,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ブランド様のご期待に添えるよう、精一杯取り組みます</t>
+          <t xml:space="preserve">ずっと我慢して参りましたが…このままでは限界です</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.polite.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8384,12 +8384,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.polite.earnest[1]</t>
+          <t xml:space="preserve">S4_silent.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8399,14 +8399,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大切なお仕事ですね。精一杯務めさせていただきます</t>
+          <t xml:space="preserve">…………（何か申し上げかけて、深く頭を下げるだけだった）</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.polite.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8416,12 +8416,12 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.polite.earnest[1]</t>
+          <t xml:space="preserve">S5.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8431,14 +8431,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">来てくださった方全員に、心から感謝を伝えたいです</t>
+          <t xml:space="preserve">もっと強くなりたいのです。特訓をお許しいただけますか</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.polite.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.polite.earnest[1]</t>
+          <t xml:space="preserve">S6.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8463,14 +8463,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に沿えるよう、歩き方から練習いたします</t>
+          <t xml:space="preserve">培ってきたものを後輩にお伝えしたいのです</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.polite.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.polite.earnest[1]</t>
+          <t xml:space="preserve">B1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8495,14 +8495,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">精一杯きれいに撮っていただけるよう頑張ります…</t>
+          <t xml:space="preserve">申し訳ございません…一日も早く復帰いたします</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.polite.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.polite.earnest[1]</t>
+          <t xml:space="preserve">B2_fighter1.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8527,14 +8527,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">トーク番組は緊張しますが…誠実に対応いたします</t>
+          <t xml:space="preserve">あの方とは…このままではチームに影響が出ます</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.polite.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.polite.earnest[1]</t>
+          <t xml:space="preserve">B2_fighter2.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8559,14 +8559,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私でよろしいんですか…？ 精一杯務めさせていただきます</t>
+          <t xml:space="preserve">団体にご迷惑はかけたくないのですが…あの方とは…</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8576,29 +8576,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">B4_brand.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">地道に努力するのが取り柄です。信じていただけますか</t>
+          <t xml:space="preserve">ブランド様のご期待に添えるよう、精一杯取り組みます</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8608,29 +8608,29 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">B4_cm.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただき、ありがとうございます。精一杯頑張ります</t>
+          <t xml:space="preserve">大切なお仕事ですね。精一杯務めさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.earnest[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8640,29 +8640,29 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[2]</t>
+          <t xml:space="preserve">B4_fan.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に応えられるよう、努力いたします</t>
+          <t xml:space="preserve">来てくださった方全員に、心から感謝を伝えたいです</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8672,29 +8672,29 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">B4_fashion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。期待にお応えいたします</t>
+          <t xml:space="preserve">ご期待に沿えるよう、歩き方から練習いたします</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8704,29 +8704,29 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">B4_gravure.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日精進いたします。見ていてください</t>
+          <t xml:space="preserve">精一杯きれいに撮っていただけるよう頑張ります…</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8736,29 +8736,29 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">B4_variety.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に応えられず、申し訳ありません</t>
+          <t xml:space="preserve">トーク番組は緊張しますが…誠実に対応いたします</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.polite.earnest[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8768,29 +8768,29 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[2]</t>
+          <t xml:space="preserve">B4.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">必ず強くなって戻ってまいります</t>
+          <t xml:space="preserve">私でよろしいんですか…？ 精一杯務めさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8815,14 +8815,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">済んだことにしたいのです。……できないだけで</t>
+          <t xml:space="preserve">地道に努力するのが取り柄です。信じていただけますか</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8847,14 +8847,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着は……ついておりません。私の中では、まだ</t>
+          <t xml:space="preserve">お選びいただき、ありがとうございます。精一杯頑張ります</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8864,12 +8864,12 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8879,14 +8879,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">地道に努力するのが取り柄です。信じていただけますか</t>
+          <t xml:space="preserve">ご期待に応えられるよう、努力いたします</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8911,14 +8911,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お選びいただき、ありがとうございます。精一杯頑張ります</t>
+          <t xml:space="preserve">ありがとうございます。期待にお応えいたします</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.earnest[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8928,12 +8928,12 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.polite.earnest[2]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8943,14 +8943,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に応えられるよう、努力いたします</t>
+          <t xml:space="preserve">毎日精進いたします。見ていてください</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8975,14 +8975,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いただいた契約の重み、忘れずにやります</t>
+          <t xml:space="preserve">ご期待に応えられず、申し訳ありません</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -9007,14 +9007,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。期待にお応えいたします</t>
+          <t xml:space="preserve">必ず強くなって戻ってまいります</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.polite.earnest[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -9039,14 +9039,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日精進いたします。見ていてください</t>
+          <t xml:space="preserve">済んだことにしたいのです。……できないだけで</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.polite.earnest[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -9071,14 +9071,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は身体が素直に動きます。学んだ分だけ、身につきます</t>
+          <t xml:space="preserve">決着は……ついておりません。私の中では、まだ</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.polite.earnest[1]</t>
+          <t xml:space="preserve">draftInterest.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -9103,14 +9103,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">同じ量をこなしても、何も積み上がりません。情けないです</t>
+          <t xml:space="preserve">地道に努力するのが取り柄です。信じていただけますか</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.polite.earnest[1]</t>
+          <t xml:space="preserve">draftJoin.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -9135,14 +9135,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">回数はこなせています。ただ、残る実感が薄くて</t>
+          <t xml:space="preserve">お選びいただき、ありがとうございます。精一杯頑張ります</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.polite.earnest[1]</t>
+          <t xml:space="preserve">draftJoin.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -9167,14 +9167,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に応えられず、申し訳ありません</t>
+          <t xml:space="preserve">ご期待に応えられるよう、努力いたします</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.earnest[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.polite.earnest[2]</t>
+          <t xml:space="preserve">faGreeting.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9199,14 +9199,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">必ず強くなって戻ってまいります</t>
+          <t xml:space="preserve">いただいた契約の重み、忘れずにやります</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.polite.earnest[1]</t>
+          <t xml:space="preserve">faSigning.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9231,14 +9231,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくださった皆様に、申し訳ありません</t>
+          <t xml:space="preserve">ありがとうございます。期待にお応えいたします</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.earnest[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.polite.earnest[2]</t>
+          <t xml:space="preserve">faWelcome.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9263,14 +9263,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここでの学び、決して忘れません</t>
+          <t xml:space="preserve">毎日精進いたします。見ていてください</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9285,7 +9285,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.polite.earnest[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9295,14 +9295,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですが、精一杯務めさせていただきます</t>
+          <t xml:space="preserve">今日は身体が素直に動きます。学んだ分だけ、身につきます</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9317,7 +9317,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.polite.earnest[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9327,14 +9327,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お声がけに恥じないよう、努めます</t>
+          <t xml:space="preserve">同じ量をこなしても、何も積み上がりません。情けないです</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.polite.earnest[1]</t>
+          <t xml:space="preserve">heatSelf.warm.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9359,14 +9359,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">実力が足りませんでした。もっと精進いたします</t>
+          <t xml:space="preserve">回数はこなせています。ただ、残る実感が薄くて</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.polite.earnest[1]</t>
+          <t xml:space="preserve">injury.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9391,14 +9391,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛できました。でも、まだまだ精進いたします</t>
+          <t xml:space="preserve">ご期待に応えられず、申し訳ありません</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.polite.earnest[1]</t>
+          <t xml:space="preserve">injury.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9423,14 +9423,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">努力が足りませんでした。一から出直します</t>
+          <t xml:space="preserve">必ず強くなって戻ってまいります</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.polite.earnest[1]</t>
+          <t xml:space="preserve">release.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9455,14 +9455,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねが報われました…本当に、ありがとうございます</t>
+          <t xml:space="preserve">応援してくださった皆様に、申し訳ありません</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">release.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9487,14 +9487,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくださった皆様に、申し訳ありません</t>
+          <t xml:space="preserve">ここでの学び、決して忘れません</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.earnest[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[2]</t>
+          <t xml:space="preserve">rentalGreeting.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9519,14 +9519,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここでの学び、決して忘れません</t>
+          <t xml:space="preserve">短い間ですが、精一杯務めさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">scoutGreeting.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9551,14 +9551,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですが、精一杯務めさせていただきます</t>
+          <t xml:space="preserve">お声がけに恥じないよう、努めます</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9590,7 +9590,7 @@
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">titleDefense.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9622,7 +9622,7 @@
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9632,12 +9632,12 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">titleLoss.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9654,7 +9654,7 @@
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9664,12 +9664,12 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">titleWin.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9686,7 +9686,7 @@
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9696,29 +9696,29 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この関係…修復できる自信がありません…</t>
+          <t xml:space="preserve">応援してくださった皆様に、申し訳ありません</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.polite[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9728,29 +9728,29 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.earnest.polite[2]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どこで間違えてしまったんでしょう…</t>
+          <t xml:space="preserve">ここでの学び、決して忘れません</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9760,29 +9760,29 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">関係を修復したいです…何とかしなければ</t>
+          <t xml:space="preserve">短い間ですが、精一杯務めさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9792,29 +9792,29 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おかげで練習にも身が入ります。感謝しています</t>
+          <t xml:space="preserve">実力が足りませんでした。もっと精進いたします</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9824,29 +9824,29 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">共に歩めること、何よりの幸せです</t>
+          <t xml:space="preserve">防衛できました。でも、まだまだ精進いたします</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9856,29 +9856,29 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.earnest.polite[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">関係も変わりました。前に進みましょう</t>
+          <t xml:space="preserve">努力が足りませんでした。一から出直します</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.polite[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9888,29 +9888,29 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.earnest.polite[2]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの因縁から学んだことは多いです。次の目標を見つけなければ</t>
+          <t xml:space="preserve">積み重ねが報われました…本当に、ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.earnest.polite[1]</t>
+          <t xml:space="preserve">bond_39_down.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9935,14 +9935,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝つために、もっと努力しなければなりません</t>
+          <t xml:space="preserve">この関係…修復できる自信がありません…</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.polite[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.earnest.polite[1]</t>
+          <t xml:space="preserve">bond_39_down.earnest.polite[2]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9967,14 +9967,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">超えることが、私の覚悟です</t>
+          <t xml:space="preserve">どこで間違えてしまったんでしょう…</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.earnest.polite[1]</t>
+          <t xml:space="preserve">bond_59_down.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9999,14 +9999,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この切磋琢磨こそが、私の原動力です</t>
+          <t xml:space="preserve">関係を修復したいです…何とかしなければ</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.earnest.polite[1]</t>
+          <t xml:space="preserve">bond_60_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -10031,14 +10031,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご期待に添えるよう、精一杯頑張らせていただきます</t>
+          <t xml:space="preserve">おかげで練習にも身が入ります。感謝しています</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.earnest.polite[1]</t>
+          <t xml:space="preserve">bond_80_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -10063,14 +10063,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大変申し訳ありませんが…退団を検討させていただきます</t>
+          <t xml:space="preserve">共に歩めること、何よりの幸せです</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.earnest.polite[1]</t>
+          <t xml:space="preserve">rivalry_29_down.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -10095,14 +10095,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">恐縮ですが…少し運営に対して不安があります…</t>
+          <t xml:space="preserve">関係も変わりました。前に進みましょう</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.polite.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.polite[2]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.polite.earnest[1]</t>
+          <t xml:space="preserve">rivalry_29_down.earnest.polite[2]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -10127,14 +10127,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不甲斐ない試合をしてしまいました。申し訳ございません</t>
+          <t xml:space="preserve">あの因縁から学んだことは多いです。次の目標を見つけなければ</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.polite.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.polite.earnest[1]</t>
+          <t xml:space="preserve">rivalry_30_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -10159,14 +10159,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝利できました。引き続き精進します</t>
+          <t xml:space="preserve">勝つために、もっと努力しなければなりません</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.polite.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.polite.earnest[1]</t>
+          <t xml:space="preserve">rivalry_50_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -10191,14 +10191,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">基本を怠らず、しっかり取り組みます</t>
+          <t xml:space="preserve">超えることが、私の覚悟です</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.polite.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.polite.earnest[1]</t>
+          <t xml:space="preserve">rivalry_70_up.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10223,14 +10223,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ともに成長できることが嬉しいです</t>
+          <t xml:space="preserve">この切磋琢磨こそが、私の原動力です</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.polite.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.polite.earnest[1]</t>
+          <t xml:space="preserve">trust_above_75.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10255,14 +10255,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">追いつくため、日々研鑽します</t>
+          <t xml:space="preserve">ご期待に添えるよう、精一杯頑張らせていただきます</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.polite.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.polite.earnest[1]</t>
+          <t xml:space="preserve">trust_below_20.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10287,14 +10287,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">出場機会をいただけるよう、より一層努力いたします</t>
+          <t xml:space="preserve">大変申し訳ありませんが…退団を検討させていただきます</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.polite.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.polite[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.polite.earnest[1]</t>
+          <t xml:space="preserve">trust_below_35.earnest.polite[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10319,14 +10319,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体調管理を怠りました。しっかり立て直します</t>
+          <t xml:space="preserve">恐縮ですが…少し運営に対して不安があります…</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.polite.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.polite.earnest[1]</t>
+          <t xml:space="preserve">GL-01.loss.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10351,14 +10351,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不甲斐ない結果が続いています…何とか打開しなければ</t>
+          <t xml:space="preserve">不甲斐ない試合をしてしまいました。申し訳ございません</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.polite.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.polite.earnest[1]</t>
+          <t xml:space="preserve">GL-01.win.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10383,14 +10383,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">結果がついてきていますが、慢心せず精進します</t>
+          <t xml:space="preserve">勝利できました。引き続き精進します</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.polite.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.polite.earnest[1]</t>
+          <t xml:space="preserve">GL-02.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10415,14 +10415,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">復帰に向けて、今できることを精一杯やります</t>
+          <t xml:space="preserve">基本を怠らず、しっかり取り組みます</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10432,12 +10432,12 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">GL-04.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10447,14 +10447,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">好調期間は終わりましたが、学びの多い日々でした</t>
+          <t xml:space="preserve">ともに成長できることが嬉しいです</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10464,29 +10464,29 @@
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.earnest[1]</t>
+          <t xml:space="preserve">GL-05.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体はぼろぼろですが…最後まで、全力でお応えします</t>
+          <t xml:space="preserve">追いつくため、日々研鑽します</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10496,29 +10496,29 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.earnest[2]</t>
+          <t xml:space="preserve">GL-06.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで繋いでくれた仲間のために、私が締めます。どんなに痛くても</t>
+          <t xml:space="preserve">出場機会をいただけるよう、より一層努力いたします</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.earnest[3]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10528,29 +10528,29 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.earnest[3]</t>
+          <t xml:space="preserve">GL-07.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">痛みは、勝ってから数えます。今は、目の前の一戦に全部を</t>
+          <t xml:space="preserve">体調管理を怠りました。しっかり立て直します</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10560,29 +10560,29 @@
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.earnest[1]</t>
+          <t xml:space="preserve">GL-08.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手がどなたでも、全力でお応えします。手を抜くのは失礼ですから</t>
+          <t xml:space="preserve">不甲斐ない結果が続いています…何とか打開しなければ</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10592,29 +10592,29 @@
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.earnest[2]</t>
+          <t xml:space="preserve">GL-09.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦ずつ、丁寧に。託された役目、途中で放り出せません</t>
+          <t xml:space="preserve">結果がついてきていますが、慢心せず精進します</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.earnest[3]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10624,29 +10624,29 @@
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.earnest[3]</t>
+          <t xml:space="preserve">GL-10.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まずは目の前の一人に、心を込めて。それが私の役目ですから</t>
+          <t xml:space="preserve">復帰に向けて、今できることを精一杯やります</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10656,29 +10656,29 @@
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、止めました。…息は上がってますが、退きません。次の方も、全力でお相手します</t>
+          <t xml:space="preserve">好調期間は終わりましたが、学びの多い日々でした</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10693,7 +10693,7 @@
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.earnest[2]</t>
+          <t xml:space="preserve">preFinal.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10703,14 +10703,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってます。仲間に繋ぐまで、このリングは渡しません。次、どうぞ</t>
+          <t xml:space="preserve">身体はぼろぼろですが…最後まで、全力でお応えします</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.earnest[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10725,7 +10725,7 @@
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.earnest[3]</t>
+          <t xml:space="preserve">preFinal.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10735,14 +10735,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、お相手しました。…はぁ、まだ立てます。繋ぐまでは、退けませんから</t>
+          <t xml:space="preserve">ここまで繋いでくれた仲間のために、私が締めます。どんなに痛くても</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.earnest[3]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="C320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.earnest[1]</t>
+          <t xml:space="preserve">preFinal.polite.earnest[3]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10767,14 +10767,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">託された順番を、最後まで全うできました。仲間に感謝しています</t>
+          <t xml:space="preserve">痛みは、勝ってから数えます。今は、目の前の一戦に全部を</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="C321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.earnest[2]</t>
+          <t xml:space="preserve">preMatch.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10799,14 +10799,14 @@
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人でつないだ勝利を、団体に持ち帰れます。それが何より嬉しいです</t>
+          <t xml:space="preserve">相手がどなたでも、全力でお応えします。手を抜くのは失礼ですから</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="C322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.polite.earnest[1]</t>
+          <t xml:space="preserve">preMatch.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10831,14 +10831,14 @@
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">評価していただいてありがとうございます。でも、次は団体ごと勝って応えたいです</t>
+          <t xml:space="preserve">一戦ずつ、丁寧に。託された役目、途中で放り出せません</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.earnest[3]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="C323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.polite.earnest[2]</t>
+          <t xml:space="preserve">preMatch.polite.earnest[3]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10863,14 +10863,14 @@
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間のためにもっとやれたはず。その反省を、次に生かします</t>
+          <t xml:space="preserve">まずは目の前の一人に、心を込めて。それが私の役目ですから</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10880,12 +10880,12 @@
       </c>
       <c r="C324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.polite.earnest[1]</t>
+          <t xml:space="preserve">survivor.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10895,14 +10895,14 @@
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で来てくださった皆さんに、全力で応えました。それだけは胸を張れます</t>
+          <t xml:space="preserve">一人、止めました。…息は上がってますが、退きません。次の方も、全力でお相手します</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10912,12 +10912,12 @@
       </c>
       <c r="C325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.polite.earnest[2]</t>
+          <t xml:space="preserve">survivor.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10927,14 +10927,14 @@
       </c>
       <c r="F325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何度も限界を感じました。でも、託された役割を途中で降りるわけにはいきません</t>
+          <t xml:space="preserve">まだ立ってます。仲間に繋ぐまで、このリングは渡しません。次、どうぞ</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.polite.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.earnest[3]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="C326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.earnest[1]</t>
+          <t xml:space="preserve">survivor.polite.earnest[3]</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10959,14 +10959,14 @@
       </c>
       <c r="F326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝…させていただきました。皆様のおかげです…！</t>
+          <t xml:space="preserve">一人、お相手しました。…はぁ、まだ立てます。繋ぐまでは、退けませんから</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.polite.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10976,12 +10976,12 @@
       </c>
       <c r="C327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.earnest[2]</t>
+          <t xml:space="preserve">champion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10991,14 +10991,14 @@
       </c>
       <c r="F327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この経験を糧に、さらに精進して参ります</t>
+          <t xml:space="preserve">託された順番を、最後まで全うできました。仲間に感謝しています</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.polite.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -11008,12 +11008,12 @@
       </c>
       <c r="C328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.polite.earnest[1]</t>
+          <t xml:space="preserve">champion.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -11023,14 +11023,14 @@
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">力不足で申し訳ございません…。もっと精進します</t>
+          <t xml:space="preserve">三人でつないだ勝利を、団体に持ち帰れます。それが何より嬉しいです</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.polite.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="C329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.polite.earnest[2]</t>
+          <t xml:space="preserve">defiant.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -11055,14 +11055,14 @@
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しゅうございます…。必ず強くなります</t>
+          <t xml:space="preserve">評価していただいてありがとうございます。でも、次は団体ごと勝って応えたいです</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.polite.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -11072,12 +11072,12 @@
       </c>
       <c r="C330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.polite.earnest[1]</t>
+          <t xml:space="preserve">defiant.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -11087,14 +11087,14 @@
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝たせていただきました…。次も全力で臨みます</t>
+          <t xml:space="preserve">仲間のためにもっとやれたはず。その反省を、次に生かします</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.polite.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -11104,12 +11104,12 @@
       </c>
       <c r="C331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.polite.earnest[2]</t>
+          <t xml:space="preserve">gauntlet.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
@@ -11119,14 +11119,14 @@
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦一戦、大切に。次もよろしくお願いいたします</t>
+          <t xml:space="preserve">全力で来てくださった皆さんに、全力で応えました。それだけは胸を張れます</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.polite.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -11136,12 +11136,12 @@
       </c>
       <c r="C332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.polite.earnest[1]</t>
+          <t xml:space="preserve">gauntlet.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -11151,14 +11151,14 @@
       </c>
       <c r="F332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">良い経験をさせていただきました。精進して参ります</t>
+          <t xml:space="preserve">何度も限界を感じました。でも、託された役割を途中で降りるわけにはいきません</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.polite.earnest[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.polite.earnest[2]</t>
+          <t xml:space="preserve">champion.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
@@ -11183,14 +11183,14 @@
       </c>
       <c r="F333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様のおかげで戦い抜けました。感謝いたします</t>
+          <t xml:space="preserve">優勝…させていただきました。皆様のおかげです…！</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.polite.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -11205,7 +11205,7 @@
       </c>
       <c r="D334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.earnest[1]</t>
+          <t xml:space="preserve">champion.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E334" t="inlineStr" s="2">
@@ -11215,14 +11215,14 @@
       </c>
       <c r="F334" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝の舞台…身に余る光栄です。全力でお応えいたします</t>
+          <t xml:space="preserve">この経験を糧に、さらに精進して参ります</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.polite.earnest[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="D335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.earnest[2]</t>
+          <t xml:space="preserve">postLose.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
@@ -11247,14 +11247,14 @@
       </c>
       <c r="F335" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この一戦に、全てをお捧げいたします</t>
+          <t xml:space="preserve">力不足で申し訳ございません…。もっと精進します</t>
         </is>
       </c>
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.polite.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -11269,7 +11269,7 @@
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.earnest[1]</t>
+          <t xml:space="preserve">postLose.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E336" t="inlineStr" s="2">
@@ -11279,14 +11279,14 @@
       </c>
       <c r="F336" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">精一杯の試合を、お見せいたします</t>
+          <t xml:space="preserve">悔しゅうございます…。必ず強くなります</t>
         </is>
       </c>
     </row>
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.polite.earnest[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="D337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.earnest[2]</t>
+          <t xml:space="preserve">postMatchWin.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E337" t="inlineStr" s="2">
@@ -11311,14 +11311,14 @@
       </c>
       <c r="F337" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ひとつひとつ丁寧に…全力で参ります</t>
+          <t xml:space="preserve">勝たせていただきました…。次も全力で臨みます</t>
         </is>
       </c>
     </row>
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.polite.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="D338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.polite.earnest[1]</t>
+          <t xml:space="preserve">postMatchWin.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E338" t="inlineStr" s="2">
@@ -11343,14 +11343,14 @@
       </c>
       <c r="F338" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身に余る光栄です。一生懸命頑張ります</t>
+          <t xml:space="preserve">一戦一戦、大切に。次もよろしくお願いいたします</t>
         </is>
       </c>
     </row>
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.polite.earnest[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -11365,7 +11365,7 @@
       </c>
       <c r="D339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.polite.earnest[2]</t>
+          <t xml:space="preserve">postWin.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E339" t="inlineStr" s="2">
@@ -11375,14 +11375,14 @@
       </c>
       <c r="F339" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お声がけいただき感謝いたします。精一杯務めます</t>
+          <t xml:space="preserve">良い経験をさせていただきました。精進して参ります</t>
         </is>
       </c>
     </row>
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -11392,12 +11392,12 @@
       </c>
       <c r="C340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D340" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">postWin.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E340" t="inlineStr" s="2">
@@ -11407,14 +11407,14 @@
       </c>
       <c r="F340" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お互い全力で…よろしくお願いいたします</t>
+          <t xml:space="preserve">皆様のおかげで戦い抜けました。感謝いたします</t>
         </is>
       </c>
     </row>
     <row r="341" ht="40" customHeight="1">
       <c r="A341" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -11424,12 +11424,12 @@
       </c>
       <c r="C341" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D341" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">preFinal.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E341" t="inlineStr" s="2">
@@ -11439,14 +11439,14 @@
       </c>
       <c r="F341" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆さまのご声援のおかげです……本当に、ありがとうございます……！</t>
+          <t xml:space="preserve">決勝の舞台…身に余る光栄です。全力でお応えいたします</t>
         </is>
       </c>
     </row>
     <row r="342" ht="40" customHeight="1">
       <c r="A342" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.polite.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="C342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D342" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">preFinal.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E342" t="inlineStr" s="2">
@@ -11471,14 +11471,14 @@
       </c>
       <c r="F342" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">失礼ながら、対抗戦のお申し込みをさせていただきます</t>
+          <t xml:space="preserve">この一戦に、全てをお捧げいたします</t>
         </is>
       </c>
     </row>
     <row r="343" ht="40" customHeight="1">
       <c r="A343" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.polite.earnest[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -11488,12 +11488,12 @@
       </c>
       <c r="C343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D343" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[2]</t>
+          <t xml:space="preserve">preMatch.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E343" t="inlineStr" s="2">
@@ -11503,14 +11503,14 @@
       </c>
       <c r="F343" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力でお相手いたしますので、覚悟なさってください</t>
+          <t xml:space="preserve">精一杯の試合を、お見せいたします</t>
         </is>
       </c>
     </row>
     <row r="344" ht="40" customHeight="1">
       <c r="A344" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.polite.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -11520,12 +11520,12 @@
       </c>
       <c r="C344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D344" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">preMatch.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E344" t="inlineStr" s="2">
@@ -11535,14 +11535,14 @@
       </c>
       <c r="F344" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残念ですが…いつかお受けいただけることを願っております</t>
+          <t xml:space="preserve">ひとつひとつ丁寧に…全力で参ります</t>
         </is>
       </c>
     </row>
     <row r="345" ht="40" customHeight="1">
       <c r="A345" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.polite.earnest[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="C345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D345" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[2]</t>
+          <t xml:space="preserve">summon.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E345" t="inlineStr" s="2">
@@ -11567,14 +11567,14 @@
       </c>
       <c r="F345" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">改めてお声がけいたします。その時はぜひ</t>
+          <t xml:space="preserve">身に余る光栄です。一生懸命頑張ります</t>
         </is>
       </c>
     </row>
     <row r="346" ht="40" customHeight="1">
       <c r="A346" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.polite.earnest[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
@@ -11584,12 +11584,12 @@
       </c>
       <c r="C346" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D346" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.polite.earnest[1]</t>
+          <t xml:space="preserve">summon.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E346" t="inlineStr" s="2">
@@ -11599,14 +11599,14 @@
       </c>
       <c r="F346" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">完敗でした…。この悔しさを胸に、精進いたします</t>
+          <t xml:space="preserve">お声がけいただき感謝いたします。精一杯務めます</t>
         </is>
       </c>
     </row>
     <row r="347" ht="40" customHeight="1">
       <c r="A347" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.polite.earnest[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -11616,12 +11616,12 @@
       </c>
       <c r="C347" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D347" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.polite.earnest[2]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E347" t="inlineStr" s="2">
@@ -11631,14 +11631,14 @@
       </c>
       <c r="F347" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">申し訳ございません…。必ず成長してお返しいたします</t>
+          <t xml:space="preserve">お互い全力で…よろしくお願いいたします</t>
         </is>
       </c>
     </row>
     <row r="348" ht="40" customHeight="1">
       <c r="A348" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.polite.earnest[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -11648,12 +11648,12 @@
       </c>
       <c r="C348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D348" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E348" t="inlineStr" s="2">
@@ -11663,14 +11663,14 @@
       </c>
       <c r="F348" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝たせていただきました。素晴らしい対抗戦に感謝いたします</t>
+          <t xml:space="preserve">皆さまのご声援のおかげです……本当に、ありがとうございます……！</t>
         </is>
       </c>
     </row>
     <row r="349" ht="40" customHeight="1">
       <c r="A349" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.polite.earnest[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -11680,12 +11680,12 @@
       </c>
       <c r="C349" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D349" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.polite.earnest[2]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E349" t="inlineStr" s="2">
@@ -11695,14 +11695,14 @@
       </c>
       <c r="F349" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様のおかげで勝利できました。ありがとうございます</t>
+          <t xml:space="preserve">失礼ながら、対抗戦のお申し込みをさせていただきます</t>
         </is>
       </c>
     </row>
     <row r="350" ht="40" customHeight="1">
       <c r="A350" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
@@ -11712,12 +11712,12 @@
       </c>
       <c r="C350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D350" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E350" t="inlineStr" s="2">
@@ -11727,14 +11727,14 @@
       </c>
       <c r="F350" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の代表として勝利できましたこと…光栄でございます</t>
+          <t xml:space="preserve">全力でお相手いたしますので、覚悟なさってください</t>
         </is>
       </c>
     </row>
     <row r="351" ht="40" customHeight="1">
       <c r="A351" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.polite.earnest[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="C351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D351" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[2]</t>
+          <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
       <c r="E351" t="inlineStr" s="2">
@@ -11759,14 +11759,14 @@
       </c>
       <c r="F351" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の名に恥じない試合ができたのであれば…嬉しゅうございます</t>
+          <t xml:space="preserve">残念ですが…いつかお受けいただけることを願っております</t>
         </is>
       </c>
     </row>
     <row r="352" ht="40" customHeight="1">
       <c r="A352" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.polite.earnest[3]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="C352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D352" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[3]</t>
+          <t xml:space="preserve">polite.earnest[2]</t>
         </is>
       </c>
       <c r="E352" t="inlineStr" s="2">
@@ -11791,14 +11791,14 @@
       </c>
       <c r="F352" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の皆様のおかげで勝利できました。心より感謝申し上げます</t>
+          <t xml:space="preserve">改めてお声がけいたします。その時はぜひ</t>
         </is>
       </c>
     </row>
     <row r="353" ht="40" customHeight="1">
       <c r="A353" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.polite.earnest[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.polite.earnest[1]</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -11808,29 +11808,29 @@
       </c>
       <c r="C353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D353" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.polite.earnest[1]</t>
+          <t xml:space="preserve">result_lose.polite.earnest[1]</t>
         </is>
       </c>
       <c r="E353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F353" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねてきた全てが報われました…ありがとうございます</t>
+          <t xml:space="preserve">完敗でした…。この悔しさを胸に、精進いたします</t>
         </is>
       </c>
     </row>
     <row r="354" ht="40" customHeight="1">
       <c r="A354" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.polite.earnest[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.polite.earnest[2]</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
@@ -11840,59 +11840,283 @@
       </c>
       <c r="C354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D354" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.earnest[1]</t>
+          <t xml:space="preserve">result_lose.polite.earnest[2]</t>
         </is>
       </c>
       <c r="E354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F354" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いただいた契約の重み、忘れずにやります</t>
+          <t xml:space="preserve">申し訳ございません…。必ず成長してお返しいたします</t>
         </is>
       </c>
     </row>
     <row r="355" ht="40" customHeight="1">
       <c r="A355" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.polite.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.polite.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝たせていただきました。素晴らしい対抗戦に感謝いたします</t>
+        </is>
+      </c>
+    </row>
+    <row r="356" ht="40" customHeight="1">
+      <c r="A356" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.polite.earnest[2]</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.polite.earnest[2]</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">皆様のおかげで勝利できました。ありがとうございます</t>
+        </is>
+      </c>
+    </row>
+    <row r="357" ht="40" customHeight="1">
+      <c r="A357" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">団体の代表として勝利できましたこと…光栄でございます</t>
+        </is>
+      </c>
+    </row>
+    <row r="358" ht="40" customHeight="1">
+      <c r="A358" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.earnest[2]</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.earnest[2]</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">団体の名に恥じない試合ができたのであれば…嬉しゅうございます</t>
+        </is>
+      </c>
+    </row>
+    <row r="359" ht="40" customHeight="1">
+      <c r="A359" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.earnest[3]</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.earnest[3]</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">団体の皆様のおかげで勝利できました。心より感謝申し上げます</t>
+        </is>
+      </c>
+    </row>
+    <row r="360" ht="40" customHeight="1">
+      <c r="A360" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.polite.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.polite.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">積み重ねてきた全てが報われました…ありがとうございます</t>
+        </is>
+      </c>
+    </row>
+    <row r="361" ht="40" customHeight="1">
+      <c r="A361" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.polite.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いただいた契約の重み、忘れずにやります</t>
+        </is>
+      </c>
+    </row>
+    <row r="362" ht="40" customHeight="1">
+      <c r="A362" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.polite.earnest[1]</t>
         </is>
       </c>
-      <c r="B355" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr" s="2">
+      <c r="B362" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr" s="12">
+      <c r="D362" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">polite.earnest[1]</t>
         </is>
       </c>
-      <c r="E355" t="inlineStr" s="2">
+      <c r="E362" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F355" t="inlineStr" s="3">
+      <c r="F362" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">お声がけに恥じないよう、努めます</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H355"/>
+  <autoFilter ref="A1:H362"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/丁寧×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×真面目.xlsx
@@ -2699,7 +2699,7 @@
       </c>
       <c r="F68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、ご迷惑は承知しています。それでも、あの方とやらせていただけませんか。</t>
+          <t xml:space="preserve">社長、ご迷惑は承知しております。それでも三人で挑ませてください。</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="F69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不躾なお願いだと分かっています。……あの方と、闘わせてください。</t>
+          <t xml:space="preserve">不躾なお願いだと分かっています。……三人で、乗り込ませてください。</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="F70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。どうかお願いします。あの方とだけは、やらせていただきたくて。</t>
+          <t xml:space="preserve">社長。どうかお願いします。この挑戦だけは、三人で行かせてください。</t>
         </is>
       </c>
     </row>
